--- a/GARP_Quiz.xlsx
+++ b/GARP_Quiz.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Carl\Desktop\GARP\AI generated quiz\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3315504D-0536-47EF-ABEC-BAAD1899EF93}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92234204-2187-4CB1-AA50-63B04FB3D088}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-60" yWindow="-16320" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7589" uniqueCount="4835">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9389" uniqueCount="6028">
   <si>
     <t>Module</t>
   </si>
@@ -14548,18 +14548,3604 @@
   <si>
     <t>Claude (set2) - Module 5</t>
   </si>
+  <si>
+    <t>A vendor markets its platform as 'AGI-ready' because it performs well on fraud detection, document classification and customer-churn prediction. Which assessment is most appropriate?</t>
+  </si>
+  <si>
+    <t>It qualifies as AGI, since breadth across three banking tasks is the accepted threshold for general intelligence</t>
+  </si>
+  <si>
+    <t>It is classical AI, since a system that performs several different tasks must rely on hand-coded IF-THEN rules</t>
+  </si>
+  <si>
+    <t>It is narrow AI only until it is trained on labeled data, after which it automatically becomes general AI</t>
+  </si>
+  <si>
+    <t>It is still narrow AI, since strong results on several specific tasks do not show human-like ability on any task</t>
+  </si>
+  <si>
+    <t>Narrow AI performs specific tasks well, whereas AGI means human-like ability across any intellectual task, and its arrival is an open, contested question. Performing well on several specific tasks does not make a system general, and the number of tasks says nothing about whether rules or learning are used.</t>
+  </si>
+  <si>
+    <t>In a two-ply game tree, the program (MAX) chooses among moves A, B and C, and the opponent (MIN) then replies. The leaf values after the opponent's replies are A: 4, 7, 6; B: 5, 2, 8; C: 3, 9, 5. Assuming the opponent plays optimally, which move does adversarial search select and what is its value?</t>
+  </si>
+  <si>
+    <t>Move A, with a value of 4</t>
+  </si>
+  <si>
+    <t>Move B, with a value of 8</t>
+  </si>
+  <si>
+    <t>Move C, with a value of 9</t>
+  </si>
+  <si>
+    <t>Move A, with a value of 7</t>
+  </si>
+  <si>
+    <t>Adversarial search assumes the opponent picks the reply that is best for the opponent, so each branch is worth its minimum leaf: A = 4, B = 2, C = 3. MAX then picks the largest of these, which is move A with value 4. Values of 9, 8 and 7 are the largest leaves in a branch and assume a cooperative opponent.</t>
+  </si>
+  <si>
+    <t>A network has inputs x = (1, 2), a hidden layer of two ReLU neurons and a linear output. Hidden neuron 1 has weights (0.5, -1.0) and bias 1.0; hidden neuron 2 has weights (1.0, 0.5) and bias -0.5. The output is 2 x h1 + 4 x h2 - 1. What is the output?</t>
+  </si>
+  <si>
+    <t>7.0</t>
+  </si>
+  <si>
+    <t>6.0</t>
+  </si>
+  <si>
+    <t>h1 = ReLU(0.5 - 2.0 + 1.0) = ReLU(-0.5) = 0 and h2 = ReLU(1.0 + 1.0 - 0.5) = 1.5, so the output is 0 + 6 - 1 = 5.0. The value 4.0 skips the ReLU (h1 = -0.5), 6.0 drops the output bias, and 7.0 drops the hidden-layer biases (h1 = 0, h2 = 2).</t>
+  </si>
+  <si>
+    <t>Which statement best distinguishes connectionism from GOFAI?</t>
+  </si>
+  <si>
+    <t>Connectionism is limited to games with perfect information, while GOFAI is designed for noisy perception problems such as images</t>
+  </si>
+  <si>
+    <t>Connectionism lets intelligence emerge from many simple connected units with learned weights, while GOFAI uses explicit rules</t>
+  </si>
+  <si>
+    <t>Connectionism requires a search tree with lookahead at every move, while GOFAI relies on activation functions to model non-linearity</t>
+  </si>
+  <si>
+    <t>Connectionism relies on hand-coded symbolic rules written by experts, while GOFAI learns its weights from data using backpropagation</t>
+  </si>
+  <si>
+    <t>Connectionism holds that intelligence can emerge from networks of simple, interconnected units, with learning adjusting the connection weights. GOFAI instead relies on explicit, human-coded rules and logic, which is why it struggles with noisy, unstructured problems.</t>
+  </si>
+  <si>
+    <t>A bank replaces 30 correlated macro variables with 4 principal components in a credit model. Multicollinearity falls and out-of-sample fit improves. Which risk consideration is most directly raised?</t>
+  </si>
+  <si>
+    <t>Each component blends many variables, so explaining any one macro variable's effect on a decision becomes harder</t>
+  </si>
+  <si>
+    <t>PCA produces correlated components, so the multicollinearity is merely moved into the transformed variables</t>
+  </si>
+  <si>
+    <t>PCA discards all but the four highest-variance variables, so the retained inputs are a simple subset of the originals</t>
+  </si>
+  <si>
+    <t>PCA is a supervised technique, so the components embed the default labels and leak outcomes into the predictors</t>
+  </si>
+  <si>
+    <t>PCA is unsupervised and creates uncorrelated linear combinations of the original variables. That helps with multicollinearity but each component mixes many inputs, which reduces interpretability and makes individual decisions harder to explain, linking to the inscrutability risk.</t>
+  </si>
+  <si>
+    <t>Consider: (1) one qualified applicant is wrongly declined by a credit model; (2) the bank receives a regulatory penalty and adverse press because of the model; (3) the same flawed model is licensed to 200 lenders and repeats the error across a market. Which assignment to the levels of ML risk is correct?</t>
+  </si>
+  <si>
+    <t>(1) individual; (2) societal; (3) organizational</t>
+  </si>
+  <si>
+    <t>(1) individual; (2) organizational; (3) societal</t>
+  </si>
+  <si>
+    <t>(1) organizational; (2) individual; (3) societal</t>
+  </si>
+  <si>
+    <t>(1) societal; (2) organizational; (3) individual</t>
+  </si>
+  <si>
+    <t>ML risk operates at three levels at once: individual (a wrongful denial), organizational (regulatory penalty, reputational damage) and societal (one flawed model replicating errors at massive scale).</t>
+  </si>
+  <si>
+    <t>An analyst has 80 observations and a relationship that appears curved, and fits a linear regression. Which statement about parametric and non-parametric approaches is most accurate?</t>
+  </si>
+  <si>
+    <t>The linear form may be misspecified; non-parametric methods are more flexible but need more than 80 observations</t>
+  </si>
+  <si>
+    <t>Non-parametric methods are always preferred, because their flexibility removes the need for out-of-sample validation</t>
+  </si>
+  <si>
+    <t>Parametric methods impose no functional form, so a linear fit cannot be misspecified whatever the sample size</t>
+  </si>
+  <si>
+    <t>Non-parametric methods assume a fixed functional form, so they need fewer observations than parametric methods</t>
+  </si>
+  <si>
+    <t>Parametric methods assume a functional form and can be misspecified if the form is wrong. Non-parametric methods impose no explicit form and are more flexible, but they generally require more observations. Flexible models still need out-of-sample validation.</t>
+  </si>
+  <si>
+    <t>In a loan data set, income is missing for 12% of applicants, and defaults are far more common among those applicants. The analyst deletes every row with missing income. What is the main problem?</t>
+  </si>
+  <si>
+    <t>Deletion creates the dummy variable trap, because missing income behaves like an omitted category in the regression</t>
+  </si>
+  <si>
+    <t>Deletion changes the scale of the income variable, so the remaining values must be standardized again before the model is fitted</t>
+  </si>
+  <si>
+    <t>Missingness is informative, so deletion drops a systematically different group and biases the model's estimates</t>
+  </si>
+  <si>
+    <t>Deletion is always preferred, because imputed values are guaranteed to be more biased than the observed data</t>
+  </si>
+  <si>
+    <t>Missing data can be informative and create bias. Here the missing group differs systematically in default behavior, so dropping it distorts the estimates. Remedies include imputation or using models that can handle missing values.</t>
+  </si>
+  <si>
+    <t>Annual incomes of four borrowers are 25,000, 50,000, 100,000 and 200,000. After a natural-log transformation, what is the difference between successive transformed values, and how does the transformation differ from scaling?</t>
+  </si>
+  <si>
+    <t>About 0.69 each; the log preserves the shape of the distribution exactly as standardization does</t>
+  </si>
+  <si>
+    <t>About 0.69 each; the log changes the shape of the distribution and reduces right skew, whereas scaling keeps the shape</t>
+  </si>
+  <si>
+    <t>About 0.30 each; the log changes the shape of the distribution and reduces right skew, whereas scaling keeps the shape</t>
+  </si>
+  <si>
+    <t>About 1.00 each; the log maps the values to the 0-1 range in the same way as min-max normalization does</t>
+  </si>
+  <si>
+    <t>Each income is double the previous one, so successive natural logs differ by ln 2 = 0.69. Transformation changes the shape of a distribution (and can change correlations), whereas scaling such as standardization or normalization preserves the shape. The value 0.30 is the base-10 logarithm of 2.</t>
+  </si>
+  <si>
+    <t>Which statement best contrasts the machine-learning approach with classical econometrics?</t>
+  </si>
+  <si>
+    <t>ML is used only with small structured data sets, whereas econometrics is designed for big and wide data</t>
+  </si>
+  <si>
+    <t>ML stresses model selection, tuning and out-of-sample prediction, with the data-generating process largely unknown</t>
+  </si>
+  <si>
+    <t>ML emphasizes t-values, p-values and in-sample R-squared to test hypotheses about a known data-generating process</t>
+  </si>
+  <si>
+    <t>ML requires a specified functional form, whereas classical econometrics lets the data choose the functional form</t>
+  </si>
+  <si>
+    <t>Compared with classical statistics and econometrics, ML treats the data-generating process as largely unknown, emphasizes model selection and tuning, and focuses on out-of-sample prediction more than on inference using t-values, p-values and R-squared. It is particularly useful for big or wide data and nonlinear relationships.</t>
+  </si>
+  <si>
+    <t>An agglomerative clustering of points A to E merges A and B at height 1.2, C and D at 1.5, E into {C, D} at 3.1, and the two remaining clusters at 6.8. How many clusters result from cutting the dendrogram at heights of 2.0 and 5.0, respectively?</t>
+  </si>
+  <si>
+    <t>2 and 1</t>
+  </si>
+  <si>
+    <t>3 and 1</t>
+  </si>
+  <si>
+    <t>4 and 3</t>
+  </si>
+  <si>
+    <t>3 and 2</t>
+  </si>
+  <si>
+    <t>At height 2.0 only the merges at 1.2 and 1.5 have occurred, leaving {A, B}, {C, D} and {E}: 3 clusters. At height 5.0 the merge at 3.1 has also occurred, leaving {A, B} and {C, D, E}: 2 clusters. Only a cut above 6.8 gives a single cluster.</t>
+  </si>
+  <si>
+    <t>A cluster contains the one-dimensional points 1, 2 and 3 (centroid 2). A new point at 100 is assigned to it and the centroid is recomputed. What is the new centroid and which weakness of K-means does this illustrate?</t>
+  </si>
+  <si>
+    <t>51.0; sensitivity to outliers that pull the centroid away from the bulk of the cluster</t>
+  </si>
+  <si>
+    <t>26.5; sensitivity to outliers that pull the centroid away from the bulk of the cluster</t>
+  </si>
+  <si>
+    <t>35.3; sensitivity to outliers that pull the centroid away from the bulk of the cluster</t>
+  </si>
+  <si>
+    <t>26.5; dependence on random starting centroids that can lead to a local optimum</t>
+  </si>
+  <si>
+    <t>The new centroid is (1 + 2 + 3 + 100) / 4 = 26.5. One extreme point drags the centroid far from the other three, showing K-means' sensitivity to outliers. The value 35.3 divides by the old count of 3, and 51.0 averages the old centroid with the outlier.</t>
+  </si>
+  <si>
+    <t>WCSS from K-means for k = 1 to 5 is 900, 500, 300, 260 and 240. Which choice of k does the elbow method suggest?</t>
+  </si>
+  <si>
+    <t>k = 4, since WCSS keeps falling beyond k = 3 and is still well below the level reached at k = 3</t>
+  </si>
+  <si>
+    <t>k = 3, since the marginal reduction in WCSS drops sharply from 200 to 40 after the third cluster</t>
+  </si>
+  <si>
+    <t>k = 5, since WCSS is lowest there and the lowest WCSS always identifies the best number of clusters</t>
+  </si>
+  <si>
+    <t>k = 2, since the first additional cluster produces the largest reduction in WCSS of any step</t>
+  </si>
+  <si>
+    <t>The reductions are 400 (k = 1 to 2), 200 (2 to 3), 40 (3 to 4) and 20 (4 to 5). The elbow is where the improvement flattens, at k = 3. WCSS falls mechanically as k rises, so the lowest WCSS is not a valid criterion.</t>
+  </si>
+  <si>
+    <t>A bank wants nested customer segments that can be viewed at coarse and fine granularity without choosing the number of segments beforehand. Which method fits and why?</t>
+  </si>
+  <si>
+    <t>PCA, because its ordered components define nested clusters whose number equals the number of components retained</t>
+  </si>
+  <si>
+    <t>DBSCAN, because the eps and minimum-points settings fix how many clusters appear at each level of granularity</t>
+  </si>
+  <si>
+    <t>Agglomerative hierarchical clustering, since its dendrogram can be cut at different heights for different cluster counts</t>
+  </si>
+  <si>
+    <t>K-means, because its centroid updates produce a dendrogram that can be cut at different heights for different granularity</t>
+  </si>
+  <si>
+    <t>Agglomerative clustering starts with each point as its own cluster and merges the closest pairs, so it does not require k in advance and its dendrogram can be cut at any height. K-means needs k and produces no dendrogram, and PCA is a dimensionality-reduction method rather than a clustering method.</t>
+  </si>
+  <si>
+    <t>A regression of default loss on exposure shows residuals that fan out as the fitted values increase. Which statement is most accurate?</t>
+  </si>
+  <si>
+    <t>Error variance is constant (homoskedasticity); coefficients are biased but the usual standard errors are reliable</t>
+  </si>
+  <si>
+    <t>A relevant variable was omitted (omitted variable bias); coefficients are unbiased but the standard errors are too small</t>
+  </si>
+  <si>
+    <t>Error variance is non-constant (heteroskedasticity); coefficients stay unbiased but standard errors are unreliable</t>
+  </si>
+  <si>
+    <t>Predictors are highly correlated (multicollinearity); coefficients are biased but the residuals have constant variance</t>
+  </si>
+  <si>
+    <t>Residuals that widen as fitted values rise indicate heteroskedasticity, meaning non-constant error variance. OLS coefficients remain unbiased, but conventional standard errors are unreliable, so inference needs adjustment. The other options mislabel the problem or its consequences.</t>
+  </si>
+  <si>
+    <t>The true model is default = b1 x DTI + b2 x Income + error, with b2 &lt; 0, and DTI and Income are negatively correlated. An analyst omits Income. What is the likely effect on the estimated DTI coefficient?</t>
+  </si>
+  <si>
+    <t>It is biased upward, since the omitted negative effect times its negative correlation with DTI is positive</t>
+  </si>
+  <si>
+    <t>It remains unbiased, since omitting a variable only affects the standard errors of the included coefficients</t>
+  </si>
+  <si>
+    <t>It is biased toward zero, since dropping any variable always shrinks the remaining coefficients</t>
+  </si>
+  <si>
+    <t>It is biased downward, since the omitted variable's negative effect passes straight into the DTI coefficient</t>
+  </si>
+  <si>
+    <t>Omitted variable bias is approximately b2 x cov(DTI, Income) / var(DTI). With b2 negative and the covariance negative, the product is positive, so the DTI coefficient is biased upward: DTI picks up the risk that is really due to low income.</t>
+  </si>
+  <si>
+    <t>A logistic regression has a DTI coefficient of 0.5 per unit. For a borrower whose current default probability is 0.20, approximately how much does a one-unit increase in DTI raise the default probability?</t>
+  </si>
+  <si>
+    <t>About 10 percentage points</t>
+  </si>
+  <si>
+    <t>About 40 percentage points</t>
+  </si>
+  <si>
+    <t>About 50 percentage points</t>
+  </si>
+  <si>
+    <t>About 8 percentage points</t>
+  </si>
+  <si>
+    <t>In a logit model the marginal effect on probability is approximately p(1 - p) x coefficient = 0.20 x 0.80 x 0.5 = 0.08, so about 8 percentage points. The coefficient itself is a change in log-odds, not in probability, and the figures 10 and 40 points each use only one of the two probability factors.</t>
+  </si>
+  <si>
+    <t>Forward stepwise selection picks 9 of 40 candidate variables and gives an in-sample R-squared of 0.91, while on a hold-out sample R-squared is 0.55. What is the most likely explanation?</t>
+  </si>
+  <si>
+    <t>Nine variables are too few, so underfitting explains the high in-sample and lower hold-out results</t>
+  </si>
+  <si>
+    <t>The hold-out sample is contaminated by training data, so the in-sample R-squared of 0.91 is the reliable figure</t>
+  </si>
+  <si>
+    <t>Stepwise selection fitted noise specific to the estimation sample, so the model overfits and does not generalize</t>
+  </si>
+  <si>
+    <t>Forward selection biases coefficients toward zero, so hold-out R-squared is always lower by design</t>
+  </si>
+  <si>
+    <t>Stepwise regression automates variable selection but can overfit to the particular data set: choosing a few variables from many candidates exploits chance patterns. A large gap between in-sample and out-of-sample fit is the classic sign of overfitting.</t>
+  </si>
+  <si>
+    <t>Adding a second, highly correlated predictor X2 changes the coefficient on X1 from 2.5 (standard error 0.4) to 0.4 (standard error 1.8). What best explains this?</t>
+  </si>
+  <si>
+    <t>Omitted variable bias: X2 was previously omitted from both models, so X1's coefficient is now unbiased and precise</t>
+  </si>
+  <si>
+    <t>Overfitting: the extra predictor enlarges the sample, which inflates the standard error of the X1 coefficient</t>
+  </si>
+  <si>
+    <t>Multicollinearity: X1 and X2 carry overlapping information, so each coefficient is estimated imprecisely and becomes unstable</t>
+  </si>
+  <si>
+    <t>Heteroskedasticity: error variance differs between X1 and X2, so the coefficients shrink and standard errors rise by chance</t>
+  </si>
+  <si>
+    <t>When predictors are highly correlated, the model cannot separate their individual effects, so coefficients become unstable and their standard errors inflate. The coefficient on X1 measures its effect holding X2 constant, which is poorly identified when they move together.</t>
+  </si>
+  <si>
+    <t>A regression tree considers splitting a node with target values 4, 6, 10 and 12 into {4, 6} and {10, 12}. By how much does the split reduce the sum of squared errors, with each leaf predicting its mean?</t>
+  </si>
+  <si>
+    <t>40</t>
+  </si>
+  <si>
+    <t>36</t>
+  </si>
+  <si>
+    <t>18</t>
+  </si>
+  <si>
+    <t>Before the split the mean is 8 and SSE = 16 + 4 + 4 + 16 = 40. After the split the leaf means are 5 and 11, giving SSE = 1 + 1 + 1 + 1 = 4. The reduction is 40 - 4 = 36. The value 40 is the parent SSE and 4 is the SSE remaining after the split.</t>
+  </si>
+  <si>
+    <t>In gradient boosting with squared-error loss, the current prediction for an observation is 10 and the actual value is 16. The next tree predicts the residual as 5, and the learning rate is 0.2. What is the updated prediction?</t>
+  </si>
+  <si>
+    <t>11.0</t>
+  </si>
+  <si>
+    <t>15.0</t>
+  </si>
+  <si>
+    <t>11.2</t>
+  </si>
+  <si>
+    <t>16.0</t>
+  </si>
+  <si>
+    <t>The update adds the learning rate times the new tree's output: 10 + 0.2 x 5 = 11.0. The value 15.0 omits the learning rate, 16.0 jumps straight to the actual value, and 11.2 uses the true residual of 6 instead of the tree's prediction.</t>
+  </si>
+  <si>
+    <t>KNN training and validation error rates are: k = 1: 0% and 22%; k = 5: 9% and 14%; k = 15: 11% and 12%; k = 50: 18% and 19%; k = 200: 30% and 31%. Which k should be chosen and why?</t>
+  </si>
+  <si>
+    <t>k = 15, because validation error is lowest and the gap between training and validation error is small</t>
+  </si>
+  <si>
+    <t>k = 50, because larger k always generalizes better and the training-validation gap remains small</t>
+  </si>
+  <si>
+    <t>k = 1, because zero training error shows that the model fits the data perfectly and will generalize</t>
+  </si>
+  <si>
+    <t>k = 5, because validation error is below 15% there and training error is under 10%</t>
+  </si>
+  <si>
+    <t>Models are selected on validation error, which is lowest (12%) at k = 15 with only a 1-point gap. At k = 1 the model memorizes the training data (overfitting), while k = 50 and k = 200 are too smooth and underfit, raising error on both samples.</t>
+  </si>
+  <si>
+    <t>Two classes of transactions form concentric rings, so no straight line separates them. Which SVM feature addresses this and how does it work?</t>
+  </si>
+  <si>
+    <t>A wider margin, which bends the boundary around the inner ring by weighting the outer ring points more heavily</t>
+  </si>
+  <si>
+    <t>Pruning, which removes low-value branches so that the resulting decision boundary becomes non-linear in shape</t>
+  </si>
+  <si>
+    <t>Backpropagation, which adjusts the boundary by passing the classification error backward through hidden layers</t>
+  </si>
+  <si>
+    <t>The kernel trick, which implicitly maps the data to a higher-dimensional space where a line can separate them</t>
+  </si>
+  <si>
+    <t>SVM finds the boundary that maximizes the margin between classes, and the kernel trick lets it handle non-linearly separable data by working in a higher-dimensional feature space. Backpropagation belongs to neural networks and pruning to decision trees.</t>
+  </si>
+  <si>
+    <t>A network computes y = w2 x ReLU(w1 x x) with x = 2, w1 = 0.5 and w2 = 3. The target is 4 and the loss is (1/2)(y - target)^2. With a learning rate of 0.1, what is w1 after one gradient-descent update?</t>
+  </si>
+  <si>
+    <t>1.1</t>
+  </si>
+  <si>
+    <t>0.8</t>
+  </si>
+  <si>
+    <t>-0.1</t>
+  </si>
+  <si>
+    <t>0.7</t>
+  </si>
+  <si>
+    <t>The forward pass gives ReLU(1) = 1 and y = 3, so the error is y - target = -1. By the chain rule dL/dw1 = (y - target) x w2 x ReLU'(1) x x = -1 x 3 x 1 x 2 = -6, so w1 = 0.5 - 0.1(-6) = 1.1. The value -0.1 has the wrong sign, 0.8 omits the factor x, and 0.7 omits w2.</t>
+  </si>
+  <si>
+    <t>A fully grown decision tree classifies 100% of the training cases correctly but only 70% of the validation cases. What does pruning do and what is the expected effect?</t>
+  </si>
+  <si>
+    <t>It removes low-value branches, adding a little bias but cutting variance, which usually improves validation results</t>
+  </si>
+  <si>
+    <t>It adds branches until every leaf is pure, lowering bias and improving performance on unseen data later</t>
+  </si>
+  <si>
+    <t>It removes low-value branches, lowering bias but raising variance, which usually improves validation performance</t>
+  </si>
+  <si>
+    <t>It randomly disables neurons during training, lowering variance without changing the structure of the tree</t>
+  </si>
+  <si>
+    <t>Pruning removes branches that add little predictive value, which reduces overfitting: a slightly simpler tree (a little more bias) varies much less from sample to sample (lower variance). Random disabling of neurons describes dropout in neural networks.</t>
+  </si>
+  <si>
+    <t>A convolutional layer applies 16 filters of size 3 x 3 to an input with 3 channels, and each filter has one bias term. How many trainable parameters does the layer have?</t>
+  </si>
+  <si>
+    <t>144</t>
+  </si>
+  <si>
+    <t>448</t>
+  </si>
+  <si>
+    <t>432</t>
+  </si>
+  <si>
+    <t>160</t>
+  </si>
+  <si>
+    <t>Each filter has 3 x 3 x 3 = 27 weights plus 1 bias = 28 parameters, and 16 x 28 = 448. The value 432 omits the biases, 160 ignores the 3 input channels ((9 + 1) x 16), and 144 ignores both channels and biases.</t>
+  </si>
+  <si>
+    <t>A lender clusters all loans into 3 groups. Cluster 1 holds 10 labeled loans (8 default, 2 non-default), cluster 2 holds 6 labeled loans (1 default, 5 non-default) and cluster 3 holds no labeled loans. What does cluster-then-label do?</t>
+  </si>
+  <si>
+    <t>It labels cluster 1 non-default and cluster 2 default, using each cluster's minority class; cluster 3 copies its nearest cluster</t>
+  </si>
+  <si>
+    <t>It labels cluster 1 default and cluster 2 non-default; cluster 3 receives the overall majority label by assumption</t>
+  </si>
+  <si>
+    <t>It labels all three clusters default, because cluster 1 has the highest default share in the whole sample</t>
+  </si>
+  <si>
+    <t>It labels cluster 1 default and cluster 2 non-default; cluster 3 cannot be labeled by this rule without more labels</t>
+  </si>
+  <si>
+    <t>In cluster-then-label every cluster takes the majority class of its labeled members, so cluster 1 becomes default and cluster 2 non-default. A cluster with no labeled members has no majority class to assign, so the method cannot label it without additional information.</t>
+  </si>
+  <si>
+    <t>Match each statement to its semi-supervised assumption: (i) nearby points should share a label, so the decision boundary lies in a low-density region; (ii) high-dimensional data lie close to a lower-dimensional structure; (iii) data form distinct groups separated by sparse regions, each group being one class.</t>
+  </si>
+  <si>
+    <t>(i) smoothness; (ii) manifold; (iii) clustering</t>
+  </si>
+  <si>
+    <t>(i) clustering; (ii) smoothness; (iii) manifold</t>
+  </si>
+  <si>
+    <t>(i) manifold; (ii) clustering; (iii) smoothness</t>
+  </si>
+  <si>
+    <t>(i) smoothness; (ii) clustering; (iii) manifold</t>
+  </si>
+  <si>
+    <t>The three assumptions are smoothness (close points share labels and the boundary sits in a low-density region), manifold (high-dimensional data lie near a simpler lower-dimensional structure) and clustering (distinct clusters separated by low-density regions, each corresponding to a class).</t>
+  </si>
+  <si>
+    <t>In co-training with Model A (balance-only view) and Model B (income-only view), Model A's most confident prediction is observation 4 (Default) and Model B's is observation 7 (Non-Default). What happens next?</t>
+  </si>
+  <si>
+    <t>Observation 4 (Default) joins Model B's training set and observation 7 (Non-Default) joins Model A's</t>
+  </si>
+  <si>
+    <t>Both observations join both models' training sets, labeled by whichever model is more confident</t>
+  </si>
+  <si>
+    <t>Neither is added until both models independently select the same observation as most confident</t>
+  </si>
+  <si>
+    <t>Observation 4 joins Model A's own training set and observation 7 joins Model B's own training set</t>
+  </si>
+  <si>
+    <t>In co-training, each model's single most confident pseudo-label is added to the other model's training set, so each model teaches the other from independent feature evidence. This is why error reinforcement is lower than in self-training.</t>
+  </si>
+  <si>
+    <t>An epsilon-greedy agent faces 5 slot machines with epsilon = 0.2. When it explores, it picks uniformly among all 5 machines, including the one currently believed best. What is the probability that it plays the currently best machine on a given trial?</t>
+  </si>
+  <si>
+    <t>0.16</t>
+  </si>
+  <si>
+    <t>0.84</t>
+  </si>
+  <si>
+    <t>0.96</t>
+  </si>
+  <si>
+    <t>The agent exploits with probability 1 - 0.2 = 0.80 and explores with probability 0.20, in which case it picks the best machine 1 time in 5. So P(best) = 0.80 + 0.20 x 0.20 = 0.84. The value 0.80 ignores the chance of choosing it while exploring, 0.96 adds 0.2 x 0.8 instead, and 0.16 is the probability of exploring and picking another machine.</t>
+  </si>
+  <si>
+    <t>Which statement correctly distinguishes a Markov decision process (MDP) from a multi-armed bandit?</t>
+  </si>
+  <si>
+    <t>In a bandit actions change the state and the next state depends only on the current state and action; an MDP has one constant state</t>
+  </si>
+  <si>
+    <t>In an MDP the next state depends on the full history of past states and actions; a bandit has transition probabilities</t>
+  </si>
+  <si>
+    <t>In an MDP rewards are never delayed because each action affects only that round; a bandit has changing states</t>
+  </si>
+  <si>
+    <t>In an MDP actions change the state and the next state depends only on the current state and action; a bandit has one constant state</t>
+  </si>
+  <si>
+    <t>A multi-armed bandit has a single, constant state and each action affects only that round's reward. An MDP covers problems in which actions change the state (such as a trading algorithm changing its portfolio), and the Markov property says the next state depends only on the current state and action, not on earlier history.</t>
+  </si>
+  <si>
+    <t>Which setting is best suited to model-based reinforcement learning?</t>
+  </si>
+  <si>
+    <t>A board game with known rules and finite actions, where the environment can be modeled and solved by planning</t>
+  </si>
+  <si>
+    <t>A recommendation engine learning from user clicks, without any explicit model of how users respond to actions</t>
+  </si>
+  <si>
+    <t>A trading agent in markets with unknown dynamics, learning only from realized trial-and-error experience over time</t>
+  </si>
+  <si>
+    <t>A self-driving car in dense traffic, where the environment is too complex to be modeled accurately in advance</t>
+  </si>
+  <si>
+    <t>Model-based RL uses an explicit model of the environment and works well for simple, well-defined settings with finite actions, as in AlphaZero mastering chess and Go. Model-free RL learns directly from experience and is needed when the real world is too complex to model accurately.</t>
+  </si>
+  <si>
+    <t>An RL task has a state space made of raw game-screen images, far too large for a table of Q-values. Which approach does the book describe for this problem?</t>
+  </si>
+  <si>
+    <t>A Monte Carlo lookup table, which stores a separate Q-value for each image after complete episodes</t>
+  </si>
+  <si>
+    <t>A policy-gradient method with a Q-table, which learns the value of every state-action pair before acting</t>
+  </si>
+  <si>
+    <t>A Deep Q-Network, which pairs temporal-difference Q-learning with a neural network that approximates Q(s, a)</t>
+  </si>
+  <si>
+    <t>An epsilon-greedy bandit, which tracks one Q-value per image and ignores the state transitions</t>
+  </si>
+  <si>
+    <t>Deep RL combines RL with neural networks to scale to huge, high-dimensional state spaces. The Deep Q-Network (DQN) combines the TD method (Q-learning) with a neural network that approximates Q(s, a) instead of storing every value in a table.</t>
+  </si>
+  <si>
+    <t>For a linear regression whose errors are independent, normal, zero-mean and of constant variance, how do the OLS and maximum likelihood estimates compare, and which method is preferred?</t>
+  </si>
+  <si>
+    <t>They are identical, so MLE is preferred because OLS cannot be used when the target is continuous</t>
+  </si>
+  <si>
+    <t>MLE gives larger coefficients because it ignores squared residuals, so MLE is preferred in this case</t>
+  </si>
+  <si>
+    <t>They differ, because MLE minimizes squared residuals while OLS maximizes the likelihood of the observed data</t>
+  </si>
+  <si>
+    <t>They are identical, but OLS is preferred because it is simpler and has an analytical solution</t>
+  </si>
+  <si>
+    <t>Under those error assumptions, MLE and OLS give identical estimates for linear regression, but OLS is simpler and tractable. MLE's value lies in its flexibility, for example for logit and probit models where the target is binary and OLS cannot be used.</t>
+  </si>
+  <si>
+    <t>An optimizer tests small one-parameter-at-a-time changes and keeps those that improve the objective, using no derivatives. Which statement about this method is correct?</t>
+  </si>
+  <si>
+    <t>It works on non-differentiable objectives, but is slow, misses parameter interactions and can stall at a local optimum</t>
+  </si>
+  <si>
+    <t>It needs the chain rule to update every weight at once, so it can be used only on differentiable neural networks</t>
+  </si>
+  <si>
+    <t>It adds a fraction of the previous update to each step, which is how it escapes shallow local minima and plateaus</t>
+  </si>
+  <si>
+    <t>It always finds the global optimum, because small changes in one parameter eventually explore every combination</t>
+  </si>
+  <si>
+    <t>This describes hill climbing: a simple heuristic that needs no derivatives, but changes one parameter at a time, is slow and easily gets stuck in local optima. Momentum (adding a fraction of the previous update) is a refinement of gradient descent, and the chain rule is used in backpropagation.</t>
+  </si>
+  <si>
+    <t>A model y = w x is fitted to the data (x, y) = (1, 3) and (2, 5) by minimizing the mean squared error. Starting from w = 1 with a learning rate of 0.05, what is w after one gradient-descent step?</t>
+  </si>
+  <si>
+    <t>1.25</t>
+  </si>
+  <si>
+    <t>0.6</t>
+  </si>
+  <si>
+    <t>1.4</t>
+  </si>
+  <si>
+    <t>1.2</t>
+  </si>
+  <si>
+    <t>Predictions are 1 and 2, so the errors (prediction - y) are -2 and -3. The MSE gradient is (2/N) x sum(error x x) = (2/2)[(-2)(1) + (-3)(2)] = -8, so w = 1 - 0.05(-8) = 1.4. The value 0.6 has the wrong sign, 1.2 drops the factor of 2, and 1.25 omits the multiplication by x.</t>
+  </si>
+  <si>
+    <t>A regression has coefficients 3, -2 and 0.5, and the regularization strength is lambda = 0.5. What are the LASSO (L1) and ridge (L2) penalty terms, respectively?</t>
+  </si>
+  <si>
+    <t>LASSO 2.75; ridge 6.63</t>
+  </si>
+  <si>
+    <t>LASSO 0.75; ridge 6.63</t>
+  </si>
+  <si>
+    <t>LASSO 6.63; ridge 2.75</t>
+  </si>
+  <si>
+    <t>LASSO 2.75; ridge 13.25</t>
+  </si>
+  <si>
+    <t>LASSO penalizes the sum of absolute coefficients: 0.5 x (3 + 2 + 0.5) = 2.75. Ridge penalizes the sum of squared coefficients: 0.5 x (9 + 4 + 0.25) = 6.63. The value 0.75 forgets the absolute values, the third option swaps the two penalties, and 13.25 omits lambda from the ridge term.</t>
+  </si>
+  <si>
+    <t>Gradient descent minimizes f(w) = w^2, whose gradient is 2w, starting at w = 1 with a learning rate of 1.2. What is w after two updates?</t>
+  </si>
+  <si>
+    <t>0.04</t>
+  </si>
+  <si>
+    <t>0.64</t>
+  </si>
+  <si>
+    <t>1.96</t>
+  </si>
+  <si>
+    <t>-1.40</t>
+  </si>
+  <si>
+    <t>First update: w = 1 - 1.2(2) = -1.4. Second update: w = -1.4 - 1.2(-2.8) = 1.96. The iterates overshoot the minimum at zero and grow in magnitude (1, -1.4, 1.96), showing that the learning rate is too large. The value -1.40 is the result after one step, 0.04 corresponds to a rate of 0.4, and 0.64 to a rate of 0.1.</t>
+  </si>
+  <si>
+    <t>In 10-fold cross-validation on 1,000 observations, how many times is a given observation used for validation and for training, respectively?</t>
+  </si>
+  <si>
+    <t>Validation once; training 9 times</t>
+  </si>
+  <si>
+    <t>Validation 10 times; training 10 times</t>
+  </si>
+  <si>
+    <t>Validation 9 times; training once</t>
+  </si>
+  <si>
+    <t>Validation once; training 10 times</t>
+  </si>
+  <si>
+    <t>The data are split into 10 folds. Each observation lies in exactly one fold, so it is validated once and used for training in the other 9 rotations. The k validation scores are then averaged.</t>
+  </si>
+  <si>
+    <t>Model A's prediction errors on four cases are 2, 2, 2 and 2; Model B's are 0, 0, 0 and 8. What does a comparison of their MAE and RMSE show?</t>
+  </si>
+  <si>
+    <t>Model B is better, because its RMSE of 4 means that its typical error is smaller than Model A's</t>
+  </si>
+  <si>
+    <t>The models are equivalent for risk purposes, because MAE and RMSE always rank models identically</t>
+  </si>
+  <si>
+    <t>Both have RMSE of 2, but MAE is 2 versus 4, showing that B's errors are concentrated in one large miss</t>
+  </si>
+  <si>
+    <t>Both have MAE of 2, but RMSE is 2 versus 4, showing that B's errors are concentrated in one large miss</t>
+  </si>
+  <si>
+    <t>MAE = 2 for both models. RMSE for A = 2, and for B = sqrt(64/4) = 4. Squaring penalizes large errors disproportionately, so RMSE reveals the concentrated large error that average-error metrics can mask, which matters in risk contexts.</t>
+  </si>
+  <si>
+    <t>A fraud model is run at two thresholds on 1,000 cases. Threshold 1: TP 80, FP 40, FN 20, TN 860. Threshold 2: TP 65, FP 15, FN 35, TN 885. A missed fraud costs 500 and a false alarm costs 50. Which threshold should be used?</t>
+  </si>
+  <si>
+    <t>Threshold 2, because it has fewer false positives, which dominate the total cost in this case</t>
+  </si>
+  <si>
+    <t>Threshold 1, because its total cost is 12,000 versus 18,250, even though threshold 2 has higher precision</t>
+  </si>
+  <si>
+    <t>Threshold 1, because its recall is higher at 0.80, although its total cost is higher than threshold 2</t>
+  </si>
+  <si>
+    <t>Threshold 2, because it has higher precision (0.81 versus 0.67) and higher accuracy than threshold 1</t>
+  </si>
+  <si>
+    <t>Total cost = 500 x FN + 50 x FP. Threshold 1: 500 x 20 + 50 x 40 = 12,000. Threshold 2: 500 x 35 + 50 x 15 = 18,250. Although threshold 2 has higher precision and accuracy (0.95 vs 0.94), false negatives are far costlier, so the threshold choice should follow the relative costs of errors.</t>
+  </si>
+  <si>
+    <t>On a test set, the total sum of squares is 200 and the model's residual sum of squares is 250. What is the out-of-sample R-squared and what does it mean?</t>
+  </si>
+  <si>
+    <t>0.80; the model explains 80% of the variance in the test set</t>
+  </si>
+  <si>
+    <t>1.25; the model explains more than all of the variance in the test set</t>
+  </si>
+  <si>
+    <t>0.25; the model explains one quarter of the variance in the test set</t>
+  </si>
+  <si>
+    <t>-0.25; the model predicts worse than simply using the sample mean</t>
+  </si>
+  <si>
+    <t>R-squared = 1 - RSS/TSS = 1 - 250/200 = -0.25. Out of sample it can be negative, which means the model's errors exceed those of simply predicting the mean. The value 0.80 is TSS/RSS.</t>
+  </si>
+  <si>
+    <t>A model ranks ten cases from highest to lowest score. The actual labels in that order are P, P, N, P, N, P, N, N, P, N (P = positive). Lowering the cutoff so that the top 4 flagged cases become the top 6 flagged cases changes precision and recall from and to which values?</t>
+  </si>
+  <si>
+    <t>Precision 0.75 to 0.67; recall 0.60 to 0.80</t>
+  </si>
+  <si>
+    <t>Precision 0.60 to 0.80; recall 0.75 to 0.67</t>
+  </si>
+  <si>
+    <t>Precision 0.75 to 0.80; recall 0.60 to 0.67</t>
+  </si>
+  <si>
+    <t>Precision 0.67 to 0.75; recall 0.80 to 0.60</t>
+  </si>
+  <si>
+    <t>There are 5 actual positives. Top 4: TP = 3, FP = 1, so precision = 3/4 = 0.75 and recall = 3/5 = 0.60. Top 6: TP = 4, FP = 2, so precision = 4/6 = 0.67 and recall = 4/5 = 0.80. Lowering the cutoff raises recall and lowers precision.</t>
+  </si>
+  <si>
+    <t>A classifier has precision of 0.90 and recall of 0.30. What is its F1 score?</t>
+  </si>
+  <si>
+    <t>0.27</t>
+  </si>
+  <si>
+    <t>0.60</t>
+  </si>
+  <si>
+    <t>0.45</t>
+  </si>
+  <si>
+    <t>F1 is the harmonic mean: 2 x 0.90 x 0.30 / (0.90 + 0.30) = 0.54 / 1.20 = 0.45. The arithmetic mean would be 0.60; the harmonic mean pulls the score toward the weaker of the two metrics. The value 0.27 is the product of precision and recall.</t>
+  </si>
+  <si>
+    <t>A pipeline removes stop words using a standard list that includes 'not'. The sentence 'the loan is not good' becomes 'loan good'. What is the consequence and a sensible mitigation?</t>
+  </si>
+  <si>
+    <t>The meaning is preserved, because stemming restores the removed words when the tokens are reduced to roots</t>
+  </si>
+  <si>
+    <t>Sentiment can flip because negation is lost; keeping negations or using bigrams such as 'not good' keeps local context</t>
+  </si>
+  <si>
+    <t>Nothing changes, because stop words carry no information in any text-classification task or sentiment application</t>
+  </si>
+  <si>
+    <t>TF-IDF restores 'not', because words that are common across documents receive the highest weights</t>
+  </si>
+  <si>
+    <t>Stop words such as 'the' and 'and' are usually removed as low-information, but a standard list may include negations that matter. Bigrams capture some local word order, such as 'not good' versus 'good'. TF-IDF down-weights common words rather than restoring them.</t>
+  </si>
+  <si>
+    <t>A sentence has 8 distinct tokens. How many features does a model using all unigrams, bigrams and trigrams from that sentence have?</t>
+  </si>
+  <si>
+    <t>24</t>
+  </si>
+  <si>
+    <t>A sentence of 8 tokens has 8 unigrams, 7 bigrams and 6 trigrams: 8 + 7 + 6 = 21. The value 24 counts 8 of each type, which is impossible because the number of n-grams falls as n rises.</t>
+  </si>
+  <si>
+    <t>The word 'risk' appears 20 times in Filing A (10,000 words) and 5 times in Filing B (1,000 words). Which statement is correct?</t>
+  </si>
+  <si>
+    <t>Filing B uses it more intensively, at 0.5% versus 0.2%, because comparisons should adjust for document length</t>
+  </si>
+  <si>
+    <t>Filing A uses it more intensively, at 20 occurrences versus 5, because raw counts are the right basis for comparison</t>
+  </si>
+  <si>
+    <t>Neither, because TF-IDF assigns both filings equal weight whenever the word appears in both of them</t>
+  </si>
+  <si>
+    <t>Filing A uses it more intensively, because 10,000 words give a more reliable frequency than 1,000 words</t>
+  </si>
+  <si>
+    <t>Relative frequency is 20/10,000 = 0.2% for A and 5/1,000 = 0.5% for B. Normalizing for document length prevents longer documents from appearing to use words more heavily just because they contain more words.</t>
+  </si>
+  <si>
+    <t>A model is given the context words 'central', 'bank', 'raised' and 'rates' and is trained to predict the missing word 'interest'. Which Word2Vec architecture is this?</t>
+  </si>
+  <si>
+    <t>Skip-gram, which predicts the surrounding context words from the target word</t>
+  </si>
+  <si>
+    <t>CBoW, which predicts the target word from its surrounding context</t>
+  </si>
+  <si>
+    <t>CBoW, which predicts the surrounding context words from the target word</t>
+  </si>
+  <si>
+    <t>Skip-gram, which predicts the target word from its surrounding context</t>
+  </si>
+  <si>
+    <t>CBoW (continuous bag of words) predicts the target word from the surrounding context words, as in this example. Skip-gram does the reverse: it predicts the surrounding context words from the target word.</t>
+  </si>
+  <si>
+    <t>An adviser gives an LLM a client's risk profile in one API call and then, in a separate call, asks for an allocation and receives a generic answer. Which explanation is most accurate?</t>
+  </si>
+  <si>
+    <t>Top-K sampling removed the relevant tokens, so the risk profile only needs to be added to the system prompt once</t>
+  </si>
+  <si>
+    <t>The temperature was too low, so the model dropped the risk profile from its next-token probability distribution</t>
+  </si>
+  <si>
+    <t>The context window was exceeded by a single sentence, so the model permanently deleted the first prompt</t>
+  </si>
+  <si>
+    <t>LLM calls are stateless, so earlier information is not retained; the context must be supplied again in each prompt</t>
+  </si>
+  <si>
+    <t>Statelessness means prior information is not automatically retained between independent prompts, so the relevant context must be supplied again (or a conversation history maintained). Temperature and Top-K shape sampling, and the context window limits how many tokens a single sequence can contain.</t>
+  </si>
+  <si>
+    <t>A model scores 92% on a public finance benchmark but 61% on the bank's internal case set. Which explanation is most consistent with the book's cautions about benchmarks?</t>
+  </si>
+  <si>
+    <t>Benchmarks measure only latency and cost, so accuracy differences between the two sets are meaningless</t>
+  </si>
+  <si>
+    <t>Standardized tests are built to match the bank's workflows, so the gap reflects hallucination in the internal set only</t>
+  </si>
+  <si>
+    <t>Contamination, saturation and a lack of real-world context can inflate public scores relative to realistic tasks</t>
+  </si>
+  <si>
+    <t>Public benchmarks are always harder than real tasks, so the internal score must contain labeling errors</t>
+  </si>
+  <si>
+    <t>Standardized benchmarks such as FinQA or MMLU are useful, but the book warns of contamination, saturation, lack of real-world context, cherry-picking and incomplete comparisons. Internal evaluation on realistic tasks is needed for decisions.</t>
+  </si>
+  <si>
+    <t>A screening model produces, for Group X, 30 false positives and 270 true negatives and, for Group Y, 20 false positives and 80 true negatives. Which statement about false positive rates is correct?</t>
+  </si>
+  <si>
+    <t>The rates are 30 and 20, so Group X is treated worse and Group Y is favored by the model overall</t>
+  </si>
+  <si>
+    <t>The rates are 10% and 20%, so Group X is twice as likely to be wrongly flagged, having more false positives</t>
+  </si>
+  <si>
+    <t>The rates are equal at 10%, because each group's false positives are a small share of all its cases</t>
+  </si>
+  <si>
+    <t>The rates are 10% and 20%, so Group Y is twice as likely to be wrongly flagged, a group-fairness gap</t>
+  </si>
+  <si>
+    <t>Fairness is assessed by comparing metrics such as precision, recall and false positive rate across groups. FPR = FP / (FP + TN): Group X = 30/300 = 10% and Group Y = 20/100 = 20%. Absolute counts are misleading because the groups differ in size.</t>
+  </si>
+  <si>
+    <t>Consider: (1) a model trained only on branch applicants fails on online applicants; (2) a lender uses a biased proxy as its target variable; (3) after launch, economic conditions shift and error rates rise for one subgroup. Which assignment to the pipeline stages at which unfairness enters is correct?</t>
+  </si>
+  <si>
+    <t>(1) problem specification and feature selection; (2) data collection and composition; (3) deployment</t>
+  </si>
+  <si>
+    <t>(1) data collection and composition; (2) problem specification and feature selection; (3) deployment</t>
+  </si>
+  <si>
+    <t>(1) model development; (2) deployment; (3) problem specification and feature selection</t>
+  </si>
+  <si>
+    <t>(1) data collection and composition; (2) model development; (3) problem specification and feature selection</t>
+  </si>
+  <si>
+    <t>The four stages are problem specification and feature selection (for example a biased proxy), data collection and composition (underrepresentation), model development (such as optimizing aggregate accuracy) and deployment (such as drift affecting subgroups unevenly).</t>
+  </si>
+  <si>
+    <t>Consider: (1) a bank tells customers that it uses AI in credit decisions and describes its purpose; (2) a shallow decision tree whose splits can be read directly; (3) a per-applicant list of the factors behind one decision from a complex ensemble. Which assignment to transparency, interpretability and explainability is correct?</t>
+  </si>
+  <si>
+    <t>(1) transparency; (2) interpretability; (3) explainability</t>
+  </si>
+  <si>
+    <t>(1) interpretability; (2) transparency; (3) explainability</t>
+  </si>
+  <si>
+    <t>(1) explainability; (2) transparency; (3) interpretability</t>
+  </si>
+  <si>
+    <t>(1) transparency; (2) explainability; (3) interpretability</t>
+  </si>
+  <si>
+    <t>Transparency is organizational disclosure about a model's existence, purpose and general functioning. Interpretability is how understandable a model's internal logic is on its own terms, as with a simple tree. Explainability describes in human terms why a specific output was produced, even for non-interpretable models.</t>
+  </si>
+  <si>
+    <t>Which statement correctly relates model complexity to interpretability?</t>
+  </si>
+  <si>
+    <t>Interpretability and transparency are the same concept, so disclosing a model automatically makes it interpretable</t>
+  </si>
+  <si>
+    <t>Explainability tools remove the black-box problem, because they make the full internal logic of the model readable</t>
+  </si>
+  <si>
+    <t>Interpretability rises with model depth, because additional layers expose more of the internal logic to reviewers</t>
+  </si>
+  <si>
+    <t>More complex models tend to trade interpretability for performance, the technical basis of the black-box problem</t>
+  </si>
+  <si>
+    <t>Deeper, more complex models tend to give up interpretability for accuracy, creating a black-box problem. Explainability techniques explain individual outputs but do not make the overall logic interpretable, and transparency is a distinct, organizational concept.</t>
+  </si>
+  <si>
+    <t>A chatbot (a) shows a customer an accurate comparison of two products' costs and benefits, while a second chatbot (b) shows a countdown timer and 'only 2 left' messages that it knows to be false, to exploit loss aversion. Which statement is correct?</t>
+  </si>
+  <si>
+    <t>Neither is a risk, because manipulation arises only when a system acts without any human oversight</t>
+  </si>
+  <si>
+    <t>(a) is manipulation because it steers customers, whereas (b) is legitimate persuasion because it is effective</t>
+  </si>
+  <si>
+    <t>(b) is manipulation because it bypasses rational agency by exploiting biases; (a) is legitimate persuasion</t>
+  </si>
+  <si>
+    <t>Both are manipulation, because any influence on a customer's decision undermines the customer's autonomy</t>
+  </si>
+  <si>
+    <t>Manipulation is influence on beliefs or decisions that bypasses rational agency, typically by exploiting biases or vulnerabilities, and is distinct from legitimate persuasion based on accurate information. It is a different dimension from autonomy, which concerns control and oversight.</t>
+  </si>
+  <si>
+    <t>A robo-advisor's faulty rebalancing logic wipes out 40% of a client's retirement savings in one day. How should this risk be classified?</t>
+  </si>
+  <si>
+    <t>A well-being risk, because financial harm always develops gradually over months or years</t>
+  </si>
+  <si>
+    <t>A well-being risk, because only physical harms can be classified as safety risks</t>
+  </si>
+  <si>
+    <t>A safety risk: an acute, direct financial harm, unlike well-being risks that develop gradually</t>
+  </si>
+  <si>
+    <t>Neither, because safety risks cover only physical harm from autonomous vehicles and medical AI</t>
+  </si>
+  <si>
+    <t>Safety risk is the potential for physical, psychological, financial or other harm, and it is often acute and direct. Well-being risks are broader, longer-term effects such as addictive engagement or gradual erosion of critical thinking.</t>
+  </si>
+  <si>
+    <t>Consider: (1) a lender's AI is found to approve fewer loans for one ethnic group; (2) a bank's AI assistant repeatedly gives wrong rates; (3) customers learn the bank used their transaction data to train a model without telling them. Which assignment to the types of reputational criticism is correct?</t>
+  </si>
+  <si>
+    <t>(1) competence; (2) ethical; (3) transparency</t>
+  </si>
+  <si>
+    <t>(1) transparency; (2) competence; (3) ethical</t>
+  </si>
+  <si>
+    <t>(1) ethical; (2) competence; (3) transparency</t>
+  </si>
+  <si>
+    <t>(1) ethical; (2) transparency; (3) competence</t>
+  </si>
+  <si>
+    <t>Ethical criticism concerns unfair or harmful outcomes, competence criticism concerns the AI simply not working well, and transparency criticism arises when stakeholders feel misled about AI use or disclosure.</t>
+  </si>
+  <si>
+    <t>Which ordering of AI risk categories from the most localized to the most extreme in scale is consistent with the book?</t>
+  </si>
+  <si>
+    <t>Individual harm, global societal risk, organizational reputational harm, existential risk</t>
+  </si>
+  <si>
+    <t>Existential risk, global societal risk, organizational reputational harm, individual harm</t>
+  </si>
+  <si>
+    <t>Organizational reputational harm, individual harm, existential risk, global societal risk</t>
+  </si>
+  <si>
+    <t>Individual harm, organizational reputational harm, global societal risk, existential risk</t>
+  </si>
+  <si>
+    <t>Module 3 moves from individual and model-level harm, to organizational (reputation), to global and societal risks, with existential risk as the most extreme, civilizational-scale (and contested) category.</t>
+  </si>
+  <si>
+    <t>Which scenario illustrates the global-level privacy and surveillance risk, as opposed to an organization-level data-governance problem?</t>
+  </si>
+  <si>
+    <t>A government links facial recognition and social media data to track residents' movements city-wide</t>
+  </si>
+  <si>
+    <t>A retailer keeps loyalty-card data for longer than its own stated retention policy permits</t>
+  </si>
+  <si>
+    <t>A bank stores customer files with weak access controls, so employees can view records without a business need</t>
+  </si>
+  <si>
+    <t>A fintech shares customer e-mail addresses with a marketing vendor without updating its consent terms</t>
+  </si>
+  <si>
+    <t>Privacy and surveillance as a global-level risk concerns societal or governmental scale, such as mass facial recognition. The other scenarios are organizational data-governance failures: access control, retention and consent.</t>
+  </si>
+  <si>
+    <t>A firm launches a GenAI advice tool for retail clients within weeks, skipping testing and controls to beat its competitors. Which GenAI risk category is most directly illustrated?</t>
+  </si>
+  <si>
+    <t>Functional risk, since the tool will certainly hallucinate and produce inconsistent outputs for clients</t>
+  </si>
+  <si>
+    <t>Societal risk, since one client-facing tool necessarily spreads coordinated disinformation across the public</t>
+  </si>
+  <si>
+    <t>Strategic risk, since hasty adoption without controls is a competitive-positioning failure, not a skills issue</t>
+  </si>
+  <si>
+    <t>Organizational risk, since staff over-reliance and skill atrophy inside the firm are the central problem</t>
+  </si>
+  <si>
+    <t>Strategic risk covers falling behind competitors and also over-hasty adoption without controls. Organizational risk concerns internal operations and skills (over-reliance, skill atrophy, inadequate oversight), and the two are commonly confused.</t>
+  </si>
+  <si>
+    <t>Realistic fabricated videos of a bank's CEO announcing insolvency spread online and trigger a deposit run. Which GenAI risk category applies, and which Chapter 8 theme does it link to?</t>
+  </si>
+  <si>
+    <t>Data and information risk, linking to privacy and surveillance because the video used personal data</t>
+  </si>
+  <si>
+    <t>Societal risk, linking to misinformation campaigns, where GenAI lowers the cost of convincing false content</t>
+  </si>
+  <si>
+    <t>Functional risk, linking to economic risk because the model hallucinated an announcement by itself</t>
+  </si>
+  <si>
+    <t>Organizational risk, linking to global inequality because staff relied on the model's output unchecked</t>
+  </si>
+  <si>
+    <t>Societal risk covers broader effects such as coordinated deepfake disinformation, which ties to the global-level misinformation campaigns category: GenAI lowers the cost and effort of producing convincing false content at scale.</t>
+  </si>
+  <si>
+    <t>Which sequence best reflects the progression of risks across Module 3?</t>
+  </si>
+  <si>
+    <t>Civilizational risks first, then organizational risks, ending with model-level technical risks such as bias and explainability</t>
+  </si>
+  <si>
+    <t>Model-level risks (bias, explainability, autonomy), then organizational (reputation), then societal and civilizational</t>
+  </si>
+  <si>
+    <t>Model-level risks, then solutions for each risk, ending with practical governance and model validation techniques</t>
+  </si>
+  <si>
+    <t>Organizational risks first, then model-level risks, ending with the regulatory compliance requirements for each risk</t>
+  </si>
+  <si>
+    <t>The module moves from individual and model-level risk (bias, explainability, autonomy) to organizational risk (reputation) to civilizational and societal risk (existential, global, GenAI). It supplies vocabulary rather than solutions, which are the subject of Modules 4 and 5.</t>
+  </si>
+  <si>
+    <t>A board member argues that a formal practical-ethics framework is only a compliance cost. Which response is most consistent with the book?</t>
+  </si>
+  <si>
+    <t>It removes ethical dilemmas by supplying one correct rule that is applied identically in every context</t>
+  </si>
+  <si>
+    <t>It can build trust and reputation, avoid scandals and support risk management, with decisions justifiable to society</t>
+  </si>
+  <si>
+    <t>It matters only for engineers, because ethical dilemmas arise solely inside the design of model code</t>
+  </si>
+  <si>
+    <t>It guarantees legal compliance, so a separate compliance function and regulatory monitoring are no longer required</t>
+  </si>
+  <si>
+    <t>The book lists reasons to adopt practical ethics: building trust and reputation, avoiding scandals, attracting and retaining talent, strengthening culture, supporting risk management, guiding responsible innovation and promoting long-term thinking. Ethics complements law rather than replacing it, and practical ethics is context-sensitive and pluralistic.</t>
+  </si>
+  <si>
+    <t>A bank approves an AI collections tool because of a forecast of large future benefits, but the probabilities and customer harms are highly uncertain and hard to measure. Which difficulty is illustrated?</t>
+  </si>
+  <si>
+    <t>Consequentialist reasoning depends on predicting and quantifying outcomes, which is subjective and uncertain</t>
+  </si>
+  <si>
+    <t>Virtue ethics assesses character, which cannot be observed in an automated collections tool at all</t>
+  </si>
+  <si>
+    <t>Deontology requires universalizable maxims, which cannot be tested without first forecasting the outcomes</t>
+  </si>
+  <si>
+    <t>Rule consequentialism ignores outcomes entirely, so the benefit forecast is irrelevant to the decision</t>
+  </si>
+  <si>
+    <t>Consequentialism is forward-looking and judges actions by their outcomes. Its challenges include subjective metrics, difficulty quantifying value and uncertainty about consequences, all of which appear when benefits and harms must be forecast.</t>
+  </si>
+  <si>
+    <t>A firm's working maxim is 'we may withhold material product risks whenever customers are unlikely to notice'. Which reasoning would a Kantian apply?</t>
+  </si>
+  <si>
+    <t>The maxim is acceptable if following the rule consistently tends to maximize utility across firms</t>
+  </si>
+  <si>
+    <t>The maxim is acceptable if the expected net benefit to all affected parties is positive</t>
+  </si>
+  <si>
+    <t>The maxim cannot be universalized without defeating itself, and it treats customers merely as means</t>
+  </si>
+  <si>
+    <t>The maxim is acceptable if a person of good character would sometimes choose it in practice</t>
+  </si>
+  <si>
+    <t>Kantian deontology emphasizes universalizable maxims and treating people as ends in themselves, not merely as means. Concealing material risks fails both tests. The alternatives describe utilitarian, virtue-ethics and rule-consequentialist reasoning.</t>
+  </si>
+  <si>
+    <t>A committee asks three questions about a hiring algorithm: (1) does it maximize overall benefit; (2) would we accept it as a duty everyone should follow, treating applicants as ends; (3) what would a person of integrity and practical wisdom do? Which assignment to consequentialism, deontology and virtue ethics is correct?</t>
+  </si>
+  <si>
+    <t>(1) consequentialism; (2) virtue ethics; (3) deontology</t>
+  </si>
+  <si>
+    <t>(1) consequentialism; (2) deontology; (3) virtue ethics</t>
+  </si>
+  <si>
+    <t>(1) virtue ethics; (2) deontology; (3) consequentialism</t>
+  </si>
+  <si>
+    <t>(1) deontology; (2) consequentialism; (3) virtue ethics</t>
+  </si>
+  <si>
+    <t>Consequentialism judges outcomes, deontology judges actions by duties and rules (treating people as ends), and virtue ethics asks what a person of good character and practical wisdom would do. The frameworks are not mutually exclusive, and practical ethics can use all three.</t>
+  </si>
+  <si>
+    <t>A board member notes that medicine has professional codes, licensing requirements and ethics committees, while AI developers have few equivalents. Which governance challenge does this contrast point to?</t>
+  </si>
+  <si>
+    <t>Lack of AI ethics structures, such as codes, specialist roles and review committees</t>
+  </si>
+  <si>
+    <t>Power asymmetries, since technology firms may out-resource the regulators who oversee them</t>
+  </si>
+  <si>
+    <t>Lack of truth-tracking, since language models produce plausible responses that may be false</t>
+  </si>
+  <si>
+    <t>Unpredictability, since models can show emergent behavior and surprising capabilities after scaling</t>
+  </si>
+  <si>
+    <t>Medical ethics illustrates the value of formal standards, specialized expertise and institutional review structures for high-stakes technology. The book contrasts this with the lack of comparable AI ethics structures: bioethicists, codes, professional requirements and ethics committees.</t>
+  </si>
+  <si>
+    <t>A regulator asks why a bank must be able to explain adverse AI decisions to the people affected. Which rationale does the explainability principle support?</t>
+  </si>
+  <si>
+    <t>Explanations guarantee that every model becomes fully interpretable to non-expert customers and staff</t>
+  </si>
+  <si>
+    <t>Explanations remove the need for human oversight of high-stakes automated decisions in practice</t>
+  </si>
+  <si>
+    <t>Explanations support accountability, detection of errors and bias, trust and protection of rights</t>
+  </si>
+  <si>
+    <t>Explanations replace the need for organizational transparency about the model's existence and purpose</t>
+  </si>
+  <si>
+    <t>Explainability means transparent and understandable explanations of AI decisions. It supports accountability, error and bias detection, trust, transparency and protection of rights. It does not make a model fully interpretable or replace oversight and transparency.</t>
+  </si>
+  <si>
+    <t>An AI pricing engine allocates cheaper credit mainly to high-income segments, and low-income applicants rarely receive offers. Which form of justice is most directly at issue?</t>
+  </si>
+  <si>
+    <t>Interactional justice, which concerns respectful treatment of people during the process</t>
+  </si>
+  <si>
+    <t>Restorative justice, which concerns repairing harm after a wrong has occurred</t>
+  </si>
+  <si>
+    <t>Distributive justice, which concerns how benefits and burdens are allocated</t>
+  </si>
+  <si>
+    <t>Procedural justice, which concerns whether rules are applied consistently and impartially</t>
+  </si>
+  <si>
+    <t>Justice includes procedural, distributive, restorative, interactional and social forms. The question concerns who receives the benefit (cheaper credit) and who is left out, which is distributive justice.</t>
+  </si>
+  <si>
+    <t>A regulator urges a bank to give free personalized financial coaching to all 2 million of its customers using AI. The bank says it cannot. Which statement about beneficence supports the bank?</t>
+  </si>
+  <si>
+    <t>Beneficence is overridden by explainability whenever a service cannot be explained to each customer individually</t>
+  </si>
+  <si>
+    <t>Beneficence has reasonable limits, because resources and competing obligations constrain what can be demanded</t>
+  </si>
+  <si>
+    <t>Beneficence is satisfied once harm is avoided, so no positive obligation to benefit others exists at all</t>
+  </si>
+  <si>
+    <t>Beneficence is unlimited, so resource constraints are irrelevant to the duty to advance everyone's welfare</t>
+  </si>
+  <si>
+    <t>Beneficence is a positive obligation to benefit others and advance welfare, not merely to avoid harm, but it has reasonable limits because resources and competing obligations constrain what can be demanded. Autonomy can also rule out unwanted benefits.</t>
+  </si>
+  <si>
+    <t>A bank documents the standardized coefficients of its logistic regression to show how every input affects scores across all applicants. How is this explanation classified?</t>
+  </si>
+  <si>
+    <t>Explanations are local (one decision) or global (overall behavior), and model-specific (tied to a model's structure) or model-agnostic (usable on any model). A coefficient table describes the whole model and relies on the structure of a regression, so it is global and model-specific.</t>
+  </si>
+  <si>
+    <t>A hiring model trained on ten years of past decisions recommends fewer women for senior roles because past managers promoted fewer women. Which source of bias is this?</t>
+  </si>
+  <si>
+    <t>Sampling bias, where the sample was not drawn at random from the relevant population</t>
+  </si>
+  <si>
+    <t>Deployment bias, where users over-rely on the model's recommendations after launch</t>
+  </si>
+  <si>
+    <t>Historical bias, where the data reflect past discriminatory or unequal decisions</t>
+  </si>
+  <si>
+    <t>Problem-specification bias, where the target variable poorly proxies the real objective</t>
+  </si>
+  <si>
+    <t>Data bias includes historical bias (data reflecting past unequal decisions), selective labels and sampling bias. Training on past promotion decisions reproduces the earlier pattern of unequal treatment.</t>
+  </si>
+  <si>
+    <t>A credit model produces far lower approval rates for applicants over 60. Which statement about legal discrimination is most accurate?</t>
+  </si>
+  <si>
+    <t>It is legally discriminatory in every jurisdiction whenever approval rates differ between any two groups of applicants</t>
+  </si>
+  <si>
+    <t>It may be legal discrimination if it disadvantages a protected class such as age, though thresholds vary by jurisdiction</t>
+  </si>
+  <si>
+    <t>It cannot be legally discriminatory, because an algorithm that is statistically unbiased is never unlawful anywhere</t>
+  </si>
+  <si>
+    <t>It is lawful by definition, because ethical fairness and legal discrimination are exactly the same standard</t>
+  </si>
+  <si>
+    <t>Algorithmic bias may count as legal discrimination when it disadvantages people based on protected classifications such as race, sex, ethnicity or age, and the exact legal threshold varies by jurisdiction. An algorithm can also be legally unbiased yet still cause unjustified harm, so ethics and law are not identical.</t>
+  </si>
+  <si>
+    <t>Approval rates are 60% for Group P and 45% for Group Q. What are the demographic parity difference and the ratio of the lower to the higher approval rate?</t>
+  </si>
+  <si>
+    <t>15 percentage points; ratio 0.75</t>
+  </si>
+  <si>
+    <t>33 percentage points; ratio 0.75</t>
+  </si>
+  <si>
+    <t>15 percentage points; ratio 0.25</t>
+  </si>
+  <si>
+    <t>15 percentage points; ratio 1.33</t>
+  </si>
+  <si>
+    <t>The demographic parity difference is 60% - 45% = 15 percentage points, and the ratio of the lower to the higher rate is 45/60 = 0.75. The value 33 is the relative difference (15/45), 0.25 is one minus the ratio, and 1.33 inverts the ratio.</t>
+  </si>
+  <si>
+    <t>A customer asks a bank to show the credit-risk segment it has inferred for her from her transactions and then to delete it. Which privacy practice is most directly engaged?</t>
+  </si>
+  <si>
+    <t>Contextual integrity, which only restricts use to the context in which data were provided</t>
+  </si>
+  <si>
+    <t>Data security, which only prevents unauthorized access, theft or corruption of the data</t>
+  </si>
+  <si>
+    <t>Data minimization, which only limits how much personal data is collected at the outset</t>
+  </si>
+  <si>
+    <t>Control over data, including access to inferences and the ability to delete data</t>
+  </si>
+  <si>
+    <t>Control over data includes the meaningful ability to deny or withdraw consent, access data and inferences, transfer data and delete data. Minimization, contextual integrity and security are separate good practices.</t>
+  </si>
+  <si>
+    <t>A firm secretly reads employees' private messages out of curiosity. No one is harmed or disciplined. Which statement is most consistent with the book?</t>
+  </si>
+  <si>
+    <t>It is not an ethical problem, because privacy matters only when tangible harm such as identity theft or blackmail occurs</t>
+  </si>
+  <si>
+    <t>It is an ethical problem only if an outside party stole the messages, which would then make it a data-security breach</t>
+  </si>
+  <si>
+    <t>It is still an ethical problem, as privacy violations can be wrong without tangible harm and treat people instrumentally</t>
+  </si>
+  <si>
+    <t>It is an ethical problem only if the firm is large enough for the practice to create wider societal risk</t>
+  </si>
+  <si>
+    <t>Privacy is an ethical issue because violations can be wrong even without tangible harm and can treat people instrumentally. Harms such as discrimination, blackmail, exposure and identity theft are additional consequences, and privacy differs from data security.</t>
+  </si>
+  <si>
+    <t>A bank considers licensing an LLM trained on scraped web content that may include copyrighted material and personal data. Which governance concern is most relevant?</t>
+  </si>
+  <si>
+    <t>Privacy and copyright concerns from scraping, with uncertainty about data-rights compliance and litigation</t>
+  </si>
+  <si>
+    <t>Unpredictability, because scraped data always cause emergent capabilities to appear after deployment</t>
+  </si>
+  <si>
+    <t>Power asymmetries, because scraping can occur only when the provider is larger than every regulator</t>
+  </si>
+  <si>
+    <t>Lack of interpretability, because scraped training data make the model's weights impossible to inspect</t>
+  </si>
+  <si>
+    <t>The book identifies privacy and copyright concerns arising from scraping and collecting personal data and ingesting copyrighted material, with uncertainty around data-rights compliance and litigation. This also links to data provenance in Module 5.</t>
+  </si>
+  <si>
+    <t>A platform optimizes a simple proxy, time spent in the app, and users' well-being falls even though the proxy improves. Which point from the book's governance discussion is illustrated?</t>
+  </si>
+  <si>
+    <t>Time-spent metrics always require biometric data, so the platform has a privacy problem rather than a design problem</t>
+  </si>
+  <si>
+    <t>Proxies can optimize simplified measures that diverge from the real objective, a problem compounded by black-box models</t>
+  </si>
+  <si>
+    <t>Regulation of proxy metrics is prohibited in most jurisdictions, so nothing can be done about the divergence</t>
+  </si>
+  <si>
+    <t>Language models track truth poorly, so the platform has generated plausible but false statements about users</t>
+  </si>
+  <si>
+    <t>In discussing lack of interpretability, the book notes that proxies can optimize simplified measures that may diverge from the real objective, and that black-box models make such divergence harder to detect.</t>
+  </si>
+  <si>
+    <t>Which statement about the EU AI Act timetable, as described in the book, is correct?</t>
+  </si>
+  <si>
+    <t>It became effective on August 1, 2024, with unacceptable-risk bans from February 2, 2025 and most provisions from August 2, 2026</t>
+  </si>
+  <si>
+    <t>It became effective on February 2, 2025, with unacceptable-risk bans from August 1, 2024 and most provisions from August 2, 2026</t>
+  </si>
+  <si>
+    <t>It became effective on August 2, 2026, with unacceptable-risk bans from February 2, 2025 and most provisions from August 1, 2024</t>
+  </si>
+  <si>
+    <t>It became effective on August 1, 2024, with unacceptable-risk bans from August 2, 2026 and most provisions from February 2, 2025</t>
+  </si>
+  <si>
+    <t>The book states that the Act became effective on August 1, 2024, that bans on unacceptable-risk practices applied from February 2, 2025, and that most provisions apply from August 2, 2026.</t>
+  </si>
+  <si>
+    <t>Which statement about an instrument and its subject matter is correct?</t>
+  </si>
+  <si>
+    <t>The EU Digital Services Act regulates gatekeepers' self-preferencing, tying and messaging interoperability</t>
+  </si>
+  <si>
+    <t>The EU GDPR requires breach notification within 30 days and applies only to organizations inside the EEA</t>
+  </si>
+  <si>
+    <t>China's generative-AI measures, effective August 15, 2023, impose obligations on illegal or discriminatory content</t>
+  </si>
+  <si>
+    <t>The U.S. NIST AI Risk Management Framework is a mandatory federal licensing regime built on four functions</t>
+  </si>
+  <si>
+    <t>China's generative-AI measures, effective August 15, 2023, place obligations on providers concerning illegal or discriminatory content and rights such as privacy. The NIST AI RMF is voluntary, gatekeeper rules are in the Digital Markets Act (the DSA covers online intermediaries and content moderation), and the GDPR uses a 72-hour notification rule and can apply outside the EEA.</t>
+  </si>
+  <si>
+    <t>Loan records in a data warehouse reference customer IDs that do not exist in the customer table. Which data-quality dimension is most directly compromised?</t>
+  </si>
+  <si>
+    <t>Provenance, because the legal right to use the data is not evidenced</t>
+  </si>
+  <si>
+    <t>Consistency, because two systems record different values for the same customer</t>
+  </si>
+  <si>
+    <t>Accuracy, because every value in the loan field is wrong by definition</t>
+  </si>
+  <si>
+    <t>Integrity, because the relationships between records are broken</t>
+  </si>
+  <si>
+    <t>The book frames data quality around accuracy, consistency and integrity. Records that point to non-existent customers are a failure of integrity. Consistency concerns conflicting values across systems, and provenance concerns ownership, handling and the legal right to use data.</t>
+  </si>
+  <si>
+    <t>An analyst stores a forward-looking GDP forecast in the same table as reported historical GDP, with no flag. Which governance control addresses this?</t>
+  </si>
+  <si>
+    <t>Data classification of observed, projected and judgment-based data, supported by metadata</t>
+  </si>
+  <si>
+    <t>Data minimization, which removes any projected variable from every model that is developed</t>
+  </si>
+  <si>
+    <t>Data provenance, which evidences the vendor's legal right to publish its GDP forecasts</t>
+  </si>
+  <si>
+    <t>Data retention, which deletes historical GDP series once forecasts become available</t>
+  </si>
+  <si>
+    <t>Data classification and metadata support controlled use: they distinguish quantitative from qualitative data and observed from projected or judgment-based data, and record origin, definitions and structures.</t>
+  </si>
+  <si>
+    <t>A modeler uses ZIP code as a proxy for income because income is unavailable, and does not record this. What does the book's data-strategy guidance require?</t>
+  </si>
+  <si>
+    <t>Only the use of non-public personal information needs documentation, so proxy use is exempt</t>
+  </si>
+  <si>
+    <t>Documentation is needed only for vendor data, because internal proxies are covered by the model's validation</t>
+  </si>
+  <si>
+    <t>Proxy variables are prohibited under any data strategy, so the modeler must delete the ZIP code variable</t>
+  </si>
+  <si>
+    <t>Treatment of missing data, trend monitoring and the use of proxies should be documented and approved</t>
+  </si>
+  <si>
+    <t>A data strategy should evaluate and approve data applicability, and the treatment of missing data, trend monitoring and the use of proxies should be documented. Proxies are not banned outright, but undocumented ones create governance and bias risk.</t>
+  </si>
+  <si>
+    <t>A market-risk model's published signals lead many firms to trade the same way, moving prices and invalidating the model's assumptions. Which risk-model governance consideration is illustrated?</t>
+  </si>
+  <si>
+    <t>Data minimization, which governance addresses by limiting how much market data is stored</t>
+  </si>
+  <si>
+    <t>Regression testing, which governance addresses by re-running unit tests after each code change</t>
+  </si>
+  <si>
+    <t>Feedback effects, which governance must weigh with incomplete scenario sets and transparent assumptions</t>
+  </si>
+  <si>
+    <t>Overfitting to the validation set, which governance addresses through additional hyperparameter tuning</t>
+  </si>
+  <si>
+    <t>Risk-model thinking has three elements (quantity of interest, scenarios with weights, and a risk measure), and governance must consider incomplete scenario sets, feedback effects and transparent communication of assumptions. A model whose use changes the market it models illustrates feedback effects.</t>
+  </si>
+  <si>
+    <t>Which function provides independent assurance that the validation function and the wider model-governance controls operate effectively?</t>
+  </si>
+  <si>
+    <t>The model owners, as the first line of defense responsible for model performance</t>
+  </si>
+  <si>
+    <t>Independent model validation, as the second line of defense that challenges models</t>
+  </si>
+  <si>
+    <t>Internal audit, as the third line of defense, which assures the whole framework</t>
+  </si>
+  <si>
+    <t>The model developers, who test their own code before it is released to users</t>
+  </si>
+  <si>
+    <t>The third line of defense (internal audit) provides independent assurance over the framework and controls, including the validation function. The first line owns model performance and data quality, and the second line sets standards and validates and challenges.</t>
+  </si>
+  <si>
+    <t>A validator cannot assess a model because the owners supplied only code. According to the book, what should the model-governance policy specify?</t>
+  </si>
+  <si>
+    <t>That documentation is optional for models classified in the lowest risk tier of the inventory</t>
+  </si>
+  <si>
+    <t>That validators write the missing documentation themselves, to preserve independence from the owners</t>
+  </si>
+  <si>
+    <t>That information requests go to internal audit, which maintains the model inventory for validators</t>
+  </si>
+  <si>
+    <t>The information model owners must provide, plus documentation and performance-monitoring standards</t>
+  </si>
+  <si>
+    <t>Model-governance policies should specify the information owners must provide and set documentation and performance-monitoring standards. Documentation should allow someone unfamiliar with the model to understand it, including its limitations and key assumptions.</t>
+  </si>
+  <si>
+    <t>A regulator asks for all vendor-supplied machine-learning models used in regulatory reporting. Which inventory attributes make this request answerable?</t>
+  </si>
+  <si>
+    <t>Developer seniority, programming language, project start date and team size</t>
+  </si>
+  <si>
+    <t>Model owner and last validation date, because these identify every type of model</t>
+  </si>
+  <si>
+    <t>Only the model's purpose and methodology, since origin is not recorded in an inventory</t>
+  </si>
+  <si>
+    <t>AI/ML status, vendor versus in-house origin, use and frequency, and regulatory use</t>
+  </si>
+  <si>
+    <t>A model inventory should track attributes including AI/ML status, vendor versus in-house origin, use and frequency, restrictions, materiality, interdependencies and regulatory use, so that targeted queries can be answered.</t>
+  </si>
+  <si>
+    <t>A developer drops 3% of observations as outliers before training and does not record the exclusion. What does the book's development guidance say?</t>
+  </si>
+  <si>
+    <t>Documentation is needed only when exclusions exceed 10% of observations, the standard threshold</t>
+  </si>
+  <si>
+    <t>Excluded data and the rationale should be documented, because outliers may be errors or useful signals</t>
+  </si>
+  <si>
+    <t>No documentation is needed, because outliers are errors by definition and always safe to delete</t>
+  </si>
+  <si>
+    <t>Documentation is needed only for transformations, since exclusions do not affect the model's design</t>
+  </si>
+  <si>
+    <t>Development should document excluded data and the rationale, transformations, model-selection rationale and safeguards against data leakage. Outliers may be errors or useful signals, so how they are treated depends on the application and must be recorded.</t>
+  </si>
+  <si>
+    <t>Consider: (1) checking that the scoring engine handles 10,000 requests per minute within the time limit; (2) deciding whether the model is ready to go live; (3) confirming that a code change has not broken existing functions. Which assignment to performance, acceptance and regression testing is correct?</t>
+  </si>
+  <si>
+    <t>(1) performance; (2) regression; (3) acceptance</t>
+  </si>
+  <si>
+    <t>(1) acceptance; (2) performance; (3) regression</t>
+  </si>
+  <si>
+    <t>(1) regression; (2) acceptance; (3) performance</t>
+  </si>
+  <si>
+    <t>(1) performance; (2) acceptance; (3) regression</t>
+  </si>
+  <si>
+    <t>Performance tests assess speed, responsiveness and stability; acceptance tests determine readiness for deployment; regression tests confirm that changes have not broken existing functionality.</t>
+  </si>
+  <si>
+    <t>A bank launches an LLM assistant. Which testing approach is best suited to uncover prompt-injection and chained-prompt weaknesses?</t>
+  </si>
+  <si>
+    <t>Regression testing after each release to confirm that earlier functions still work correctly</t>
+  </si>
+  <si>
+    <t>Adversarial or red-team testing that probes extreme scenarios, edge cases and odd queries</t>
+  </si>
+  <si>
+    <t>Acceptance testing against the business requirements that were signed off at design</t>
+  </si>
+  <si>
+    <t>Unit testing of each function in isolation against its written specification and design</t>
+  </si>
+  <si>
+    <t>Adversarial or red-team testing probes extreme scenarios and edge cases, including prompt injection, chained prompts and unexpected queries. Beta or parallel-to-production periods can expose further issues that real users trigger.</t>
+  </si>
+  <si>
+    <t>A material change to a credit model is approved on the condition that it is not used for small-business lending. What should the change record contain?</t>
+  </si>
+  <si>
+    <t>Only the modifications and approval, since conditions belong in the inventory's restrictions field alone</t>
+  </si>
+  <si>
+    <t>Only the validation results, because approval decisions are recorded by the board in a separate document</t>
+  </si>
+  <si>
+    <t>The reason and approval, since conditions apply only to initial validation and not to later model changes</t>
+  </si>
+  <si>
+    <t>The reason, modifications, validation results, approval, rationale and decision, with conditions and limitations</t>
+  </si>
+  <si>
+    <t>All changes should record the reason, modifications, validation results, approval, rationale, decision, and any conditions or limitations, and approved changes belong in the model inventory.</t>
+  </si>
+  <si>
+    <t>After recalibration on new data, a retail-credit model is proposed for use on a new commercial product. Which consideration is most consistent with the book?</t>
+  </si>
+  <si>
+    <t>Technical recalibration alone is sufficient, because the intended use is fixed when a model is first built</t>
+  </si>
+  <si>
+    <t>Only the developer needs to confirm that accuracy improved, because use and risk tier are validation matters</t>
+  </si>
+  <si>
+    <t>The new product needs no review, because recalibrated models inherit the original approval permanently</t>
+  </si>
+  <si>
+    <t>Change governance must ask whether the model remains appropriate for its intended use, risk tier and monitoring</t>
+  </si>
+  <si>
+    <t>Governance of change is not only technical recalibration: it must consider whether the model remains appropriate for its intended use and whether the changed system still fits its approved governance, risk tier, documentation and monitoring.</t>
+  </si>
+  <si>
+    <t>In ongoing validation, a challenger model outperforms the production model by 1 percentage point of AUC. Which response is most consistent with the book?</t>
+  </si>
+  <si>
+    <t>Discard the challenger, since validation is meant to prove that the production model is perfectly valid</t>
+  </si>
+  <si>
+    <t>Replace the production model immediately, since any benchmark outperformance proves the production model invalid</t>
+  </si>
+  <si>
+    <t>Ignore the result, since challenger models may be used only at initial validation and not afterward</t>
+  </si>
+  <si>
+    <t>Treat it as input to an iterative, documented review of purpose, assumptions, data and performance</t>
+  </si>
+  <si>
+    <t>Ongoing validation asks whether purpose, assumptions, data, methodology and performance remain appropriate. It is iterative, documented and risk-tiered, and can use benchmark or challenger models. Validation seeks weaknesses rather than proof of a perfect model.</t>
+  </si>
+  <si>
+    <t>Validators report to the head of model development, who also sets their bonuses. Which element of effective challenge is most compromised?</t>
+  </si>
+  <si>
+    <t>Sufficient influence, since bonuses determine the number of validation findings that validators raise</t>
+  </si>
+  <si>
+    <t>Independence, since validators answer to and are paid by the developers whose models they challenge</t>
+  </si>
+  <si>
+    <t>Technical competence, since reporting lines determine how well validators understand modeling methods</t>
+  </si>
+  <si>
+    <t>Documentation quality, since the head of development reviews all validation reports before issue</t>
+  </si>
+  <si>
+    <t>Effective challenge requires independence, competence and sufficient influence to drive improvement. Validators who report to and are paid by the developers' manager lack structural independence.</t>
+  </si>
+  <si>
+    <t>Which is a validation challenge distinctive to GenAI compared with traditional models?</t>
+  </si>
+  <si>
+    <t>Data drift does not occur, because pre-trained models cannot be affected by changes in input data</t>
+  </si>
+  <si>
+    <t>Rapid technological change and reliance on open-source or third-party models that the bank does not control</t>
+  </si>
+  <si>
+    <t>Validation can be fully automated, because open-ended outputs have a single correct reference answer</t>
+  </si>
+  <si>
+    <t>Outputs are fully deterministic, which makes one test per prompt sufficient to cover all behavior</t>
+  </si>
+  <si>
+    <t>GenAI validation requires special attention to open-ended outputs, different and more complex metrics, data drift and coverage, hallucination, bias, multimodal inputs, explainability, rapid technological change, open-source and third-party models, computational resources and human review.</t>
+  </si>
+  <si>
+    <t>A real-time scoring system calls an external cloud API for one input, and total response time breaches the customer-service limit at peak load. Which implementation consideration is illustrated?</t>
+  </si>
+  <si>
+    <t>Adaptation risk, because the original developers have left and the model has become a black box over time</t>
+  </si>
+  <si>
+    <t>Coordination risk, because the model designer also wrote the core implementation of the model engine</t>
+  </si>
+  <si>
+    <t>Computational design must weigh total response time, hardware dependence, API and cloud latency and bottlenecks</t>
+  </si>
+  <si>
+    <t>Misinterpretation risk, because users over-emphasize point estimates in the model's output when deciding</t>
+  </si>
+  <si>
+    <t>Running models requires reliable data gathering, processing, computation, analysis and reporting. Computational design must consider total response time, hardware dependence, APIs and cloud latency and parallel-process bottlenecks.</t>
+  </si>
+  <si>
+    <t>To speed up a model, a developer replaces readable logic with hand-tuned shortcuts that are undocumented and conflict with the design specification. Which implementation risk is illustrated?</t>
+  </si>
+  <si>
+    <t>Core and system implementation requiring identical skills, so one person should always do both</t>
+  </si>
+  <si>
+    <t>Scheduled runs gradually replacing ad hoc runs, which removes useful flexibility from the process</t>
+  </si>
+  <si>
+    <t>Overemphasis on point estimates, which hides uncertainty from the people who use the output</t>
+  </si>
+  <si>
+    <t>Optimization pressure creating opaque 'hacks' that conflict with design intent and hinder later adaptation</t>
+  </si>
+  <si>
+    <t>The book notes that optimization pressure can create opaque shortcuts or 'hacks' that conflict with design intent, adding to coordination risks and making later adaptation harder. Core and system implementation also require different skills.</t>
+  </si>
+  <si>
+    <t>A bank wants consistent AI governance standards but also wants each business line to adapt practices to its own models. Which organizational structure from the book fits best?</t>
+  </si>
+  <si>
+    <t>Assignment to existing roles only, with no cross-functional network or community of practice</t>
+  </si>
+  <si>
+    <t>Hub-and-spoke, with a central team setting standards and embedded units applying them</t>
+  </si>
+  <si>
+    <t>Fully centralized, with one team approving every model and use case in all business lines</t>
+  </si>
+  <si>
+    <t>Fully decentralized, with each business line setting its own standards and no central team</t>
+  </si>
+  <si>
+    <t>Organizational structures may be centralized, hub-and-spoke, decentralized, assigned to existing roles or created as dedicated functions, and cross-functional networks and communities of practice are possible. Hub-and-spoke combines central standards with local adaptation.</t>
+  </si>
+  <si>
+    <t>An auditor re-runs the same prompt on a GenAI tool and obtains different outputs, so the original result cannot be reproduced. Which statement is most consistent with the book?</t>
+  </si>
+  <si>
+    <t>Outputs are often opaque and probabilistic, creating audit and reproducibility challenges that logging helps address</t>
+  </si>
+  <si>
+    <t>This is irrelevant to governance, because only the base model's weights, not its outputs, are audited</t>
+  </si>
+  <si>
+    <t>This indicates a defect, because a validated GenAI model must return identical outputs to identical prompts</t>
+  </si>
+  <si>
+    <t>This is resolved by a one-time approval, because approved models return stable outputs afterward in production</t>
+  </si>
+  <si>
+    <t>GenAI is harder to govern because outputs are often opaque and probabilistic: the same prompt can produce different outputs, creating audit and reproducibility challenges. Adaptive practices include logs, audits, feedback loops, red-teaming and usage logging.</t>
+  </si>
+  <si>
+    <t>A bank's model-risk team lacks experience with cloud deployment and MLOps for its new ML models. Which action is most consistent with the book's final thoughts?</t>
+  </si>
+  <si>
+    <t>Rely on SR 11-7 alone, because principle-based guidance means technical skills are unnecessary</t>
+  </si>
+  <si>
+    <t>Build or hire specialists in cloud platforms, CI/CD, MLOps and monitoring, using external experts when needed</t>
+  </si>
+  <si>
+    <t>Limit validation to model design, since implementation and monitoring are not part of AI/ML risk</t>
+  </si>
+  <si>
+    <t>Delay validation until the models are retired, since specialist skills are needed only for decommissioning</t>
+  </si>
+  <si>
+    <t>Effective AI/ML validation needs hands-on AI/ML expertise plus strong foundations, and model-risk teams may need specialists in cloud platforms, CI/CD, MLOps, monitoring and ML observability, with external experts where internal expertise is insufficient. SR 11-7 remains relevant but does not replace skills.</t>
+  </si>
+  <si>
+    <t>Claude (set3) - Module 1</t>
+  </si>
+  <si>
+    <t>Claude (set3) - Module 2</t>
+  </si>
+  <si>
+    <t>Claude (set3) - Module 3</t>
+  </si>
+  <si>
+    <t>Claude (set3) - Module 4</t>
+  </si>
+  <si>
+    <t>Claude (set3) - Module 5</t>
+  </si>
+  <si>
+    <t>Claude (set4) - Module 1</t>
+  </si>
+  <si>
+    <t>Claude (set4) - Module 2</t>
+  </si>
+  <si>
+    <t>Claude (set4) - Module 3</t>
+  </si>
+  <si>
+    <t>Claude (set4) - Module 4</t>
+  </si>
+  <si>
+    <t>Claude (set4) - Module 5</t>
+  </si>
+  <si>
+    <t>A chess engine scores a position using material weights: queen 9, rook 5, bishop 3, knight 3, pawn 1. White has Q, 2R, B and 6P; Black has Q, R, 2B, 2N and 4P. What is White's score (White minus Black) and what is such a score used for?</t>
+  </si>
+  <si>
+    <t>-2; an exact game-theoretic value that guarantees the outcome of the game under best play</t>
+  </si>
+  <si>
+    <t>-2; a rule-of-thumb estimate that lets lookahead stop before the whole game tree is searched</t>
+  </si>
+  <si>
+    <t>0; a rule-of-thumb estimate that lets lookahead stop before the whole game tree is searched</t>
+  </si>
+  <si>
+    <t>+2; a rule-of-thumb estimate that lets lookahead stop before the whole game tree is searched</t>
+  </si>
+  <si>
+    <t>White = 9 + 10 + 3 + 6 = 28; Black = 9 + 5 + 6 + 6 + 4 = 30, so the score is -2 (equal piece counts would wrongly give 0). Heuristics are rules-of-thumb estimates that avoid exhaustive search of the combinatorially exploding game tree; they are not exact values.</t>
+  </si>
+  <si>
+    <t>Which statement best describes how heuristics, search and learning fit together in game-playing AI?</t>
+  </si>
+  <si>
+    <t>Reinforcement learning produced the heuristics first, and search was then dropped because lookahead became impossible</t>
+  </si>
+  <si>
+    <t>Heuristic evaluations let lookahead stop early, and reinforcement learning can later refine them with experience</t>
+  </si>
+  <si>
+    <t>Heuristics replaced search entirely, and reinforcement learning was used only to hard-code opening rules for the engine</t>
+  </si>
+  <si>
+    <t>Heuristics are exact values from exhaustive search, and reinforcement learning then makes them approximate to save time</t>
+  </si>
+  <si>
+    <t>Classical game AI combined search and lookahead with heuristics, which are rule-of-thumb estimates used to avoid exhaustive search. Heuristics can be refined with reinforcement learning. They are approximations rather than exact values, and they supplement rather than replace search.</t>
+  </si>
+  <si>
+    <t>A network has 4 inputs, a first hidden layer of 5 neurons, a second hidden layer of 3 neurons and an output layer of 2 neurons. Every neuron has one bias. How many trainable parameters does it have?</t>
+  </si>
+  <si>
+    <t>51</t>
+  </si>
+  <si>
+    <t>41</t>
+  </si>
+  <si>
+    <t>43</t>
+  </si>
+  <si>
+    <t>49</t>
+  </si>
+  <si>
+    <t>Weights: 4 x 5 + 5 x 3 + 3 x 2 = 20 + 15 + 6 = 41. Biases: 5 + 3 + 2 = 10. Total = 51. The value 41 counts weights only, 49 omits the output biases, and 43 omits the hidden-layer biases (41 + 2).</t>
+  </si>
+  <si>
+    <t>A neuron has binary inputs x1 and x2, weights (1, 1) and a step activation that outputs 1 if the weighted sum plus bias is greater than 0. Which bias makes it behave like a logical OR?</t>
+  </si>
+  <si>
+    <t>-1.5</t>
+  </si>
+  <si>
+    <t>-0.5</t>
+  </si>
+  <si>
+    <t>-2.5</t>
+  </si>
+  <si>
+    <t>0.5</t>
+  </si>
+  <si>
+    <t>With bias -0.5 the sum is -0.5 for inputs (0, 0) (output 0), 0.5 for one active input (output 1) and 1.5 for both (output 1), which is OR. A bias of -1.5 gives AND, +0.5 always fires, and -2.5 never fires.</t>
+  </si>
+  <si>
+    <t>A data set holds 1,000 loans, with the default outcome recorded for only 120 of them. Which statement about the learning types that could use it is correct?</t>
+  </si>
+  <si>
+    <t>Supervised learning could use all 1,000 loans, since unlabeled rows can simply be treated as non-default</t>
+  </si>
+  <si>
+    <t>Only unsupervised learning is possible, since a label must exist for every row before any supervised step</t>
+  </si>
+  <si>
+    <t>Reinforcement learning is the natural choice, since partial labels play the role of rewards for actions</t>
+  </si>
+  <si>
+    <t>Supervised learning could use the 120 labeled loans, while semi-supervised learning could use all 1,000 loans</t>
+  </si>
+  <si>
+    <t>Supervised learning needs labeled input-output examples (the 120 loans). Semi-supervised learning combines a small labeled set with a much larger unlabeled one, and unsupervised learning can use all 1,000 rows while ignoring the outcomes. Reinforcement learning needs reward or penalty feedback from an environment, which partial labels are not.</t>
+  </si>
+  <si>
+    <t>Which design best counters over-reliance in a human review step for AI credit recommendations?</t>
+  </si>
+  <si>
+    <t>Reviewers are rewarded for fast turnaround, so they do not second-guess the model on routine cases</t>
+  </si>
+  <si>
+    <t>A second model replaces the reviewers, so no human can defer to the output of the first model</t>
+  </si>
+  <si>
+    <t>Reviewers form their own view first and see model uncertainty, and override rates are tracked</t>
+  </si>
+  <si>
+    <t>Reviewers see only the final approve or decline output, so they are not distracted by supporting details</t>
+  </si>
+  <si>
+    <t>Over-reliance is the risk that humans defer to model output without sufficient scrutiny, so the check becomes nominal. Encouraging independent judgment, showing uncertainty and monitoring override rates keep human oversight meaningful. Hiding details or rewarding speed makes deference more likely.</t>
+  </si>
+  <si>
+    <t>A PCA is run on annual income in dollars (variance around 10^9) and a debt-to-income ratio (variance around 0.02) without scaling. What is the likely result?</t>
+  </si>
+  <si>
+    <t>The first component is dominated by income because PCA follows variance; standardize first to equalize scales</t>
+  </si>
+  <si>
+    <t>The result is unaffected, because PCA gives identical components whatever units the variables are measured in</t>
+  </si>
+  <si>
+    <t>The first component becomes supervised, because it weights income by its correlation with the default outcome</t>
+  </si>
+  <si>
+    <t>The first component is dominated by the ratio, because variables with small variance load most heavily on component one</t>
+  </si>
+  <si>
+    <t>PCA builds components that capture the most variability, so a variable measured on a vastly larger scale dominates the first component. Scaling or transforming predictors first is recommended. PCA is unsupervised and is not invariant to units.</t>
+  </si>
+  <si>
+    <t>A modeler converts continuous age into five age bands before fitting a regression. What is the most likely cost of this discretization?</t>
+  </si>
+  <si>
+    <t>Variation within each band is lost and the fitted relationship becomes a step function</t>
+  </si>
+  <si>
+    <t>Age is automatically standardized, which removes any non-linear effect that it had on the target variable</t>
+  </si>
+  <si>
+    <t>The relationship between age and the target is forced to be one straight line across the whole sample</t>
+  </si>
+  <si>
+    <t>Outliers in age are amplified, because each age band is rescaled to the 0-1 range before estimation</t>
+  </si>
+  <si>
+    <t>Discretization (binning) converts a continuous variable into ranges or categories. All observations in a band are treated alike, so within-band information is lost and the effect is modeled as a step function rather than a smooth relationship.</t>
+  </si>
+  <si>
+    <t>A card-transaction data set has a few amounts about 200 times the median. A cleaning script deletes all such values before a fraud model is built. What is the main concern?</t>
+  </si>
+  <si>
+    <t>Outliers affect only unsupervised methods, so a supervised fraud model cannot be harmed by removing them</t>
+  </si>
+  <si>
+    <t>Deleting rows changes the scale of the other variables, so standardization must be redone using the deleted rows</t>
+  </si>
+  <si>
+    <t>Outliers may be errors or useful signals, so deleting them may remove the very fraud cases of interest</t>
+  </si>
+  <si>
+    <t>Extreme values should always be replaced with the mean, because outliers are by definition data-entry errors</t>
+  </si>
+  <si>
+    <t>Data cleaning must address outliers, but they may be errors or informative signals, so treatment depends on the application. In fraud detection the extreme values may be exactly what the model needs to learn from.</t>
+  </si>
+  <si>
+    <t>A panel contains 500 firms observed for 10 years, giving 5,000 rows, and an analyst treats all rows as independent observations. What is the likely consequence?</t>
+  </si>
+  <si>
+    <t>Time dependence disappears once the variables are standardized, so the 5,000 rows are effectively independent</t>
+  </si>
+  <si>
+    <t>Longitudinal data are always independent, so no adjustment is needed once the rows are sorted by firm</t>
+  </si>
+  <si>
+    <t>Rows from one firm are dependent over time, so information is overstated and standard errors too small</t>
+  </si>
+  <si>
+    <t>The coefficients are biased toward zero, although the reported standard errors remain exactly correct</t>
+  </si>
+  <si>
+    <t>Cross-sectional observations are generally treated as independent, whereas longitudinal or time-series data have temporal or other dependence. Treating repeated observations of the same firm as independent overstates the effective sample size and understates uncertainty.</t>
+  </si>
+  <si>
+    <t>Three observations have silhouette values of 0.85, 0.05 and -0.40. Which interpretation is correct?</t>
+  </si>
+  <si>
+    <t>All three are well assigned, because silhouette values matter only when they fall below the value of -0.5</t>
+  </si>
+  <si>
+    <t>0.85 is well matched to its cluster, 0.05 lies near a cluster boundary, and -0.40 is probably in the wrong cluster</t>
+  </si>
+  <si>
+    <t>-0.40 is the best assignment, because values closer to -1 indicate tighter and better separated clusters</t>
+  </si>
+  <si>
+    <t>0.85 lies near a cluster boundary, 0.05 is well matched to its cluster, and -0.40 is a near-perfect assignment</t>
+  </si>
+  <si>
+    <t>Silhouette values near 1 indicate a well-separated, well-matched observation, values near 0 indicate an observation on the boundary between clusters, and negative values suggest the observation is closer to another cluster than to its own.</t>
+  </si>
+  <si>
+    <t>Points are A = (0, 0), B = (6, 0) and C = (3, 3). Which statement about their distances from A is correct?</t>
+  </si>
+  <si>
+    <t>Euclidean: B and C are equally far (6 each); Manhattan: C is nearer to A than B is (4.24 versus 6)</t>
+  </si>
+  <si>
+    <t>Both measures: C is nearer to A than B is, because squaring differences never changes the ranking of distances</t>
+  </si>
+  <si>
+    <t>Euclidean: B is nearer to A than C is (6 versus 6.7); Manhattan: C is nearer to A than B is (4.2 versus 6)</t>
+  </si>
+  <si>
+    <t>Euclidean: C is nearer to A than B is (4.24 versus 6); Manhattan: B and C are equally far (6 each)</t>
+  </si>
+  <si>
+    <t>Euclidean distance AC = sqrt(3^2 + 3^2) = 4.24 and AB = 6, so C is nearer. Manhattan distance AC = 3 + 3 = 6 and AB = 6, so they tie. The choice of distance measure can change which points are neighbors.</t>
+  </si>
+  <si>
+    <t>K-means with two clusters is applied to the one-dimensional points 2, 4, 10, 12 and 20, with initial centroids at 2 and 20. After the algorithm converges, what are the centroids and the WCSS?</t>
+  </si>
+  <si>
+    <t>Centroids 4.00 and 16.00; WCSS = 72.00</t>
+  </si>
+  <si>
+    <t>Centroids 2.00 and 20.00; WCSS = 132.00</t>
+  </si>
+  <si>
+    <t>Centroids 5.33 and 16.00; WCSS = 17.33</t>
+  </si>
+  <si>
+    <t>Centroids 5.33 and 16.00; WCSS = 66.67</t>
+  </si>
+  <si>
+    <t>First assignment: 2, 4, 10 go to centroid 2 and 12, 20 go to centroid 20, giving new centroids 5.33 and 16. Reassignment leaves the clusters unchanged, so the algorithm has converged. WCSS = (11.11 + 1.78 + 21.78) + (16 + 16) = 66.67. The value 17.33 sums absolute deviations, 72.00 uses medians, and 132.00 is the WCSS at the initial centroids.</t>
+  </si>
+  <si>
+    <t>A customer data set has one very large dense group, a small distant group and elongated, crescent-shaped groups. K-means with k = 2 splits the large group instead of separating the others. What best explains this?</t>
+  </si>
+  <si>
+    <t>WCSS is too high at k = 2, so setting k equal to the number of observations would give the correct clusters</t>
+  </si>
+  <si>
+    <t>K-means is a hierarchical method that merges the closest pairs, so unequal sizes only change dendrogram heights</t>
+  </si>
+  <si>
+    <t>K-means needs labeled data, so the split reflects missing labels and adding labels would correct the clusters</t>
+  </si>
+  <si>
+    <t>K-means assumes spherical, evenly sized clusters, so uneven sizes and crescents split badly; use density-based</t>
+  </si>
+  <si>
+    <t>A key weakness of K-means is its assumption of roughly spherical, evenly sized clusters. Density-based methods such as DBSCAN find irregular shapes and flag isolated points. K-means is unsupervised, not hierarchical, and setting k equal to the number of observations drives WCSS to zero without meaning.</t>
+  </si>
+  <si>
+    <t>A logistic model gives a baseline default probability of 0.25. A binary risk flag has a coefficient of ln(3) = 1.10. What is the default probability when the flag is on, other variables unchanged?</t>
+  </si>
+  <si>
+    <t>0.75</t>
+  </si>
+  <si>
+    <t>Baseline odds = 0.25 / 0.75 = 1/3. The flag multiplies the odds by e^1.10 = 3, giving odds of 1 and a probability of 1 / (1 + 1) = 0.50. The value 0.75 wrongly multiplies the probability by 3, and 0.33 is the baseline odds.</t>
+  </si>
+  <si>
+    <t>Backward elimination starts with four predictors whose p-values are 0.45 (X1), 0.08 (X2), 0.30 (X3) and 0.01 (X4), and removes a variable when its p-value exceeds 0.10. What happens first?</t>
+  </si>
+  <si>
+    <t>X1 and X3 are removed together at once, without refitting, because both exceed the threshold</t>
+  </si>
+  <si>
+    <t>X2 is removed first, because it is the variable closest to the removal threshold</t>
+  </si>
+  <si>
+    <t>X1 is removed first, then the model is refit and p-values re-examined before further removals</t>
+  </si>
+  <si>
+    <t>X4 is removed first, because it is the most significant variable in the current model</t>
+  </si>
+  <si>
+    <t>Backward elimination removes variables one at a time, starting with the least significant (highest p-value, X1). Because coefficients and p-values change when a variable leaves, the model must be refit before deciding on further removals.</t>
+  </si>
+  <si>
+    <t>A fitted model is y = 2 + 0.5 X1 - 1.2 X2 + 3 D, where D = 1 for secured loans. What is the prediction for X1 = 4, X2 = 1, D = 1, and how does it change if X2 rises by 2 with everything else fixed?</t>
+  </si>
+  <si>
+    <t>5.8; it falls by 2.4</t>
+  </si>
+  <si>
+    <t>5.8; it rises by 2.4</t>
+  </si>
+  <si>
+    <t>5.8; it falls by 1.2</t>
+  </si>
+  <si>
+    <t>2.8; it falls by 2.4</t>
+  </si>
+  <si>
+    <t>Prediction = 2 + 0.5(4) - 1.2(1) + 3(1) = 5.8. A coefficient is the effect of a one-unit change holding other variables constant, so a rise of 2 in X2 changes y by -1.2 x 2 = -2.4. The value 2.8 omits the dummy and -1.2 is the effect of one unit.</t>
+  </si>
+  <si>
+    <t>Consider (1) delinquency status: current, 30, 60 or 90+ days late; (2) a borrower's choice among fixed-rate, adjustable-rate or no mortgage; (3) default versus no default. Which models fit best?</t>
+  </si>
+  <si>
+    <t>(1) ordinal logit; (2) binary logistic regression; (3) multinomial logit</t>
+  </si>
+  <si>
+    <t>(1) binary logistic regression; (2) multinomial logit; (3) ordinal logit</t>
+  </si>
+  <si>
+    <t>(1) ordinal logit; (2) multinomial logit; (3) binary logistic regression</t>
+  </si>
+  <si>
+    <t>(1) multinomial logit; (2) ordinal logit; (3) binary logistic regression</t>
+  </si>
+  <si>
+    <t>Ordinal logistic regression is for ordered categories (delinquency stages), multinomial logistic regression for three or more unordered categories (product choice), and ordinary logistic regression for a binary outcome.</t>
+  </si>
+  <si>
+    <t>A regulator requires a bank to justify the sign of each coefficient in its PD model. A neural network improves AUC by 0.004 over the logistic model. Which view is best supported?</t>
+  </si>
+  <si>
+    <t>The logistic model cannot be validated, because maximum likelihood coefficients lack a probabilistic interpretation</t>
+  </si>
+  <si>
+    <t>Interpretability is irrelevant to regulated risk models, because validation relies only on out-of-sample accuracy</t>
+  </si>
+  <si>
+    <t>Econometric models stay valuable in regulation since coefficients are interpretable, outweighing a tiny AUC gain</t>
+  </si>
+  <si>
+    <t>The neural network must be chosen, because any AUC gain proves that the logistic model is misspecified and invalid</t>
+  </si>
+  <si>
+    <t>The book notes that econometric models remain valuable in regulated risk contexts because of their interpretability. A very small predictive gain from a less interpretable model must be weighed against explainability, supervisory feedback and cost.</t>
+  </si>
+  <si>
+    <t>A random forest of 500 trees has 320 trees voting Default for a borrower. What is the predicted class under a simple majority vote and under a decision rule that requires a vote share of at least 0.70 to predict Default?</t>
+  </si>
+  <si>
+    <t>Default under majority vote (share 0.64); Non-default under the 0.70 rule</t>
+  </si>
+  <si>
+    <t>Default under both rules, because 320 trees exceed half of the forest</t>
+  </si>
+  <si>
+    <t>Non-default under majority vote (share 0.36); Default under the 0.70 rule</t>
+  </si>
+  <si>
+    <t>Non-default under both rules, because the vote share is below 0.70</t>
+  </si>
+  <si>
+    <t>The vote share for Default is 320/500 = 0.64, which exceeds 0.50 (majority vote gives Default) but is below 0.70 (the stricter rule gives Non-default). Cutoffs can be tuned to reflect the relative cost of errors.</t>
+  </si>
+  <si>
+    <t>A hidden layer of 250 neurons uses dropout with probability 0.4 during training. How many neurons are expected to be active on a training step, and how is the layer used at prediction time?</t>
+  </si>
+  <si>
+    <t>About 250 are active; dropout changes only the weights and never which neurons are used</t>
+  </si>
+  <si>
+    <t>About 150 are active; all neurons are used at prediction time because dropout is switched off</t>
+  </si>
+  <si>
+    <t>About 150 are active; only those 150 neurons are retained permanently once training has ended</t>
+  </si>
+  <si>
+    <t>About 100 are active; all neurons are used at prediction time because dropout is switched off</t>
+  </si>
+  <si>
+    <t>Dropout randomly disables neurons during training to mitigate overfitting. With probability 0.4 of dropping, 250 x 0.6 = 150 neurons are expected to remain active. At prediction time dropout is switched off and the whole layer is used.</t>
+  </si>
+  <si>
+    <t>A trained SVM with 10,000 training points has 40 support vectors. If 500 points that are not support vectors are deleted and the model is retrained, what is the likely result?</t>
+  </si>
+  <si>
+    <t>The boundary stays the same, because it is determined only by the points on or inside the margin</t>
+  </si>
+  <si>
+    <t>The boundary shifts toward the deleted points, because every training point contributes equally to its position</t>
+  </si>
+  <si>
+    <t>The kernel must be changed, because deleting any points breaks the separability of the two classes</t>
+  </si>
+  <si>
+    <t>The margin doubles in width, because fewer points are available to constrain the position of the boundary</t>
+  </si>
+  <si>
+    <t>An SVM finds the boundary that maximizes the margin, and only the support vectors (points on or inside the margin) determine it. Removing other points leaves the boundary unchanged.</t>
+  </si>
+  <si>
+    <t>A KNN classifier is trained on 500 loans, 60% of which are non-default. What happens if k is set equal to 500?</t>
+  </si>
+  <si>
+    <t>Predictions equal the training labels exactly, so the training error is zero and validation error is minimized</t>
+  </si>
+  <si>
+    <t>The model becomes unsupervised, because no distances are needed once all observations are neighbors</t>
+  </si>
+  <si>
+    <t>Every prediction equals the nearest single neighbor, so the model memorizes the training data and overfits</t>
+  </si>
+  <si>
+    <t>Every prediction is the majority class (Non-default), so the model underfits and ignores the features entirely</t>
+  </si>
+  <si>
+    <t>With k equal to the number of training points, every query is compared with all observations and the majority vote is the same everywhere: the majority class. This is extreme underfitting, the opposite of k = 1, which memorizes the training data.</t>
+  </si>
+  <si>
+    <t>An autoencoder for anomaly detection is built with a hidden layer as wide as the input layer. Why is this a poor design?</t>
+  </si>
+  <si>
+    <t>A wide hidden layer causes vanishing gradients, so the decoder part of the network cannot be trained at all</t>
+  </si>
+  <si>
+    <t>It raises the reconstruction error for normal data, so every transaction ends up being flagged as an anomaly</t>
+  </si>
+  <si>
+    <t>With no bottleneck it can copy its input, so anomalies are reconstructed well and the error signal is lost</t>
+  </si>
+  <si>
+    <t>A wide hidden layer forces the use of labeled fraud examples, so the network turns into a supervised model</t>
+  </si>
+  <si>
+    <t>An autoencoder is trained to reconstruct its input through a compressed bottleneck, and anomalies are detected because they reconstruct poorly. Without a bottleneck the network can simply copy the input, so even unusual inputs are reconstructed well.</t>
+  </si>
+  <si>
+    <t>Why does ReLU mitigate the vanishing-gradient problem in deep networks better than sigmoid?</t>
+  </si>
+  <si>
+    <t>Its derivative is negative for positive inputs, so gradients change sign and cancel local minima</t>
+  </si>
+  <si>
+    <t>It randomizes the weights at every layer, so the chain rule is not needed during backpropagation</t>
+  </si>
+  <si>
+    <t>Its output is bounded between 0 and 1, so gradients can never exceed the value of the activation</t>
+  </si>
+  <si>
+    <t>Its derivative is 1 for positive inputs, so many layers of multiplication do not shrink the gradient</t>
+  </si>
+  <si>
+    <t>Backpropagation multiplies many derivatives via the chain rule; with sigmoid these are small (at most 0.25), so the gradient shrinks toward zero. ReLU has a derivative of 1 for positive inputs, which preserves the gradient through many layers.</t>
+  </si>
+  <si>
+    <t>A regression-tree leaf contains the target values 10, 14 and 30, and a classification-tree leaf contains 7 defaults and 3 non-defaults. What do the two leaves predict?</t>
+  </si>
+  <si>
+    <t>18 and Default</t>
+  </si>
+  <si>
+    <t>18 and Non-default</t>
+  </si>
+  <si>
+    <t>14 and Default</t>
+  </si>
+  <si>
+    <t>54 and Default</t>
+  </si>
+  <si>
+    <t>A regression leaf predicts the average outcome: (10 + 14 + 30) / 3 = 18 (the outlier pulls it above the median of 14). A classification leaf predicts the majority class, here Default (7 of 10). The value 54 is the sum.</t>
+  </si>
+  <si>
+    <t>Consider (1) PCA fitted on all 50,200 loans, then a supervised model trained on the 200 labeled loans; (2) K-means on all loans, with each cluster given its majority label; (3) an autoencoder trained on the unlabeled pool, then fine-tuned on the labeled loans. Which strategies are these?</t>
+  </si>
+  <si>
+    <t>(1) cluster-then-label; (2) feature extraction; (3) pre-training</t>
+  </si>
+  <si>
+    <t>(1) feature extraction; (2) pre-training; (3) cluster-then-label</t>
+  </si>
+  <si>
+    <t>(1) pre-training; (2) cluster-then-label; (3) feature extraction</t>
+  </si>
+  <si>
+    <t>(1) feature extraction; (2) cluster-then-label; (3) pre-training</t>
+  </si>
+  <si>
+    <t>The three unsupervised pre-processing strategies are feature extraction (PCA or autoencoders on all data, then supervised learning on the labeled part), cluster-then-label (cluster all data and assign each cluster its majority class) and pre-training (train on unlabeled data, then fine-tune on labeled data).</t>
+  </si>
+  <si>
+    <t>An analyst proposes dropping 2 million unlabeled transactions and training only on 300 confirmed frauds, calling the unlabeled data unreliable. What is the best critique?</t>
+  </si>
+  <si>
+    <t>Discarding unlabeled data wastes information; semi-supervised methods can use it when their assumptions hold</t>
+  </si>
+  <si>
+    <t>The unlabeled data should first be labeled by hand, so that the whole problem becomes an unsupervised one</t>
+  </si>
+  <si>
+    <t>The proposal is correct, because semi-supervised learning requires more labeled than unlabeled observations</t>
+  </si>
+  <si>
+    <t>Unlabeled data can never improve a model, so the proposal is correct and the extra data would only add noise</t>
+  </si>
+  <si>
+    <t>Semi-supervised learning bridges unsupervised and supervised learning by using a small labeled set plus much more unlabeled data. Discarding either wastes information, and labeling everything manually is often too costly or impossible, as with rare confirmed fraud.</t>
+  </si>
+  <si>
+    <t>A self-training model adds every unlabeled observation whose predicted class probability is at least 0.90. P(default) for five unlabeled observations is 0.97, 0.52, 0.08, 0.93 and 0.15. Which are added, with which pseudo-labels?</t>
+  </si>
+  <si>
+    <t>Observations 1 and 4 as Default only</t>
+  </si>
+  <si>
+    <t>Observations 1 and 4 as Default, and observation 3 as Non-default</t>
+  </si>
+  <si>
+    <t>Observations 2 and 5 as Non-default, and observation 1 as Default</t>
+  </si>
+  <si>
+    <t>Observations 1, 3 and 5 as Default, and observation 4 as Non-default</t>
+  </si>
+  <si>
+    <t>Confidence is the probability of the predicted class: 0.97 (Default), 0.52 (Default), 0.92 (Non-default), 0.93 (Default) and 0.85 (Non-default) for observations 1 to 5. Those at or above 0.90 are observations 1, 3 and 4, with pseudo-labels Default, Non-default and Default.</t>
+  </si>
+  <si>
+    <t>A greedy agent plays machine A once (reward 4) and machine B once (reward 1), then always plays A. The true mean payouts are A = 3 and B = 6. Why does the agent fail and what would help?</t>
+  </si>
+  <si>
+    <t>Pure exploration stops Q-values from converging; lowering the discount factor would let the agent settle on B</t>
+  </si>
+  <si>
+    <t>Q-values should be updated only at the end of an episode; Monte Carlo averaging would make machine A look worse</t>
+  </si>
+  <si>
+    <t>Rewards should be normalized to the 0-1 range before estimating Q; this would make machine A look worse</t>
+  </si>
+  <si>
+    <t>Pure exploitation locks onto a lucky early estimate; epsilon-greedy exploration would let it revisit B</t>
+  </si>
+  <si>
+    <t>A greedy strategy always exploits the best-so-far machine and can get stuck on a suboptimal choice, never trying options that might be better. Epsilon-greedy balances exploration and exploitation by exploring at random with probability epsilon.</t>
+  </si>
+  <si>
+    <t>Consider (1) the expected future reward from being in a state under a policy; (2) the expected future reward from taking a specific action in a state and then following the policy; (3) the rule mapping states to actions. Which terms match?</t>
+  </si>
+  <si>
+    <t>(1) policy; (2) Q(s, a); (3) V(s)</t>
+  </si>
+  <si>
+    <t>(1) V(s); (2) policy; (3) Q(s, a)</t>
+  </si>
+  <si>
+    <t>(1) V(s); (2) Q(s, a); (3) policy</t>
+  </si>
+  <si>
+    <t>(1) Q(s, a); (2) V(s); (3) policy</t>
+  </si>
+  <si>
+    <t>The value function V(s) is the expected future reward from state s under a policy, the action-value function Q(s, a) is the expected future reward from taking action a in state s and then following the policy, and the policy is the rule mapping states to actions.</t>
+  </si>
+  <si>
+    <t>Which problem is best framed as reinforcement learning?</t>
+  </si>
+  <si>
+    <t>Predicting next-quarter default probabilities from a labeled history of loan outcomes and borrower features</t>
+  </si>
+  <si>
+    <t>Compressing 40 correlated macro variables into a few uncorrelated components that keep most variance</t>
+  </si>
+  <si>
+    <t>Executing a large block order through the day, where each slice affects later prices and the agent learns from market impact</t>
+  </si>
+  <si>
+    <t>Grouping customers into segments from unlabeled transaction data without any outcome or reward signal</t>
+  </si>
+  <si>
+    <t>Reinforcement learning applies when an agent's actions affect the environment and it learns a policy from rewards or penalties, such as minimizing the market impact of block orders. Default prediction is supervised, and customer grouping and PCA are unsupervised.</t>
+  </si>
+  <si>
+    <t>Why is it problematic to treat the minimization of market impact in order execution as supervised learning on historical orders?</t>
+  </si>
+  <si>
+    <t>Supervised models cannot be trained on time-stamped data, so the historical orders would have to be treated as unlabeled</t>
+  </si>
+  <si>
+    <t>The agent's own actions change prices and future states, so historical labels cannot show the consequences of new actions; RL learns a policy through interaction</t>
+  </si>
+  <si>
+    <t>Historical orders always lack features, so only clustering could be applied to describe the trading data</t>
+  </si>
+  <si>
+    <t>Supervised learning requires a discount factor, which cannot be defined for market prices or order sizes</t>
+  </si>
+  <si>
+    <t>Reinforcement learning outputs an action or policy rather than a prediction, and the agent's own actions affect what it observes next. A supervised model fitted to historical orders cannot capture how new actions change the market; RL learns from rewards or penalties through trial-and-error interaction.</t>
+  </si>
+  <si>
+    <t>Which model requires nonlinear least squares rather than OLS?</t>
+  </si>
+  <si>
+    <t>y = a + b1 x1 + b2 x2 + error, which has two regressors but is linear in all parameters</t>
+  </si>
+  <si>
+    <t>y = a + b x + c x^2 + error, which is nonlinear in x but linear in a, b and c</t>
+  </si>
+  <si>
+    <t>y = a x exp(b x) + error, which is nonlinear in the parameters a and b</t>
+  </si>
+  <si>
+    <t>y = a + b ln(x) + error, which uses a transformed regressor but is linear in a and b</t>
+  </si>
+  <si>
+    <t>OLS has an analytical solution for models linear in their parameters, even when the regressors are transformed (squares, logs). Models that are nonlinear in the parameters, such as a x exp(b x) or neural networks, have no closed-form solution and need nonlinear least squares.</t>
+  </si>
+  <si>
+    <t>OLS is used to fit y = a + b x to the points (1, 2), (2, 3) and (3, 5). What are the estimated slope and intercept?</t>
+  </si>
+  <si>
+    <t>Slope 1.50; intercept 0.33</t>
+  </si>
+  <si>
+    <t>Slope 1.00; intercept 1.00</t>
+  </si>
+  <si>
+    <t>Slope 0.64; intercept 2.05</t>
+  </si>
+  <si>
+    <t>Slope 1.50; intercept 1.83</t>
+  </si>
+  <si>
+    <t>x-bar = 2 and y-bar = 3.33. Slope = sum of (x - x-bar)(y - y-bar) / sum of (x - x-bar)^2 = 3 / 2 = 1.5, and intercept = 3.33 - 1.5 x 2 = 0.33. The value 1.83 forgets to multiply the slope by x-bar, 1.00/1.00 fits only two points, and 0.64 comes from regressing x on y.</t>
+  </si>
+  <si>
+    <t>Which sequence correctly describes training a neural network with backpropagation?</t>
+  </si>
+  <si>
+    <t>Feedforward pass; initialize weights randomly; update weights by gradient descent; calculate error; backward pass; repeat</t>
+  </si>
+  <si>
+    <t>Initialize weights to zero; calculate error; feedforward pass; backward pass of the error; update weights; repeat</t>
+  </si>
+  <si>
+    <t>Initialize weights randomly; feedforward pass; calculate error; backward pass; update by gradient descent; repeat</t>
+  </si>
+  <si>
+    <t>Initialize weights randomly; backward pass of the error; feedforward pass; calculate error; update weights; repeat</t>
+  </si>
+  <si>
+    <t>Backpropagation applies gradient descent to all weights using the chain rule: weights and biases are initialized randomly, a feedforward pass computes the output, the error is calculated, the error is propagated backward from the output layer, weights are updated, and the process repeats.</t>
+  </si>
+  <si>
+    <t>OLS gives coefficients of +50 and -48 on two nearly identical features. What does ridge regularization do and why is it helpful here?</t>
+  </si>
+  <si>
+    <t>It increases both coefficients, because the penalty term is added to the fitted values rather than to the loss</t>
+  </si>
+  <si>
+    <t>It removes both features entirely, because the L2 penalty sets the coefficients of correlated features to exactly zero</t>
+  </si>
+  <si>
+    <t>It shrinks both coefficients toward zero, preventing a large positive coefficient from being offset by a large negative one</t>
+  </si>
+  <si>
+    <t>It leaves both unchanged, because regularization applies only to the intercept and not to the slopes</t>
+  </si>
+  <si>
+    <t>Ridge (L2) adds the sum of squared coefficients to the loss, shrinking coefficients toward (but rarely exactly to) zero. It is especially useful for correlated features, where unregularized estimates can be large and offsetting.</t>
+  </si>
+  <si>
+    <t>A linear model, a gradient-boosted model and a neural network have R-squared values of 0.62, 0.71 and 0.74 out of sample. Regulators require every decision to be explained. Which statement best reflects the accuracy-interpretability trade-off?</t>
+  </si>
+  <si>
+    <t>Linear models are less interpretable, because their coefficients cannot support any causal reasoning</t>
+  </si>
+  <si>
+    <t>More flexible models often predict better but are less interpretable, so gains must be weighed against explainability</t>
+  </si>
+  <si>
+    <t>More flexible models are both more accurate and more interpretable, because they have more parameters to inspect</t>
+  </si>
+  <si>
+    <t>Accuracy and interpretability are unrelated, so the choice depends only on how fast each model trains</t>
+  </si>
+  <si>
+    <t>Flexible models can fit more shapes and tend to predict more accurately but are less interpretable (black boxes). Simple models such as linear regression remain popular in finance because they are interpretable and support reasoning about relationships.</t>
+  </si>
+  <si>
+    <t>A modeler tunes lambda over the grid 0, 10, 20, ..., 100, but the best value is near 0.003. What is the problem and the fix?</t>
+  </si>
+  <si>
+    <t>Grid search cannot tune lambda, so hill climbing must be used because lambda is not differentiable</t>
+  </si>
+  <si>
+    <t>A coarse linear grid can miss the optimum when the scale is unknown; use a log scale such as 10^-4 to 10^1</t>
+  </si>
+  <si>
+    <t>The grid is too fine, so reducing it to the two points 0 and 100 would locate the optimum faster</t>
+  </si>
+  <si>
+    <t>Cross-validation should be removed, because evaluating each lambda on the full sample is more accurate</t>
+  </si>
+  <si>
+    <t>Grid search evaluates a predefined set of hyperparameter values with cross-validation. A weakness is that you may not know the right scale to search, so a log or power scale (10^-1, 10^0, 10^1 and so on) may be needed; a coarse grid can miss the optimum entirely.</t>
+  </si>
+  <si>
+    <t>A model's ROC curve passes through (FPR, TPR) = (0.2, 0.2), (0.5, 0.5) and (0.8, 0.8). What does this indicate?</t>
+  </si>
+  <si>
+    <t>The AUC is about 0.2, because the first point on the curve has a false positive rate of 0.2</t>
+  </si>
+  <si>
+    <t>The AUC is about 0.8, because the highest point on the curve has a value of 0.8</t>
+  </si>
+  <si>
+    <t>The AUC is about 0.5, since TPR equals FPR throughout, so ranking is no better than random</t>
+  </si>
+  <si>
+    <t>The AUC is about 1.0, because TPR equals FPR at every threshold and the classes are separated</t>
+  </si>
+  <si>
+    <t>A ROC curve on the diagonal (TPR = FPR) means that raising the true positive rate costs an equal rise in false positives, so the model has no discriminatory power: AUC-ROC = 0.5, no better than random.</t>
+  </si>
+  <si>
+    <t>A fraud model has an AUC-ROC of 0.35 on a large test set. What is the best interpretation?</t>
+  </si>
+  <si>
+    <t>It ranks cases in the wrong direction; reversing its scores would give an AUC near 0.65, so check the labeling</t>
+  </si>
+  <si>
+    <t>It is better than random, because any AUC above zero indicates that the model has some predictive power</t>
+  </si>
+  <si>
+    <t>It has no information, because AUC below 0.5 arises only from sampling noise in small samples of data</t>
+  </si>
+  <si>
+    <t>It is well calibrated, because AUC below 0.5 indicates conservative probability estimates by the model</t>
+  </si>
+  <si>
+    <t>An AUC of 0.5 is no better than random. A value of 0.35 on a large sample means the scores are systematically inverted: flipping them would yield 1 - 0.35 = 0.65. The likely cause is a labeling or score-direction error, not noise or calibration.</t>
+  </si>
+  <si>
+    <t>An AML model (1) fails to flag a genuine launderer and (2) flags a legitimate customer. How are the two errors classified and which metric does each lower?</t>
+  </si>
+  <si>
+    <t>(1) false negative, lowering recall; (2) false positive, lowering precision</t>
+  </si>
+  <si>
+    <t>(1) false negative, lowering precision; (2) false positive, lowering recall</t>
+  </si>
+  <si>
+    <t>(1) true negative, lowering specificity; (2) true positive, lowering accuracy</t>
+  </si>
+  <si>
+    <t>(1) false positive, lowering precision; (2) false negative, lowering recall</t>
+  </si>
+  <si>
+    <t>A false negative is an actual positive predicted negative; it reduces recall = TP/(TP + FN). A false positive is an actual negative predicted positive; it reduces precision = TP/(TP + FP).</t>
+  </si>
+  <si>
+    <t>An LGD model has an MSE of 0.04 and an MAE of 0.15 (LGD measured as a decimal). What is the RMSE and what does its comparison with the MAE suggest?</t>
+  </si>
+  <si>
+    <t>RMSE is 0.04, equal to the MSE, which signals that all errors are uniformly small</t>
+  </si>
+  <si>
+    <t>RMSE is 0.20, above the MAE of 0.15, which signals that some errors are larger than typical</t>
+  </si>
+  <si>
+    <t>RMSE is 0.20, equal to the MAE, which signals that all errors have the same magnitude</t>
+  </si>
+  <si>
+    <t>RMSE is 0.0016, the square of the MSE, which signals that errors are negligible in size</t>
+  </si>
+  <si>
+    <t>RMSE = sqrt(MSE) = sqrt(0.04) = 0.20, which returns to the original units. Squaring penalizes large errors disproportionately, so RMSE above MAE (0.20 versus 0.15) indicates that error sizes vary, with some large misses.</t>
+  </si>
+  <si>
+    <t>A bank's loss from a pricing error grows with the square of the error, so large mistakes are disproportionately costly. Which evaluation metric best matches this objective?</t>
+  </si>
+  <si>
+    <t>MAE, since it penalizes large errors disproportionately more than small errors do</t>
+  </si>
+  <si>
+    <t>R-squared, since it measures the monetary cost of large errors directly in the loss</t>
+  </si>
+  <si>
+    <t>Accuracy, since it ranks pricing errors by their sign rather than their magnitude</t>
+  </si>
+  <si>
+    <t>MSE or RMSE, since squaring penalizes large errors disproportionately, like the bank's loss</t>
+  </si>
+  <si>
+    <t>MSE penalizes large errors disproportionately because of squaring, and RMSE returns the measure to the original units. MAE treats errors proportionally, and R-squared measures the proportion of variance explained rather than loss.</t>
+  </si>
+  <si>
+    <t>One text-processing method returns the dictionary form of a word using vocabulary and morphology, while another chops off suffixes and may produce non-words. Which statement correctly names them?</t>
+  </si>
+  <si>
+    <t>Neither changes the tokens; both only split the text into words or sub-words</t>
+  </si>
+  <si>
+    <t>Both return dictionary forms, but stemming also removes stop words from the sentence</t>
+  </si>
+  <si>
+    <t>Stemming returns the dictionary form; lemmatization chops suffixes and may produce non-words</t>
+  </si>
+  <si>
+    <t>Lemmatization returns the dictionary form; stemming chops suffixes and may produce non-words</t>
+  </si>
+  <si>
+    <t>Stemming and lemmatization both reduce words to a root form. Lemmatization uses vocabulary and morphology to return a proper base form, while stemming crudely strips suffixes and can produce non-words. Splitting text into words is tokenization.</t>
+  </si>
+  <si>
+    <t>'The bank denied the borrower' and 'The borrower denied the bank' give identical bag-of-words vectors. What does this show and what partly mitigates it?</t>
+  </si>
+  <si>
+    <t>Bag-of-words keeps word order but loses word frequency, so simply counting the words fixes the problem</t>
+  </si>
+  <si>
+    <t>Bag-of-words discards word order so different meanings can share a vector; n-grams capture some local word order</t>
+  </si>
+  <si>
+    <t>Bag-of-words uses dense embeddings, so the vectors coincide only when the embedding is trained on a small corpus</t>
+  </si>
+  <si>
+    <t>Bag-of-words treats synonyms as identical, so a longer stop-word list would give the two sentences different vectors</t>
+  </si>
+  <si>
+    <t>A bag-of-words representation counts words regardless of order, so sentences with the same words but different meanings look identical. N-grams, such as bigrams, capture some local word order, and contextual models such as transformers go further.</t>
+  </si>
+  <si>
+    <t>A general-purpose sentiment dictionary scores 10-K filings as very negative because it treats 'liability', 'tax' and 'cost' as negative words. Which statement best explains the problem?</t>
+  </si>
+  <si>
+    <t>Dictionary methods cannot be interpreted, so scores cannot be traced back to individual words in the filings</t>
+  </si>
+  <si>
+    <t>Dictionary methods need labeled training data, so the dictionary should be re-estimated using the filings' own labels</t>
+  </si>
+  <si>
+    <t>Dictionary methods miss context and domain meaning; a finance-specific lexicon or a trained model would handle it better</t>
+  </si>
+  <si>
+    <t>The problem arises from n-grams, so using only single words would remove the domain mismatch entirely</t>
+  </si>
+  <si>
+    <t>Dictionary-based classification compares text with predefined word lists. It is simple, interpretable and needs no training data, but it misses context (negation, sarcasm, domain-specific meaning) and out-of-vocabulary words.</t>
+  </si>
+  <si>
+    <t>A relevant clause sits at the start of a 2,000-token filing. Which statement best compares RNNs, LSTMs and transformers on long-range dependencies?</t>
+  </si>
+  <si>
+    <t>LSTMs use multi-head self-attention in parallel, whereas transformers rely on forget, input and output gates</t>
+  </si>
+  <si>
+    <t>RNNs suffer from vanishing gradients, LSTM gates mitigate this, and transformers use parallel self-attention</t>
+  </si>
+  <si>
+    <t>All three have identical long-range ability and differ only in the dimension of the embeddings that they use</t>
+  </si>
+  <si>
+    <t>RNNs handle long ranges best because recurrent memory is unlimited, and transformers process tokens strictly one at a time</t>
+  </si>
+  <si>
+    <t>RNNs process sequences with recurrent memory but struggle with long-range dependencies because of vanishing gradients. LSTMs add forget, input and output gates to mitigate this. Transformers use self-attention, process sequences in parallel and capture long-range dependencies.</t>
+  </si>
+  <si>
+    <t>An LLM's next-token probabilities, from highest to lowest, are 0.35, 0.25, 0.15, 0.10, 0.08 and 0.07. With Top-K sampling at K = 3 and the retained probabilities renormalized, what is the probability of the top token?</t>
+  </si>
+  <si>
+    <t>0.47</t>
+  </si>
+  <si>
+    <t>0.35</t>
+  </si>
+  <si>
+    <t>Top-K keeps the 3 most probable tokens, with total probability 0.35 + 0.25 + 0.15 = 0.75. Renormalizing gives 0.35 / 0.75 = 0.47 for the top token (and 0.33 and 0.20 for the others). The value 0.35 is before renormalization and 0.75 is the pool's total.</t>
+  </si>
+  <si>
+    <t>Consider (1) giving the model three worked input-output examples in the prompt; (2) instructing it to reason step by step before answering; (3) sampling several reasoning paths and taking the majority answer. Which techniques are these?</t>
+  </si>
+  <si>
+    <t>(1) few-shot prompting; (2) self-consistency; (3) chain-of-thought</t>
+  </si>
+  <si>
+    <t>(1) zero-shot prompting; (2) chain-of-thought; (3) tree-of-thought</t>
+  </si>
+  <si>
+    <t>(1) chain-of-thought; (2) few-shot prompting; (3) self-consistency</t>
+  </si>
+  <si>
+    <t>(1) few-shot prompting; (2) chain-of-thought; (3) self-consistency</t>
+  </si>
+  <si>
+    <t>Few-shot prompting supplies a few examples in the prompt, chain-of-thought elicits step-by-step reasoning, and self-consistency samples several reasoning paths and chooses the most common answer. Zero-shot gives no examples.</t>
+  </si>
+  <si>
+    <t>A screening model flags 50 applicants in Group A, of whom 40 are true positives, and 30 applicants in Group B, of whom 15 are true positives. Which statement is correct?</t>
+  </si>
+  <si>
+    <t>Precision is 0.20 versus 0.50, so flags against Group A are less reliable than flags against Group B</t>
+  </si>
+  <si>
+    <t>Precision is 0.80 versus 0.50, so Group B is advantaged because fewer of its flags turn out to be correct</t>
+  </si>
+  <si>
+    <t>Precision is equal across groups, because both groups have a similar absolute number of correct flags</t>
+  </si>
+  <si>
+    <t>Precision is 0.80 versus 0.50, so flags against Group B are far less often correct, a predictive-value gap</t>
+  </si>
+  <si>
+    <t>Precision = TP / (TP + FP): Group A = 40/50 = 0.80 and Group B = 15/30 = 0.50. The book notes that fairness is assessed by comparing metrics such as precision, recall and false positive rate across groups; a flag is much less reliable for Group B.</t>
+  </si>
+  <si>
+    <t>Two applicants have identical financial profiles except for gender, and the model scores differ by 60 points, although approval rates by gender are equal overall. Which statement is most accurate?</t>
+  </si>
+  <si>
+    <t>Group parity can hold while individual fairness is violated, since similar individuals get different predictions</t>
+  </si>
+  <si>
+    <t>Individual fairness is satisfied, because it requires only that approval rates are equal across the groups</t>
+  </si>
+  <si>
+    <t>Fairness is satisfied, because equal group approval rates imply that every pair of individuals is treated equally</t>
+  </si>
+  <si>
+    <t>Neither notion applies, because fairness concerns only the training data and never the model's predictions</t>
+  </si>
+  <si>
+    <t>Individual fairness requires similar individuals to receive similar predictions, while group fairness requires statistically comparable outcomes across groups. They are distinct and can conflict: equal group approval rates do not guarantee that similar individuals are treated alike.</t>
+  </si>
+  <si>
+    <t>A bank uses a simple linear scorecard whose coefficients anyone can read, but it has never told customers or regulators that the scorecard is used. How should this be described?</t>
+  </si>
+  <si>
+    <t>Transparent but not interpretable: the use is disclosed, but the internal logic cannot be understood</t>
+  </si>
+  <si>
+    <t>Neither, since a linear scorecard cannot be interpreted without a post-hoc explanation method</t>
+  </si>
+  <si>
+    <t>Both transparent and interpretable, since a model that is easy to read is automatically disclosed</t>
+  </si>
+  <si>
+    <t>Interpretable but not transparent: the logic is easy to read, but nothing is disclosed organizationally</t>
+  </si>
+  <si>
+    <t>Interpretability is how understandable a model's internal logic is on its own terms (a simple linear scorecard scores high). Transparency is organizational disclosure about its existence, purpose and general functioning. They are independent, so a model can be interpretable but undisclosed.</t>
+  </si>
+  <si>
+    <t>Explanations for declined applicants show that ZIP code dominates the decision for one demographic group. Which benefit of explainability is illustrated?</t>
+  </si>
+  <si>
+    <t>Explanations help detect bias and errors, here revealing a proxy variable that may reproduce disparity</t>
+  </si>
+  <si>
+    <t>Explanations demonstrate transparency, since the bank has disclosed that the model exists</t>
+  </si>
+  <si>
+    <t>Explanations make the model interpretable overall, so no further bias testing is necessary</t>
+  </si>
+  <si>
+    <t>Explanations prove group fairness, since one dominant variable implies equal outcomes across groups</t>
+  </si>
+  <si>
+    <t>Explainability supports accountability, error and bias detection, trust and protection of rights. Local explanations can expose that a variable correlated with a protected attribute is driving decisions, which prompts review of the proxy; they do not prove fairness or make the whole model interpretable.</t>
+  </si>
+  <si>
+    <t>An autonomous agent executes 200 trades per minute and a human reviews its activity every 15 minutes. What is the maximum unreviewed activity, and which control best addresses the autonomy risk?</t>
+  </si>
+  <si>
+    <t>Up to 3,000 trades; shorten the checkpoint interval or add approval and exposure limits to cap errors</t>
+  </si>
+  <si>
+    <t>Up to 3,000 trades; the risk is lack of transparency, so publishing the model's design is the best control</t>
+  </si>
+  <si>
+    <t>Up to 13 trades; the risk is negligible, so no further human oversight is needed for the agent</t>
+  </si>
+  <si>
+    <t>Up to 200 trades; the risk is manipulation of the traders, so disclosure of the agent's purpose is the best control</t>
+  </si>
+  <si>
+    <t>Between reviews the agent can execute 200 x 15 = 3,000 trades. Higher autonomy increases risk because errors propagate further before human intervention, so meaningful oversight checkpoints, tighter intervals or limits on exposure reduce it.</t>
+  </si>
+  <si>
+    <t>Which monitoring approach is best suited to detecting a well-being risk from an AI companion app, as opposed to an acute safety risk?</t>
+  </si>
+  <si>
+    <t>A single pre-launch crash test, since well-being harms are fully determined at the design stage</t>
+  </si>
+  <si>
+    <t>Quarterly financial audits, since psychological effects show up in revenue before users notice them</t>
+  </si>
+  <si>
+    <t>A real-time incident hotline, since well-being harms appear as discrete accidents with clear timing</t>
+  </si>
+  <si>
+    <t>Longitudinal tracking of user outcomes, such as usage and reliance, since the harm builds gradually</t>
+  </si>
+  <si>
+    <t>Safety risks are often acute, direct incidents, whereas well-being risks are broader and longer-term, developing gradually and being harder to detect (for example addictive engagement or erosion of critical thinking). Detecting them needs tracking over time rather than incident-based tools.</t>
+  </si>
+  <si>
+    <t>Consider (1) proactive disclosure that AI is used; (2) robust pre-deployment testing with ongoing monitoring; (3) human oversight of high-stakes decisions with fairness testing. Which type of criticism is each mainly designed to address?</t>
+  </si>
+  <si>
+    <t>(1) competence criticism; (2) transparency criticism; (3) ethical criticism</t>
+  </si>
+  <si>
+    <t>(1) transparency criticism; (2) competence criticism; (3) ethical criticism</t>
+  </si>
+  <si>
+    <t>(1) ethical criticism; (2) competence criticism; (3) transparency criticism</t>
+  </si>
+  <si>
+    <t>(1) transparency criticism; (2) ethical criticism; (3) competence criticism</t>
+  </si>
+  <si>
+    <t>Disclosure addresses stakeholders feeling misled (transparency criticism). Testing and monitoring address AI that does not work well (competence criticism). Human oversight and fairness testing address unfair or harmful outcomes (ethical criticism).</t>
+  </si>
+  <si>
+    <t>Which feature most distinguishes existential risk from the global-level risks in the book?</t>
+  </si>
+  <si>
+    <t>Scale and immediacy: civilizational, low-probability outcomes tied to advanced AI, versus risks already visible</t>
+  </si>
+  <si>
+    <t>Existential risk is already occurring through current labor-market displacement, whereas global risks are speculative</t>
+  </si>
+  <si>
+    <t>Existential risk is limited to one organization's operations, whereas global risks extend beyond individual firms</t>
+  </si>
+  <si>
+    <t>Existential risk is settled and imminent, whereas global risks are contested among researchers and policymakers</t>
+  </si>
+  <si>
+    <t>Existential risk is the most extreme, civilizational-scale category: contested, low-probability but catastrophic, and tied to sufficiently advanced AI capability rather than current systems. Global risks such as economic displacement, inequality, misinformation and surveillance are closer and already visible.</t>
+  </si>
+  <si>
+    <t>Why do global-level AI risks need more than organization-level controls?</t>
+  </si>
+  <si>
+    <t>They are the same as individual model risks, only counted across a larger number of customers</t>
+  </si>
+  <si>
+    <t>They concern only data-governance failures within one organization, so internal audit alone would be sufficient</t>
+  </si>
+  <si>
+    <t>They arise only from firms that adopt AI too quickly, so slower adoption by each firm would remove them</t>
+  </si>
+  <si>
+    <t>They extend beyond one organization to economies and societies, so firm controls alone cannot suffice</t>
+  </si>
+  <si>
+    <t>The global-level categories (economic risk, global inequality, misinformation campaigns, privacy and surveillance) extend beyond any single organization to affect economies, societies and populations, so organizational controls are necessary but not sufficient.</t>
+  </si>
+  <si>
+    <t>An LLM coding assistant reproduces proprietary code from a competitor's repository, and engineers paste it into the bank's product. Which risk category applies and what mitigates it?</t>
+  </si>
+  <si>
+    <t>Data and information risk (IP infringement), mitigated by provenance checks, usage policies and review of outputs</t>
+  </si>
+  <si>
+    <t>Functional risk (hallucination), mitigated by raising the temperature so that the model produces more varied code</t>
+  </si>
+  <si>
+    <t>Societal risk (disinformation), mitigated by watermarking, which prevents proprietary code from being reproduced</t>
+  </si>
+  <si>
+    <t>Strategic risk (falling behind competitors), mitigated by adopting more assistants across all development teams</t>
+  </si>
+  <si>
+    <t>Data and information risk covers leakage of confidential information and IP infringement. Controls include checking provenance and the legal right to use outputs, policies on use, and human review. Hallucination is functional risk and disinformation is societal risk.</t>
+  </si>
+  <si>
+    <t>A GenAI letter generator produces a wrong fact in 2% of its outputs and writes 50,000 letters a month. What is the expected number of erroneous letters and which control fits best?</t>
+  </si>
+  <si>
+    <t>About 1,000 a month; functional risk, mitigated by validation, testing and human review of outputs</t>
+  </si>
+  <si>
+    <t>About 100 a month; functional risk, mitigated by validation, testing and human review of outputs</t>
+  </si>
+  <si>
+    <t>About 10,000 a month; strategic risk, mitigated by launching the tool across more of the business lines</t>
+  </si>
+  <si>
+    <t>About 1,000 a month; societal risk, mitigated by watermarking and usage logging of the generated letters</t>
+  </si>
+  <si>
+    <t>Expected errors = 0.02 x 50,000 = 1,000 letters a month. Hallucination and inconsistent outputs are functional risks, mitigated by validation, testing and human review. Other categories (data and information, organizational, strategic, societal) need different mitigations.</t>
+  </si>
+  <si>
+    <t>Consider (1) judging whether using insurance claims data for credit pricing respects the context in which it was shared; (2) setting approval and validation for a material model change; (3) naming the type of criticism a failing chatbot attracts. Which module is the best home for each?</t>
+  </si>
+  <si>
+    <t>(1) Module 4; (2) Module 3; (3) Module 5</t>
+  </si>
+  <si>
+    <t>(1) Module 3; (2) Module 5; (3) Module 4</t>
+  </si>
+  <si>
+    <t>(1) Module 5; (2) Module 4; (3) Module 3</t>
+  </si>
+  <si>
+    <t>(1) Module 4; (2) Module 5; (3) Module 3</t>
+  </si>
+  <si>
+    <t>Contextual integrity is a privacy practice in Module 4 (responsible and ethical AI). Change management and validation are Module 5 (data and model governance). The types of reputational criticism (ethical, competence, transparency) belong to the Module 3 risk taxonomy.</t>
+  </si>
+  <si>
+    <t>Which task best illustrates practical ethics as the book defines it?</t>
+  </si>
+  <si>
+    <t>Determining whether moral statements can be true or false in an absolute sense, independent of any real situation</t>
+  </si>
+  <si>
+    <t>Proving which single ethical theory is correct for all time, so that every future dilemma can be settled mechanically</t>
+  </si>
+  <si>
+    <t>Describing how people actually behave when they face moral dilemmas, without recommending what they should do</t>
+  </si>
+  <si>
+    <t>Developing guidance on how a hiring algorithm should balance candidates' interests in a way justifiable to society</t>
+  </si>
+  <si>
+    <t>Practical ethics applies ethical theory and develops good practices to solve real-world moral dilemmas, aiming at concrete guidance for decisions that someone may lose out from and that should be justifiable to society. It is applied, not purely abstract or descriptive.</t>
+  </si>
+  <si>
+    <t>A committee wants a measurable metric that aggregates benefits and harms for all affected parties to compare AI deployment options. Which framework offers this, and what is the main caveat?</t>
+  </si>
+  <si>
+    <t>Deontology, though duties cannot be ranked, so no deployment option can be compared with any other</t>
+  </si>
+  <si>
+    <t>Rule consequentialism, though the rules always produce identical outcomes for every deployment option</t>
+  </si>
+  <si>
+    <t>Virtue ethics, though the character of an organization cannot be observed, so no metric of benefit is possible</t>
+  </si>
+  <si>
+    <t>Consequentialism, though its metrics can be subjective, hard to quantify and uncertain, and may override rights</t>
+  </si>
+  <si>
+    <t>Consequentialism (utilitarianism) judges actions by outcomes and offers a potentially quantifiable metric. Challenges include subjective metrics, difficulty quantifying value, uncertainty about consequences, and the possibility of justifying actions that violate individual rights.</t>
+  </si>
+  <si>
+    <t>A utilitarian analysis favors a model that raises efficiency by 5% while denying a small minority, but a deontological analysis forbids it. What does the book's approach suggest the committee should do?</t>
+  </si>
+  <si>
+    <t>Adopt the deontological result, since duties always outrank outcomes in every practical ethics decision</t>
+  </si>
+  <si>
+    <t>Adopt the utilitarian result, since it is the only framework that can produce a quantified comparison</t>
+  </si>
+  <si>
+    <t>Use the frameworks together, surface the conflict, weigh rights and outcomes, and justify the trade-off</t>
+  </si>
+  <si>
+    <t>Defer to the framework the model developers know best, since the frameworks are mutually exclusive</t>
+  </si>
+  <si>
+    <t>The book notes that the three frameworks are not mutually exclusive and that practical ethics is pluralistic, able to blend frameworks. Where they conflict, the committee should make the conflict explicit and justify the compromise, since decisions should be justifiable to society.</t>
+  </si>
+  <si>
+    <t>An analyst proposes breaching a data-use rule once to catch a fraud ring, arguing that the net outcome is positive. How do act utilitarianism and rule consequentialism respond?</t>
+  </si>
+  <si>
+    <t>Act utilitarianism rejects it because rules are absolute; rule consequentialism approves each case separately</t>
+  </si>
+  <si>
+    <t>Both approve the breach, since the two frameworks differ only in terminology and not in substance</t>
+  </si>
+  <si>
+    <t>Act utilitarianism may approve on net benefit; rule consequentialism, judging the rule, likely rejects</t>
+  </si>
+  <si>
+    <t>Both reject the breach, since neither framework permits any calculation of benefits and harms</t>
+  </si>
+  <si>
+    <t>Utilitarianism seeks the greatest net utility, evaluating each act by its consequences. Rule consequentialism evaluates acts by whether they follow rules that tend to maximize utility, so a one-off breach that undermines a generally beneficial rule is likely to be rejected.</t>
+  </si>
+  <si>
+    <t>A credit analyst is asked to decide alone whether to use social-media data in lending, which raises privacy, fairness and consumer-harm questions. Which lesson from medical ethics is most relevant?</t>
+  </si>
+  <si>
+    <t>Ethics committees are needed only after harm has occurred, so the analyst should wait for evidence</t>
+  </si>
+  <si>
+    <t>Technical skill is not ethical analysis; medicine uses formal standards, specialists and institutional review</t>
+  </si>
+  <si>
+    <t>Medicine resolves its dilemmas using technical staff alone, so the analyst should do likewise</t>
+  </si>
+  <si>
+    <t>The Hippocratic Oath is a binding legal rulebook, so the analyst's individual judgment is sufficient</t>
+  </si>
+  <si>
+    <t>Medical ethics shows why resolving dilemmas should not rest solely on technical professionals, whose expertise is not necessarily ethical analysis, and it illustrates the value of formal standards, specialized expertise and institutional review structures for high-stakes technology.</t>
+  </si>
+  <si>
+    <t>Which practice most clearly undermines autonomy?</t>
+  </si>
+  <si>
+    <t>A notice that tells customers how to withdraw consent and request deletion of their data at any time</t>
+  </si>
+  <si>
+    <t>A discount offered to customers who knowingly choose to share additional data after a clear explanation</t>
+  </si>
+  <si>
+    <t>A consent screen that explains each data use plainly and lets customers decline without any penalty</t>
+  </si>
+  <si>
+    <t>A consent screen with pre-ticked boxes and misleading wording, so customers agree without realizing</t>
+  </si>
+  <si>
+    <t>Autonomy is the capacity and right to make informed, uncoerced decisions. Coercion, deception, manipulation and undue influence undermine it, and ethical AI should support people's own goals. Pre-ticked boxes with misleading wording obtain agreement through deception.</t>
+  </si>
+  <si>
+    <t>A bank's chatbot repeatedly speaks dismissively to declined applicants and refuses to give any reasons. Which form of justice is most directly at stake?</t>
+  </si>
+  <si>
+    <t>Restorative justice, which concerns repairing the harm after a wrong has been committed</t>
+  </si>
+  <si>
+    <t>Social justice, which concerns the fairness of society's overall structures and institutions</t>
+  </si>
+  <si>
+    <t>Distributive justice, which concerns how benefits and burdens are allocated among applicants</t>
+  </si>
+  <si>
+    <t>Interactional justice, which concerns respectful and informative treatment during the process</t>
+  </si>
+  <si>
+    <t>Justice includes procedural, distributive, restorative, interactional and social forms. Interactional justice concerns whether people are treated with respect and given adequate information during a process.</t>
+  </si>
+  <si>
+    <t>Consider (1) a bank proactively alerts customers at risk of fraud; (2) a bank withholds a model after tests show it could cause disproportionate harm. Which principles are primarily at work?</t>
+  </si>
+  <si>
+    <t>(1) explainability; (2) autonomy</t>
+  </si>
+  <si>
+    <t>(1) beneficence; (2) nonmaleficence</t>
+  </si>
+  <si>
+    <t>(1) autonomy; (2) justice</t>
+  </si>
+  <si>
+    <t>(1) nonmaleficence; (2) beneficence</t>
+  </si>
+  <si>
+    <t>Beneficence is the positive obligation to benefit others and advance welfare (proactively protecting customers). Nonmaleficence is the obligation to avoid harming others and avoid unjustified or disproportionate risks (withholding a model that could cause such harm).</t>
+  </si>
+  <si>
+    <t>Consider (1) a declined applicant asks what to change to be approved; (2) a regulator asks how the model behaves overall; (3) an auditor tests an explanation method that works on any model. Which explanation types fit?</t>
+  </si>
+  <si>
+    <t>(1) global; (2) counterfactual; (3) model-agnostic</t>
+  </si>
+  <si>
+    <t>(1) counterfactual; (2) global; (3) model-agnostic</t>
+  </si>
+  <si>
+    <t>(1) counterfactual; (2) model-specific; (3) global</t>
+  </si>
+  <si>
+    <t>(1) local; (2) model-agnostic; (3) counterfactual</t>
+  </si>
+  <si>
+    <t>Counterfactual explanations show what would need to change for a different outcome. Global explanations describe overall model behavior (versus local ones for a single decision), and model-agnostic methods can be applied to any model (versus model-specific ones).</t>
+  </si>
+  <si>
+    <t>A fitness-linked insurance model is trained on data from voluntary wearable users, who are younger and healthier than the insured population. Which source of bias is this?</t>
+  </si>
+  <si>
+    <t>Selective labels, since only the outcomes of decisions that were actually made are recorded</t>
+  </si>
+  <si>
+    <t>Sampling bias, since a non-random sample may not generalize to the population</t>
+  </si>
+  <si>
+    <t>Historical bias, since the data reflect past discriminatory decisions by human underwriters</t>
+  </si>
+  <si>
+    <t>Problem-specification bias, since the target variable poorly captures the real-world objective</t>
+  </si>
+  <si>
+    <t>Data bias includes historical bias, selective labels and sampling bias. Training on a self-selected, non-random sample whose members differ from the target population creates sampling bias.</t>
+  </si>
+  <si>
+    <t>Model 1 has overall accuracy of 91.5% (Group A 96%, Group B 66%); Model 2 has 88.8% (Group A 90%, Group B 82%). A team picks the model with higher overall accuracy. Which statement is correct?</t>
+  </si>
+  <si>
+    <t>Aggregate accuracy hides a 30-point versus 8-point subgroup gap; model selection can introduce bias</t>
+  </si>
+  <si>
+    <t>Model 2 is clearly unfair, since its accuracy for Group A is lower than that of Model 1</t>
+  </si>
+  <si>
+    <t>Model 1 is clearly the fairer choice, since its overall accuracy is higher than that of Model 2</t>
+  </si>
+  <si>
+    <t>The subgroup gaps are irrelevant, since fairness is assessed only through overall accuracy</t>
+  </si>
+  <si>
+    <t>The book notes that modeling choices such as optimization functions and model selection can introduce bias. Model 1 is better overall but has a 30-point accuracy gap between groups, whereas Model 2 has an 8-point gap; choosing on the aggregate metric alone ignores this.</t>
+  </si>
+  <si>
+    <t>Consider (1) the board cannot assess AI risk; (2) outputs are never reviewed by an independent party; (3) minority groups are underrepresented in the training data. Which mitigation tools fit each?</t>
+  </si>
+  <si>
+    <t>(1) diverse, representative or synthetic data; (2) algorithmic auditing; (3) training for boards and the C-suite</t>
+  </si>
+  <si>
+    <t>(1) training for boards and the C-suite; (2) diverse, representative or synthetic data; (3) algorithmic auditing</t>
+  </si>
+  <si>
+    <t>(1) training for boards and the C-suite; (2) algorithmic auditing; (3) diverse, representative or synthetic data</t>
+  </si>
+  <si>
+    <t>(1) algorithmic auditing; (2) training for boards and the C-suite; (3) diverse, representative or synthetic data</t>
+  </si>
+  <si>
+    <t>The book lists mitigation tools including technological fairness tools and audits, high-quality, diverse, updated and representative data, synthetic data where appropriate, algorithmic auditing, ethics committees and training for boards and the C-suite.</t>
+  </si>
+  <si>
+    <t>Consider (1) a customer withdraws consent for marketing use of her data; (2) a bank reuses medical-expense data from insurance claims for credit scoring; (3) a system purges transaction logs after the retention period. Which privacy practices apply?</t>
+  </si>
+  <si>
+    <t>(1) contextual integrity; (2) data deletion; (3) control over data</t>
+  </si>
+  <si>
+    <t>(1) control over data; (2) contextual integrity; (3) data deletion</t>
+  </si>
+  <si>
+    <t>(1) control over data; (2) data minimization; (3) data security</t>
+  </si>
+  <si>
+    <t>(1) data minimization; (2) control over data; (3) contextual integrity</t>
+  </si>
+  <si>
+    <t>Control over data includes the ability to deny or withdraw consent. Contextual integrity means data use should respect the norms of the context in which it was provided. Data should be deleted when no longer necessary.</t>
+  </si>
+  <si>
+    <t>A bank keeps application files for rejected applicants for eight years 'just in case'. Which privacy practices does this conflict with?</t>
+  </si>
+  <si>
+    <t>Contextual integrity only, since retention concerns solely the context in which data were first provided</t>
+  </si>
+  <si>
+    <t>Data minimization and data deletion, since data should be kept only as needed and then deleted</t>
+  </si>
+  <si>
+    <t>The right to privacy only, since retention is lawful whenever the stored data are encrypted</t>
+  </si>
+  <si>
+    <t>Differential privacy only, since retention is addressed by adding noise to the stored records</t>
+  </si>
+  <si>
+    <t>Data minimization means collecting only what is necessary for a specific purpose, and data should be deleted when no longer necessary. Indefinite retention for hypothetical future use conflicts with both, and encryption does not remove those obligations.</t>
+  </si>
+  <si>
+    <t>Which statement about regulatory gaps is consistent with the book?</t>
+  </si>
+  <si>
+    <t>Gaps are hard to close because AI is international, despite the European AI Office and global moves</t>
+  </si>
+  <si>
+    <t>The European AI Office has made international coordination unnecessary for any AI regulation</t>
+  </si>
+  <si>
+    <t>Gaps are easily closed, since national laws automatically apply to models that were trained abroad</t>
+  </si>
+  <si>
+    <t>Gaps matter only to US firms, because the EU already regulates every aspect of AI comprehensively</t>
+  </si>
+  <si>
+    <t>Lack of national and international regulation is a governance challenge, difficult because AI is international. The book notes the European AI Office and anticipates movement toward international regulation or agreed best practices.</t>
+  </si>
+  <si>
+    <t>An LLM chatbot states that a named executive was convicted of fraud, which is false. Which governance challenge is most directly illustrated?</t>
+  </si>
+  <si>
+    <t>Power asymmetries: the executive has less wealth and influence than the technology company</t>
+  </si>
+  <si>
+    <t>Lack of transparency: the developer has not disclosed the training data or the safety-tuning process</t>
+  </si>
+  <si>
+    <t>Lack of regulation: LLM statements about individuals are illegal by definition in all jurisdictions</t>
+  </si>
+  <si>
+    <t>Lack of truth-tracking: LLMs give plausible answers, creating misinformation and libel risks</t>
+  </si>
+  <si>
+    <t>LLMs do not track truth in the way a truth-based knowledge system would; they generate plausible responses, which can create misinformation, safety, libel and other governance risks.</t>
+  </si>
+  <si>
+    <t>A business practice is legal but exploits customers' inability to understand a product. Which statement is most consistent with the book?</t>
+  </si>
+  <si>
+    <t>Law sets enforceable minimums while ethics is broader, so a legal practice can still be unethical</t>
+  </si>
+  <si>
+    <t>Ethics matters only where no law exists, so legality ends the discussion about the practice</t>
+  </si>
+  <si>
+    <t>If a practice is legal then it is ethical, since ethics and law cover exactly the same ground</t>
+  </si>
+  <si>
+    <t>Ethics sets the enforceable minimums, while law covers the broader moral questions in society</t>
+  </si>
+  <si>
+    <t>The book states that ethics complements law: law generally establishes minimum enforceable requirements, while ethics is broader and helps identify moral issues, assess justice and envision desirable forms of social life.</t>
+  </si>
+  <si>
+    <t>Which statement about the United States regulatory landscape is consistent with the book?</t>
+  </si>
+  <si>
+    <t>State laws such as the CCPA apply only to federal agencies, while NIST sets binding AI licensing rules</t>
+  </si>
+  <si>
+    <t>No comprehensive federal privacy law exists, state laws are a patchwork, and the NIST AI RMF is voluntary</t>
+  </si>
+  <si>
+    <t>A comprehensive federal privacy law replaced the state laws in 2021, and the NIST AI framework is mandatory</t>
+  </si>
+  <si>
+    <t>HIPAA is the comprehensive privacy law for all personal data, and state privacy laws are unenforceable</t>
+  </si>
+  <si>
+    <t>The book describes no comprehensive federal privacy law and a patchwork of state rules (for example California's CCPA and Illinois' BIPA), with HIPAA protecting health information. NIST's 2023 AI Risk Management Framework is voluntary, with the functions Govern, Map, Measure and Manage.</t>
+  </si>
+  <si>
+    <t>A junior analyst has read access to full customer PII although her task needs only aggregated balances. Which principle is breached?</t>
+  </si>
+  <si>
+    <t>Data classification, which requires separating quantitative from qualitative data</t>
+  </si>
+  <si>
+    <t>Data quality, which requires accuracy, consistency and integrity of the data</t>
+  </si>
+  <si>
+    <t>Data provenance, which requires evidence of the legal right to use the data</t>
+  </si>
+  <si>
+    <t>Access should match legitimate permission and need, with controls such as encryption</t>
+  </si>
+  <si>
+    <t>Data protection and security include safeguarding access, privacy and confidentiality; access must match legitimate permission and need, with controls such as encryption. Granting full PII access for an aggregate task breaches that principle.</t>
+  </si>
+  <si>
+    <t>Errors in model scores are traced to a table, but no one can identify its source system, definitions or how its fields map to upstream systems. Which gap does this show?</t>
+  </si>
+  <si>
+    <t>Missing metadata on origin, definitions, structures and mappings, which supports lineage and control</t>
+  </si>
+  <si>
+    <t>Missing synthetic data, which should replace any table whose source is unknown to the team</t>
+  </si>
+  <si>
+    <t>Missing retention policy, which should delete every table whose source system is unknown</t>
+  </si>
+  <si>
+    <t>Missing model-inventory attributes, which record the model's validation dates and approvals</t>
+  </si>
+  <si>
+    <t>Metadata (descriptive, structural, administrative, reference or statistical) should cover origin, definitions, structures, mappings, relationships and processes. Without it, the source and meaning of data cannot be traced or controlled.</t>
+  </si>
+  <si>
+    <t>A bank buys a one-off alternative data set for a stress test, while another team subscribes to a recurring feed. Which statement is most consistent with the book?</t>
+  </si>
+  <si>
+    <t>Alternative data should be treated as traditional data, since providers never change definitions or streams</t>
+  </si>
+  <si>
+    <t>Only the recurring feed needs authorization for non-public personal information; one-off data are exempt</t>
+  </si>
+  <si>
+    <t>The strategy should set single or recurring use, source and controls; recurring feeds need ongoing scrutiny</t>
+  </si>
+  <si>
+    <t>Single versus recurring use is irrelevant, since alternative data need no extra scrutiny once purchased</t>
+  </si>
+  <si>
+    <t>The data strategy should define vision, goals, priorities, authorization for non-public personal information, intended single or recurring use, source and controls for alternative data. Alternative data needs extra scrutiny because providers may change definitions and streams can disappear or become biased.</t>
+  </si>
+  <si>
+    <t>A bank applies one validation standard to every model, regardless of materiality or complexity. According to the book, which element is missing from its policy?</t>
+  </si>
+  <si>
+    <t>A rule that models may be used only when their owners are also the validators of the same models</t>
+  </si>
+  <si>
+    <t>A single universal acceptance threshold that applies identically to each model whatever its materiality</t>
+  </si>
+  <si>
+    <t>Risk tiers tied to a defined model-risk appetite, so that validation and monitoring scale with risk</t>
+  </si>
+  <si>
+    <t>A requirement that all models be built in-house so that vendor risk can never arise</t>
+  </si>
+  <si>
+    <t>Model-governance policies should define a model versus an end-user tool, define model risk, establish risk tiers, define validation, document risk appetite and set documentation and monitoring standards. Validation intensity should be risk-based.</t>
+  </si>
+  <si>
+    <t>A senior manager rejects a model because 'it does not capture every feature of reality'. Which response is most consistent with the book?</t>
+  </si>
+  <si>
+    <t>Validation is meant to prove a model correct, so any unmodeled feature shows that validation failed</t>
+  </si>
+  <si>
+    <t>Simplification is a defect that governance should remove by adding features until residual risk is zero</t>
+  </si>
+  <si>
+    <t>A model simplifies reality, and its usefulness depends on fitness for purpose rather than perfection</t>
+  </si>
+  <si>
+    <t>A model is valid only if it replicates reality exactly, so the manager is right to reject it</t>
+  </si>
+  <si>
+    <t>The book defines a model as a simplified representation or abstraction of reality, and notes that usefulness and validity are not identical. Validation is an attempt to find weaknesses, not proof of a perfect model.</t>
+  </si>
+  <si>
+    <t>Management receives a single risk number with no information on the scenario set or assumptions behind it. Which governance consideration is most directly relevant?</t>
+  </si>
+  <si>
+    <t>Feedback effects, since publishing the number necessarily changes how market participants behave afterwards</t>
+  </si>
+  <si>
+    <t>Transparent communication of assumptions and incomplete scenario sets, so users see what is excluded</t>
+  </si>
+  <si>
+    <t>Overfitting, since the number was estimated only on the training sample and not on any holdout data</t>
+  </si>
+  <si>
+    <t>Data leakage, since the scenarios were drawn from the test data set rather than from the history</t>
+  </si>
+  <si>
+    <t>Risk-model thinking has three elements (quantity of interest, scenarios with weights, risk measure), and governance must consider incomplete scenario sets, feedback effects and transparent communication of assumptions.</t>
+  </si>
+  <si>
+    <t>Two models have equal materiality and exposure. P is a logistic scorecard on 20,000 rows of structured data, recalibrated annually; Q is a deep network on unstructured data, recalibrated weekly. How should they rank?</t>
+  </si>
+  <si>
+    <t>They rank equally, since materiality and exposure alone determine the model-risk ranking of models</t>
+  </si>
+  <si>
+    <t>Q ranks higher, since AI/ML assessment weights complexity, data, output type and recalibration</t>
+  </si>
+  <si>
+    <t>Q ranks lower, since frequent recalibration reduces model risk to zero in practice for all models</t>
+  </si>
+  <si>
+    <t>P ranks higher, since simpler models always carry greater model risk than more complex models do</t>
+  </si>
+  <si>
+    <t>The inventory assessment for AI/ML gives extra weight to methodology and design complexity, data volume, structure and quality, output type, recalibration needs and model-risk ranking. Materiality, complexity and exposure are key ranking factors.</t>
+  </si>
+  <si>
+    <t>A model is tested only for in-sample accuracy before approval. Which testing dimensions from the book are missing?</t>
+  </si>
+  <si>
+    <t>Only acceptance testing, since robustness and stability are validated by the board</t>
+  </si>
+  <si>
+    <t>Nothing, since accuracy alone demonstrates sound design, theory and data relevance</t>
+  </si>
+  <si>
+    <t>Robustness, stability, limitations, assumptions and judgmental elements, as well as accuracy</t>
+  </si>
+  <si>
+    <t>Only vendor contract terms, since development testing covers legal conditions rather than model behavior</t>
+  </si>
+  <si>
+    <t>Sound development requires a clear purpose, sound design, theory and logic, robust methodology, rigorous data-quality assessment, documentation, and testing of accuracy, robustness, stability, limitations, assumptions and qualitative or judgmental elements.</t>
+  </si>
+  <si>
+    <t>A new credit-decision engine will run for three months alongside the old engine without affecting live decisions. What is the main benefit?</t>
+  </si>
+  <si>
+    <t>It removes the need to document limitations, since users will observe them directly in operation</t>
+  </si>
+  <si>
+    <t>It can expose bugs and behaviors that real users or live data trigger before the bank relies on it</t>
+  </si>
+  <si>
+    <t>It replaces independent validation, since parallel results prove the conceptual soundness of the model</t>
+  </si>
+  <si>
+    <t>It guarantees unbiased outputs, since two engines are being compared on the same applications</t>
+  </si>
+  <si>
+    <t>Beta or parallel-to-production periods can expose additional bugs that users may trigger. They complement, but do not replace, validation and documentation of limitations.</t>
+  </si>
+  <si>
+    <t>Junior developers hide known model weaknesses for fear of blame, so reviewers never see them. Which remedy is most consistent with the book's view of a healthy modeling culture?</t>
+  </si>
+  <si>
+    <t>Build awareness, transparency and experience, with open discussion and documentation of limitations</t>
+  </si>
+  <si>
+    <t>Reward developers according to the number of models released, so that weaknesses are fixed later</t>
+  </si>
+  <si>
+    <t>Remove the documentation of limitations so that blame cannot be assigned to individual developers</t>
+  </si>
+  <si>
+    <t>Allow only senior staff to see test results, since weaknesses are best handled by a small group</t>
+  </si>
+  <si>
+    <t>The book emphasizes awareness, transparency and experience as foundations of a healthy modeling culture, along with explicit model limitations and approved-use boundaries.</t>
+  </si>
+  <si>
+    <t>A model change was approved and implemented, but performance monitoring was not updated and no one checked whether objectives still held. What did the book require?</t>
+  </si>
+  <si>
+    <t>Deletion of the old monitoring history, to avoid confusion between versions of the model</t>
+  </si>
+  <si>
+    <t>Controlled implementation with updated monitoring and continued observation of objectives</t>
+  </si>
+  <si>
+    <t>A new initial validation only, since monitoring is unaffected by approved changes to a model</t>
+  </si>
+  <si>
+    <t>No further steps, since approval ends the change-management process for the model</t>
+  </si>
+  <si>
+    <t>If a change is material, change-based validation is scheduled, and approved changes should be implemented in a controlled manner with updated performance monitoring and continued observation of whether objectives and regulatory requirements remain satisfied.</t>
+  </si>
+  <si>
+    <t>A bank validates an AI hiring-screening model using only data scientists. Which gap does the book suggest?</t>
+  </si>
+  <si>
+    <t>The data scientists should be replaced by internal audit, who validate models in the third line</t>
+  </si>
+  <si>
+    <t>Excess scope, since HR and compliance must be excluded to protect validator independence</t>
+  </si>
+  <si>
+    <t>AI/ML validation may need broader stakeholders such as HR, compliance and operational risk</t>
+  </si>
+  <si>
+    <t>None, since validation of AI models is a purely statistical exercise for specialists</t>
+  </si>
+  <si>
+    <t>AI/ML validation may need broader stakeholders such as HR, compliance and operational risk. Black-box contexts increase the importance of explainability, extreme-case assessment, appropriate back-testing and cross-validation, and output reporting.</t>
+  </si>
+  <si>
+    <t>A 99% one-day VaR is back-tested over 250 trading days and shows 9 exceptions, against an expectation of 2.5. What is the best conclusion?</t>
+  </si>
+  <si>
+    <t>The result is uninformative, since back-testing applies only at initial validation</t>
+  </si>
+  <si>
+    <t>Exceptions far above expectation suggest the model understates risk and needs review</t>
+  </si>
+  <si>
+    <t>Fewer than ten exceptions are acceptable for any model, so no action is needed</t>
+  </si>
+  <si>
+    <t>The model is conservative, since more exceptions mean larger estimated losses</t>
+  </si>
+  <si>
+    <t>At 99% confidence, about 1% of 250 days (2.5) should breach VaR. Nine exceptions is far above this, indicating that the model likely understates risk. Appropriately timed back-testing is part of validation scope and applies on an ongoing basis.</t>
+  </si>
+  <si>
+    <t>Validators tested the model in a development sandbox, but the production platform with different access controls was never reviewed. Which point from the book's validation scope is relevant?</t>
+  </si>
+  <si>
+    <t>Expert-judgment overlays, which are excluded from validation scope by definition of the term</t>
+  </si>
+  <si>
+    <t>Parameter stability, which concerns coefficient changes over time, so nothing is missing from the review</t>
+  </si>
+  <si>
+    <t>Outcomes analysis, which compares predictions with realized results, so nothing is missing from the review</t>
+  </si>
+  <si>
+    <t>The implementation platform and access controls are part of validation scope, not only conceptual soundness</t>
+  </si>
+  <si>
+    <t>Validation scope includes data sources, assumptions, conceptual soundness, benchmarks, monitoring plans, documentation, implementation and access controls, implementation platform, outcomes analysis, stress tests, parameter stability and back-testing.</t>
+  </si>
+  <si>
+    <t>A monitoring plan sets KRIs but nobody knows who must act when one breaches its limit. Which element is missing?</t>
+  </si>
+  <si>
+    <t>An escalation procedure assigning responsibility and timing for acting on breaches</t>
+  </si>
+  <si>
+    <t>A challenger model, since KRIs can breach only when a benchmark model is available</t>
+  </si>
+  <si>
+    <t>More frequent initial validation, since KRIs are checked only when a model is first launched</t>
+  </si>
+  <si>
+    <t>A larger training set, since KRIs measure the volume of the data used for development</t>
+  </si>
+  <si>
+    <t>Validation covers monitoring plans, KRIs and escalation. A KRI is useful only if breaches trigger a defined escalation procedure with responsibilities and timing.</t>
+  </si>
+  <si>
+    <t>A firm's model pipeline uses a bespoke exotic system with custom interfaces and suffers frequent outages. Which principle from the book applies?</t>
+  </si>
+  <si>
+    <t>Interfaces should be customized per model, so that failures cannot spread from one model to another</t>
+  </si>
+  <si>
+    <t>More exotic components increase robustness, because diversity protects against any outage</t>
+  </si>
+  <si>
+    <t>Robustness depends only on model accuracy and not on data gathering, processing or reporting</t>
+  </si>
+  <si>
+    <t>Robustness improves when exotic systems are minimized and interfaces are standardized</t>
+  </si>
+  <si>
+    <t>Running models requires reliable data gathering, processing, computation, analysis and reporting. Robustness improves when exotic systems are minimized and interfaces are standardized.</t>
+  </si>
+  <si>
+    <t>Analysts increasingly run a model ad hoc to meet urgent requests, and scheduled runs are now rare. What is the concern?</t>
+  </si>
+  <si>
+    <t>Scheduled runs are riskier, since they cannot be repeated and always require manual intervention</t>
+  </si>
+  <si>
+    <t>Ad hoc runs are always safer, since manual intervention adds an extra layer of review to the outputs</t>
+  </si>
+  <si>
+    <t>Ad hoc use needs knowledgeable staff and controls, and should not replace repeatable scheduled runs</t>
+  </si>
+  <si>
+    <t>Ad hoc runs are exempt from controls, since each run is a one-off and not a production process</t>
+  </si>
+  <si>
+    <t>Scheduled runs provide repeatable, low-manual-intervention operation. Ad hoc runs provide flexibility but need knowledgeable staff and careful controls, so that ad hoc use does not gradually replace controlled scheduled processes.</t>
+  </si>
+  <si>
+    <t>A bank's LLM provider suffers a 12-hour outage, and a critical process stops with no fallback. Which element of AI risk frameworks was missing?</t>
+  </si>
+  <si>
+    <t>Data catalogs, since outages arise from missing metadata about the data used by the model</t>
+  </si>
+  <si>
+    <t>A policy on terms of use only, since outages concern the behavior of users and not providers</t>
+  </si>
+  <si>
+    <t>A hub-and-spoke structure, since outages occur only under decentralized governance</t>
+  </si>
+  <si>
+    <t>Business continuity and incident-response planning, with ongoing monitoring and skills upkeep</t>
+  </si>
+  <si>
+    <t>Risk frameworks should support vulnerability audits, safety evaluation, incident response, business continuity, skills maintenance and ongoing monitoring, often using established frameworks such as the three lines of defense.</t>
+  </si>
+  <si>
+    <t>The bank wants to rehearse its response to a deepfake video of its CEO before one occurs. Which adaptive practice from the book fits best?</t>
+  </si>
+  <si>
+    <t>Usage logging alone, which replaces the need for any rehearsal of the response</t>
+  </si>
+  <si>
+    <t>Watermarking incoming videos, which prevents any deepfake from circulating in the market</t>
+  </si>
+  <si>
+    <t>Scenario planning and tabletop exercises, then updates to policies, training and escalation</t>
+  </si>
+  <si>
+    <t>A one-time approval of the GenAI tool, which is sufficient for any future incident</t>
+  </si>
+  <si>
+    <t>Adaptive practices include continuous monitoring, logs, audits, feedback loops, red-teaming, scenario plans and tabletop exercises, safeguards such as watermarking and usage logging where feasible, and updating policies, training and escalation after incidents.</t>
+  </si>
+  <si>
+    <t>Validators reviewed the algorithm and back-test of a new ML model but not its data pipeline, implementation, monitoring or user documentation. Which principle was ignored?</t>
+  </si>
+  <si>
+    <t>Validation should be end-to-end, since AI/ML affects data, implementation, monitoring and use</t>
+  </si>
+  <si>
+    <t>End-to-end review applies only to GenAI, and never to machine learning models</t>
+  </si>
+  <si>
+    <t>Validation should be limited to the algorithm, since all other items are the first line's responsibility</t>
+  </si>
+  <si>
+    <t>Validation is complete once back-testing passes, since back-testing covers every other component</t>
+  </si>
+  <si>
+    <t>The book notes that validation should be reviewed end-to-end because AI/ML affects not only model design but also data, implementation, monitoring, documentation and use. SR 11-7 remains relevant.</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <charset val="1"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <b/>
@@ -14589,6 +18175,10 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Arial"/>
     </font>
   </fonts>
   <fills count="3">
@@ -14638,35 +18228,43 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal 2" xfId="1" xr:uid="{8F0FC594-B5F4-41F5-BC42-3283666E22CC}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -14928,7 +18526,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I911"/>
+  <dimension ref="A1:I1111"/>
   <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
@@ -17958,7 +21556,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="117" spans="1:8" ht="79.2" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:8" ht="66" x14ac:dyDescent="0.3">
       <c r="A117" s="2" t="s">
         <v>1607</v>
       </c>
@@ -18686,7 +22284,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="145" spans="1:8" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:8" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A145" s="2" t="s">
         <v>1607</v>
       </c>
@@ -18920,7 +22518,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="154" spans="1:8" ht="66" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:8" ht="52.8" x14ac:dyDescent="0.3">
       <c r="A154" s="2" t="s">
         <v>1607</v>
       </c>
@@ -19700,7 +23298,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="184" spans="1:8" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:8" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A184" s="2" t="s">
         <v>1607</v>
       </c>
@@ -23678,7 +27276,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="337" spans="1:8" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="337" spans="1:8" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A337" s="2" t="s">
         <v>1579</v>
       </c>
@@ -24952,7 +28550,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="386" spans="1:8" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="386" spans="1:8" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A386" s="2" t="s">
         <v>1579</v>
       </c>
@@ -25758,7 +29356,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="417" spans="1:8" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="417" spans="1:8" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A417" s="2" t="s">
         <v>1608</v>
       </c>
@@ -27084,7 +30682,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="468" spans="1:8" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="468" spans="1:8" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A468" s="2" t="s">
         <v>1608</v>
       </c>
@@ -27630,7 +31228,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="489" spans="1:8" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="489" spans="1:8" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A489" s="2" t="s">
         <v>1608</v>
       </c>
@@ -28696,7 +32294,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="530" spans="1:8" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="530" spans="1:8" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A530" s="2" t="s">
         <v>1608</v>
       </c>
@@ -30308,7 +33906,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="592" spans="1:8" ht="66" x14ac:dyDescent="0.3">
+    <row r="592" spans="1:8" ht="52.8" x14ac:dyDescent="0.3">
       <c r="A592" s="2" t="s">
         <v>1608</v>
       </c>
@@ -30516,7 +34114,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="600" spans="1:8" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="600" spans="1:8" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A600" s="2" t="s">
         <v>1608</v>
       </c>
@@ -30750,7 +34348,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="609" spans="1:9" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="609" spans="1:9" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A609" s="2" t="s">
         <v>1608</v>
       </c>
@@ -30776,7 +34374,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="610" spans="1:9" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="610" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A610" s="2" t="s">
         <v>1608</v>
       </c>
@@ -35149,7 +38747,7 @@
         <v>4147</v>
       </c>
     </row>
-    <row r="761" spans="1:9" ht="72" x14ac:dyDescent="0.3">
+    <row r="761" spans="1:9" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A761" s="5" t="s">
         <v>3744</v>
       </c>
@@ -37005,7 +40603,7 @@
         <v>4281</v>
       </c>
     </row>
-    <row r="825" spans="1:9" ht="72" x14ac:dyDescent="0.3">
+    <row r="825" spans="1:9" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A825" s="5" t="s">
         <v>4831</v>
       </c>
@@ -38397,7 +41995,7 @@
         <v>4577</v>
       </c>
     </row>
-    <row r="873" spans="1:9" ht="72" x14ac:dyDescent="0.3">
+    <row r="873" spans="1:9" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A873" s="5" t="s">
         <v>4832</v>
       </c>
@@ -38890,7 +42488,7 @@
         <v>4687</v>
       </c>
     </row>
-    <row r="890" spans="1:9" ht="72" x14ac:dyDescent="0.3">
+    <row r="890" spans="1:9" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A890" s="5" t="s">
         <v>4833</v>
       </c>
@@ -38948,7 +42546,7 @@
         <v>4700</v>
       </c>
     </row>
-    <row r="892" spans="1:9" ht="72" x14ac:dyDescent="0.3">
+    <row r="892" spans="1:9" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A892" s="5" t="s">
         <v>4834</v>
       </c>
@@ -38977,7 +42575,7 @@
         <v>4707</v>
       </c>
     </row>
-    <row r="893" spans="1:9" ht="72" x14ac:dyDescent="0.3">
+    <row r="893" spans="1:9" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A893" s="5" t="s">
         <v>4834</v>
       </c>
@@ -39526,6 +43124,5806 @@
       </c>
       <c r="I911" s="7" t="s">
         <v>4829</v>
+      </c>
+    </row>
+    <row r="912" spans="1:9" ht="69" x14ac:dyDescent="0.3">
+      <c r="A912" s="5" t="s">
+        <v>5423</v>
+      </c>
+      <c r="B912" s="8" t="s">
+        <v>4199</v>
+      </c>
+      <c r="C912" s="8" t="s">
+        <v>4835</v>
+      </c>
+      <c r="D912" s="8" t="s">
+        <v>4836</v>
+      </c>
+      <c r="E912" s="8" t="s">
+        <v>4837</v>
+      </c>
+      <c r="F912" s="8" t="s">
+        <v>4838</v>
+      </c>
+      <c r="G912" s="8" t="s">
+        <v>4839</v>
+      </c>
+      <c r="H912" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="I912" s="8" t="s">
+        <v>4840</v>
+      </c>
+    </row>
+    <row r="913" spans="1:9" ht="82.8" x14ac:dyDescent="0.3">
+      <c r="A913" s="5" t="s">
+        <v>5423</v>
+      </c>
+      <c r="B913" s="8" t="s">
+        <v>4199</v>
+      </c>
+      <c r="C913" s="8" t="s">
+        <v>4841</v>
+      </c>
+      <c r="D913" s="8" t="s">
+        <v>4842</v>
+      </c>
+      <c r="E913" s="8" t="s">
+        <v>4843</v>
+      </c>
+      <c r="F913" s="8" t="s">
+        <v>4844</v>
+      </c>
+      <c r="G913" s="8" t="s">
+        <v>4845</v>
+      </c>
+      <c r="H913" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I913" s="8" t="s">
+        <v>4846</v>
+      </c>
+    </row>
+    <row r="914" spans="1:9" ht="69" x14ac:dyDescent="0.3">
+      <c r="A914" s="5" t="s">
+        <v>5423</v>
+      </c>
+      <c r="B914" s="8" t="s">
+        <v>4212</v>
+      </c>
+      <c r="C914" s="8" t="s">
+        <v>4847</v>
+      </c>
+      <c r="D914" s="8" t="s">
+        <v>4848</v>
+      </c>
+      <c r="E914" s="8" t="s">
+        <v>4849</v>
+      </c>
+      <c r="F914" s="8" t="s">
+        <v>3663</v>
+      </c>
+      <c r="G914" s="8" t="s">
+        <v>3662</v>
+      </c>
+      <c r="H914" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="I914" s="8" t="s">
+        <v>4850</v>
+      </c>
+    </row>
+    <row r="915" spans="1:9" ht="69" x14ac:dyDescent="0.3">
+      <c r="A915" s="5" t="s">
+        <v>5423</v>
+      </c>
+      <c r="B915" s="8" t="s">
+        <v>4212</v>
+      </c>
+      <c r="C915" s="8" t="s">
+        <v>4851</v>
+      </c>
+      <c r="D915" s="8" t="s">
+        <v>4852</v>
+      </c>
+      <c r="E915" s="8" t="s">
+        <v>4853</v>
+      </c>
+      <c r="F915" s="8" t="s">
+        <v>4854</v>
+      </c>
+      <c r="G915" s="8" t="s">
+        <v>4855</v>
+      </c>
+      <c r="H915" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="I915" s="8" t="s">
+        <v>4856</v>
+      </c>
+    </row>
+    <row r="916" spans="1:9" ht="69" x14ac:dyDescent="0.3">
+      <c r="A916" s="5" t="s">
+        <v>5423</v>
+      </c>
+      <c r="B916" s="8" t="s">
+        <v>4225</v>
+      </c>
+      <c r="C916" s="8" t="s">
+        <v>4857</v>
+      </c>
+      <c r="D916" s="8" t="s">
+        <v>4858</v>
+      </c>
+      <c r="E916" s="8" t="s">
+        <v>4859</v>
+      </c>
+      <c r="F916" s="8" t="s">
+        <v>4860</v>
+      </c>
+      <c r="G916" s="8" t="s">
+        <v>4861</v>
+      </c>
+      <c r="H916" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I916" s="8" t="s">
+        <v>4862</v>
+      </c>
+    </row>
+    <row r="917" spans="1:9" ht="82.8" x14ac:dyDescent="0.3">
+      <c r="A917" s="5" t="s">
+        <v>5423</v>
+      </c>
+      <c r="B917" s="8" t="s">
+        <v>4225</v>
+      </c>
+      <c r="C917" s="8" t="s">
+        <v>4863</v>
+      </c>
+      <c r="D917" s="8" t="s">
+        <v>4864</v>
+      </c>
+      <c r="E917" s="8" t="s">
+        <v>4865</v>
+      </c>
+      <c r="F917" s="8" t="s">
+        <v>4866</v>
+      </c>
+      <c r="G917" s="8" t="s">
+        <v>4867</v>
+      </c>
+      <c r="H917" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="I917" s="8" t="s">
+        <v>4868</v>
+      </c>
+    </row>
+    <row r="918" spans="1:9" ht="69" x14ac:dyDescent="0.3">
+      <c r="A918" s="5" t="s">
+        <v>5424</v>
+      </c>
+      <c r="B918" s="8" t="s">
+        <v>4238</v>
+      </c>
+      <c r="C918" s="8" t="s">
+        <v>4869</v>
+      </c>
+      <c r="D918" s="8" t="s">
+        <v>4870</v>
+      </c>
+      <c r="E918" s="8" t="s">
+        <v>4871</v>
+      </c>
+      <c r="F918" s="8" t="s">
+        <v>4872</v>
+      </c>
+      <c r="G918" s="8" t="s">
+        <v>4873</v>
+      </c>
+      <c r="H918" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I918" s="8" t="s">
+        <v>4874</v>
+      </c>
+    </row>
+    <row r="919" spans="1:9" ht="69" x14ac:dyDescent="0.3">
+      <c r="A919" s="5" t="s">
+        <v>5424</v>
+      </c>
+      <c r="B919" s="8" t="s">
+        <v>4238</v>
+      </c>
+      <c r="C919" s="8" t="s">
+        <v>4875</v>
+      </c>
+      <c r="D919" s="8" t="s">
+        <v>4876</v>
+      </c>
+      <c r="E919" s="8" t="s">
+        <v>4877</v>
+      </c>
+      <c r="F919" s="8" t="s">
+        <v>4878</v>
+      </c>
+      <c r="G919" s="8" t="s">
+        <v>4879</v>
+      </c>
+      <c r="H919" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="I919" s="8" t="s">
+        <v>4880</v>
+      </c>
+    </row>
+    <row r="920" spans="1:9" ht="69" x14ac:dyDescent="0.3">
+      <c r="A920" s="5" t="s">
+        <v>5424</v>
+      </c>
+      <c r="B920" s="8" t="s">
+        <v>4238</v>
+      </c>
+      <c r="C920" s="8" t="s">
+        <v>4881</v>
+      </c>
+      <c r="D920" s="8" t="s">
+        <v>4882</v>
+      </c>
+      <c r="E920" s="8" t="s">
+        <v>4883</v>
+      </c>
+      <c r="F920" s="8" t="s">
+        <v>4884</v>
+      </c>
+      <c r="G920" s="8" t="s">
+        <v>4885</v>
+      </c>
+      <c r="H920" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="I920" s="8" t="s">
+        <v>4886</v>
+      </c>
+    </row>
+    <row r="921" spans="1:9" ht="69" x14ac:dyDescent="0.3">
+      <c r="A921" s="5" t="s">
+        <v>5424</v>
+      </c>
+      <c r="B921" s="8" t="s">
+        <v>4238</v>
+      </c>
+      <c r="C921" s="8" t="s">
+        <v>4887</v>
+      </c>
+      <c r="D921" s="8" t="s">
+        <v>4888</v>
+      </c>
+      <c r="E921" s="8" t="s">
+        <v>4889</v>
+      </c>
+      <c r="F921" s="8" t="s">
+        <v>4890</v>
+      </c>
+      <c r="G921" s="8" t="s">
+        <v>4891</v>
+      </c>
+      <c r="H921" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="I921" s="8" t="s">
+        <v>4892</v>
+      </c>
+    </row>
+    <row r="922" spans="1:9" ht="69" x14ac:dyDescent="0.3">
+      <c r="A922" s="5" t="s">
+        <v>5424</v>
+      </c>
+      <c r="B922" s="8" t="s">
+        <v>4263</v>
+      </c>
+      <c r="C922" s="8" t="s">
+        <v>4893</v>
+      </c>
+      <c r="D922" s="8" t="s">
+        <v>4894</v>
+      </c>
+      <c r="E922" s="8" t="s">
+        <v>4895</v>
+      </c>
+      <c r="F922" s="8" t="s">
+        <v>4896</v>
+      </c>
+      <c r="G922" s="8" t="s">
+        <v>4897</v>
+      </c>
+      <c r="H922" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="I922" s="8" t="s">
+        <v>4898</v>
+      </c>
+    </row>
+    <row r="923" spans="1:9" ht="55.2" x14ac:dyDescent="0.3">
+      <c r="A923" s="5" t="s">
+        <v>5424</v>
+      </c>
+      <c r="B923" s="8" t="s">
+        <v>4263</v>
+      </c>
+      <c r="C923" s="8" t="s">
+        <v>4899</v>
+      </c>
+      <c r="D923" s="8" t="s">
+        <v>4900</v>
+      </c>
+      <c r="E923" s="8" t="s">
+        <v>4901</v>
+      </c>
+      <c r="F923" s="8" t="s">
+        <v>4902</v>
+      </c>
+      <c r="G923" s="8" t="s">
+        <v>4903</v>
+      </c>
+      <c r="H923" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="I923" s="8" t="s">
+        <v>4904</v>
+      </c>
+    </row>
+    <row r="924" spans="1:9" ht="55.2" x14ac:dyDescent="0.3">
+      <c r="A924" s="5" t="s">
+        <v>5424</v>
+      </c>
+      <c r="B924" s="8" t="s">
+        <v>4263</v>
+      </c>
+      <c r="C924" s="8" t="s">
+        <v>4905</v>
+      </c>
+      <c r="D924" s="8" t="s">
+        <v>4906</v>
+      </c>
+      <c r="E924" s="8" t="s">
+        <v>4907</v>
+      </c>
+      <c r="F924" s="8" t="s">
+        <v>4908</v>
+      </c>
+      <c r="G924" s="8" t="s">
+        <v>4909</v>
+      </c>
+      <c r="H924" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="I924" s="8" t="s">
+        <v>4910</v>
+      </c>
+    </row>
+    <row r="925" spans="1:9" ht="69" x14ac:dyDescent="0.3">
+      <c r="A925" s="5" t="s">
+        <v>5424</v>
+      </c>
+      <c r="B925" s="8" t="s">
+        <v>4263</v>
+      </c>
+      <c r="C925" s="8" t="s">
+        <v>4911</v>
+      </c>
+      <c r="D925" s="8" t="s">
+        <v>4912</v>
+      </c>
+      <c r="E925" s="8" t="s">
+        <v>4913</v>
+      </c>
+      <c r="F925" s="8" t="s">
+        <v>4914</v>
+      </c>
+      <c r="G925" s="8" t="s">
+        <v>4915</v>
+      </c>
+      <c r="H925" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="I925" s="8" t="s">
+        <v>4916</v>
+      </c>
+    </row>
+    <row r="926" spans="1:9" ht="69" x14ac:dyDescent="0.3">
+      <c r="A926" s="5" t="s">
+        <v>5424</v>
+      </c>
+      <c r="B926" s="8" t="s">
+        <v>4288</v>
+      </c>
+      <c r="C926" s="8" t="s">
+        <v>4917</v>
+      </c>
+      <c r="D926" s="8" t="s">
+        <v>4918</v>
+      </c>
+      <c r="E926" s="8" t="s">
+        <v>4919</v>
+      </c>
+      <c r="F926" s="8" t="s">
+        <v>4920</v>
+      </c>
+      <c r="G926" s="8" t="s">
+        <v>4921</v>
+      </c>
+      <c r="H926" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="I926" s="8" t="s">
+        <v>4922</v>
+      </c>
+    </row>
+    <row r="927" spans="1:9" ht="69" x14ac:dyDescent="0.3">
+      <c r="A927" s="5" t="s">
+        <v>5424</v>
+      </c>
+      <c r="B927" s="8" t="s">
+        <v>4288</v>
+      </c>
+      <c r="C927" s="8" t="s">
+        <v>4923</v>
+      </c>
+      <c r="D927" s="8" t="s">
+        <v>4924</v>
+      </c>
+      <c r="E927" s="8" t="s">
+        <v>4925</v>
+      </c>
+      <c r="F927" s="8" t="s">
+        <v>4926</v>
+      </c>
+      <c r="G927" s="8" t="s">
+        <v>4927</v>
+      </c>
+      <c r="H927" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I927" s="8" t="s">
+        <v>4928</v>
+      </c>
+    </row>
+    <row r="928" spans="1:9" ht="55.2" x14ac:dyDescent="0.3">
+      <c r="A928" s="5" t="s">
+        <v>5424</v>
+      </c>
+      <c r="B928" s="8" t="s">
+        <v>4288</v>
+      </c>
+      <c r="C928" s="8" t="s">
+        <v>4929</v>
+      </c>
+      <c r="D928" s="8" t="s">
+        <v>4930</v>
+      </c>
+      <c r="E928" s="8" t="s">
+        <v>4931</v>
+      </c>
+      <c r="F928" s="8" t="s">
+        <v>4932</v>
+      </c>
+      <c r="G928" s="8" t="s">
+        <v>4933</v>
+      </c>
+      <c r="H928" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="I928" s="8" t="s">
+        <v>4934</v>
+      </c>
+    </row>
+    <row r="929" spans="1:9" ht="69" x14ac:dyDescent="0.3">
+      <c r="A929" s="5" t="s">
+        <v>5424</v>
+      </c>
+      <c r="B929" s="8" t="s">
+        <v>4288</v>
+      </c>
+      <c r="C929" s="8" t="s">
+        <v>4935</v>
+      </c>
+      <c r="D929" s="8" t="s">
+        <v>4936</v>
+      </c>
+      <c r="E929" s="8" t="s">
+        <v>4937</v>
+      </c>
+      <c r="F929" s="8" t="s">
+        <v>4938</v>
+      </c>
+      <c r="G929" s="8" t="s">
+        <v>4939</v>
+      </c>
+      <c r="H929" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="I929" s="8" t="s">
+        <v>4940</v>
+      </c>
+    </row>
+    <row r="930" spans="1:9" ht="69" x14ac:dyDescent="0.3">
+      <c r="A930" s="5" t="s">
+        <v>5424</v>
+      </c>
+      <c r="B930" s="8" t="s">
+        <v>4288</v>
+      </c>
+      <c r="C930" s="8" t="s">
+        <v>4941</v>
+      </c>
+      <c r="D930" s="8" t="s">
+        <v>4942</v>
+      </c>
+      <c r="E930" s="8" t="s">
+        <v>4943</v>
+      </c>
+      <c r="F930" s="8" t="s">
+        <v>4944</v>
+      </c>
+      <c r="G930" s="8" t="s">
+        <v>4945</v>
+      </c>
+      <c r="H930" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="I930" s="8" t="s">
+        <v>4946</v>
+      </c>
+    </row>
+    <row r="931" spans="1:9" ht="55.2" x14ac:dyDescent="0.3">
+      <c r="A931" s="5" t="s">
+        <v>5424</v>
+      </c>
+      <c r="B931" s="8" t="s">
+        <v>4317</v>
+      </c>
+      <c r="C931" s="8" t="s">
+        <v>4947</v>
+      </c>
+      <c r="D931" s="8" t="s">
+        <v>3743</v>
+      </c>
+      <c r="E931" s="8" t="s">
+        <v>4948</v>
+      </c>
+      <c r="F931" s="8" t="s">
+        <v>4949</v>
+      </c>
+      <c r="G931" s="8" t="s">
+        <v>4950</v>
+      </c>
+      <c r="H931" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="I931" s="8" t="s">
+        <v>4951</v>
+      </c>
+    </row>
+    <row r="932" spans="1:9" ht="55.2" x14ac:dyDescent="0.3">
+      <c r="A932" s="5" t="s">
+        <v>5424</v>
+      </c>
+      <c r="B932" s="8" t="s">
+        <v>4317</v>
+      </c>
+      <c r="C932" s="8" t="s">
+        <v>4952</v>
+      </c>
+      <c r="D932" s="8" t="s">
+        <v>4953</v>
+      </c>
+      <c r="E932" s="8" t="s">
+        <v>4954</v>
+      </c>
+      <c r="F932" s="8" t="s">
+        <v>4955</v>
+      </c>
+      <c r="G932" s="8" t="s">
+        <v>4956</v>
+      </c>
+      <c r="H932" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I932" s="8" t="s">
+        <v>4957</v>
+      </c>
+    </row>
+    <row r="933" spans="1:9" ht="55.2" x14ac:dyDescent="0.3">
+      <c r="A933" s="5" t="s">
+        <v>5424</v>
+      </c>
+      <c r="B933" s="8" t="s">
+        <v>4317</v>
+      </c>
+      <c r="C933" s="8" t="s">
+        <v>4958</v>
+      </c>
+      <c r="D933" s="8" t="s">
+        <v>4959</v>
+      </c>
+      <c r="E933" s="8" t="s">
+        <v>4960</v>
+      </c>
+      <c r="F933" s="8" t="s">
+        <v>4961</v>
+      </c>
+      <c r="G933" s="8" t="s">
+        <v>4962</v>
+      </c>
+      <c r="H933" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I933" s="8" t="s">
+        <v>4963</v>
+      </c>
+    </row>
+    <row r="934" spans="1:9" ht="69" x14ac:dyDescent="0.3">
+      <c r="A934" s="5" t="s">
+        <v>5424</v>
+      </c>
+      <c r="B934" s="8" t="s">
+        <v>4317</v>
+      </c>
+      <c r="C934" s="8" t="s">
+        <v>4964</v>
+      </c>
+      <c r="D934" s="8" t="s">
+        <v>4965</v>
+      </c>
+      <c r="E934" s="8" t="s">
+        <v>4966</v>
+      </c>
+      <c r="F934" s="8" t="s">
+        <v>4967</v>
+      </c>
+      <c r="G934" s="8" t="s">
+        <v>4968</v>
+      </c>
+      <c r="H934" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="I934" s="8" t="s">
+        <v>4969</v>
+      </c>
+    </row>
+    <row r="935" spans="1:9" ht="55.2" x14ac:dyDescent="0.3">
+      <c r="A935" s="5" t="s">
+        <v>5424</v>
+      </c>
+      <c r="B935" s="8" t="s">
+        <v>4317</v>
+      </c>
+      <c r="C935" s="8" t="s">
+        <v>4970</v>
+      </c>
+      <c r="D935" s="8" t="s">
+        <v>4971</v>
+      </c>
+      <c r="E935" s="8" t="s">
+        <v>4972</v>
+      </c>
+      <c r="F935" s="8" t="s">
+        <v>4973</v>
+      </c>
+      <c r="G935" s="8" t="s">
+        <v>4974</v>
+      </c>
+      <c r="H935" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I935" s="8" t="s">
+        <v>4975</v>
+      </c>
+    </row>
+    <row r="936" spans="1:9" ht="69" x14ac:dyDescent="0.3">
+      <c r="A936" s="5" t="s">
+        <v>5424</v>
+      </c>
+      <c r="B936" s="8" t="s">
+        <v>4317</v>
+      </c>
+      <c r="C936" s="8" t="s">
+        <v>4976</v>
+      </c>
+      <c r="D936" s="8" t="s">
+        <v>4977</v>
+      </c>
+      <c r="E936" s="8" t="s">
+        <v>4978</v>
+      </c>
+      <c r="F936" s="8" t="s">
+        <v>4979</v>
+      </c>
+      <c r="G936" s="8" t="s">
+        <v>4980</v>
+      </c>
+      <c r="H936" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I936" s="8" t="s">
+        <v>4981</v>
+      </c>
+    </row>
+    <row r="937" spans="1:9" ht="41.4" x14ac:dyDescent="0.3">
+      <c r="A937" s="5" t="s">
+        <v>5424</v>
+      </c>
+      <c r="B937" s="8" t="s">
+        <v>4317</v>
+      </c>
+      <c r="C937" s="8" t="s">
+        <v>4982</v>
+      </c>
+      <c r="D937" s="8" t="s">
+        <v>4983</v>
+      </c>
+      <c r="E937" s="8" t="s">
+        <v>4984</v>
+      </c>
+      <c r="F937" s="8" t="s">
+        <v>4985</v>
+      </c>
+      <c r="G937" s="8" t="s">
+        <v>4986</v>
+      </c>
+      <c r="H937" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="I937" s="8" t="s">
+        <v>4987</v>
+      </c>
+    </row>
+    <row r="938" spans="1:9" ht="69" x14ac:dyDescent="0.3">
+      <c r="A938" s="5" t="s">
+        <v>5424</v>
+      </c>
+      <c r="B938" s="8" t="s">
+        <v>4359</v>
+      </c>
+      <c r="C938" s="8" t="s">
+        <v>4988</v>
+      </c>
+      <c r="D938" s="8" t="s">
+        <v>4989</v>
+      </c>
+      <c r="E938" s="8" t="s">
+        <v>4990</v>
+      </c>
+      <c r="F938" s="8" t="s">
+        <v>4991</v>
+      </c>
+      <c r="G938" s="8" t="s">
+        <v>4992</v>
+      </c>
+      <c r="H938" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="I938" s="8" t="s">
+        <v>4993</v>
+      </c>
+    </row>
+    <row r="939" spans="1:9" ht="82.8" x14ac:dyDescent="0.3">
+      <c r="A939" s="5" t="s">
+        <v>5424</v>
+      </c>
+      <c r="B939" s="8" t="s">
+        <v>4359</v>
+      </c>
+      <c r="C939" s="8" t="s">
+        <v>4994</v>
+      </c>
+      <c r="D939" s="8" t="s">
+        <v>4995</v>
+      </c>
+      <c r="E939" s="8" t="s">
+        <v>4996</v>
+      </c>
+      <c r="F939" s="8" t="s">
+        <v>4997</v>
+      </c>
+      <c r="G939" s="8" t="s">
+        <v>4998</v>
+      </c>
+      <c r="H939" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I939" s="8" t="s">
+        <v>4999</v>
+      </c>
+    </row>
+    <row r="940" spans="1:9" ht="55.2" x14ac:dyDescent="0.3">
+      <c r="A940" s="5" t="s">
+        <v>5424</v>
+      </c>
+      <c r="B940" s="8" t="s">
+        <v>4359</v>
+      </c>
+      <c r="C940" s="8" t="s">
+        <v>5000</v>
+      </c>
+      <c r="D940" s="8" t="s">
+        <v>5001</v>
+      </c>
+      <c r="E940" s="8" t="s">
+        <v>5002</v>
+      </c>
+      <c r="F940" s="8" t="s">
+        <v>5003</v>
+      </c>
+      <c r="G940" s="8" t="s">
+        <v>5004</v>
+      </c>
+      <c r="H940" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I940" s="8" t="s">
+        <v>5005</v>
+      </c>
+    </row>
+    <row r="941" spans="1:9" ht="69" x14ac:dyDescent="0.3">
+      <c r="A941" s="5" t="s">
+        <v>5424</v>
+      </c>
+      <c r="B941" s="8" t="s">
+        <v>4378</v>
+      </c>
+      <c r="C941" s="8" t="s">
+        <v>5006</v>
+      </c>
+      <c r="D941" s="8" t="s">
+        <v>5007</v>
+      </c>
+      <c r="E941" s="8" t="s">
+        <v>4447</v>
+      </c>
+      <c r="F941" s="8" t="s">
+        <v>5008</v>
+      </c>
+      <c r="G941" s="8" t="s">
+        <v>5009</v>
+      </c>
+      <c r="H941" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="I941" s="8" t="s">
+        <v>5010</v>
+      </c>
+    </row>
+    <row r="942" spans="1:9" ht="69" x14ac:dyDescent="0.3">
+      <c r="A942" s="5" t="s">
+        <v>5424</v>
+      </c>
+      <c r="B942" s="8" t="s">
+        <v>4378</v>
+      </c>
+      <c r="C942" s="8" t="s">
+        <v>5011</v>
+      </c>
+      <c r="D942" s="8" t="s">
+        <v>5012</v>
+      </c>
+      <c r="E942" s="8" t="s">
+        <v>5013</v>
+      </c>
+      <c r="F942" s="8" t="s">
+        <v>5014</v>
+      </c>
+      <c r="G942" s="8" t="s">
+        <v>5015</v>
+      </c>
+      <c r="H942" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="I942" s="8" t="s">
+        <v>5016</v>
+      </c>
+    </row>
+    <row r="943" spans="1:9" ht="69" x14ac:dyDescent="0.3">
+      <c r="A943" s="5" t="s">
+        <v>5424</v>
+      </c>
+      <c r="B943" s="8" t="s">
+        <v>4378</v>
+      </c>
+      <c r="C943" s="8" t="s">
+        <v>5017</v>
+      </c>
+      <c r="D943" s="8" t="s">
+        <v>5018</v>
+      </c>
+      <c r="E943" s="8" t="s">
+        <v>5019</v>
+      </c>
+      <c r="F943" s="8" t="s">
+        <v>5020</v>
+      </c>
+      <c r="G943" s="8" t="s">
+        <v>5021</v>
+      </c>
+      <c r="H943" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I943" s="8" t="s">
+        <v>5022</v>
+      </c>
+    </row>
+    <row r="944" spans="1:9" ht="69" x14ac:dyDescent="0.3">
+      <c r="A944" s="5" t="s">
+        <v>5424</v>
+      </c>
+      <c r="B944" s="8" t="s">
+        <v>4378</v>
+      </c>
+      <c r="C944" s="8" t="s">
+        <v>5023</v>
+      </c>
+      <c r="D944" s="8" t="s">
+        <v>5024</v>
+      </c>
+      <c r="E944" s="8" t="s">
+        <v>5025</v>
+      </c>
+      <c r="F944" s="8" t="s">
+        <v>5026</v>
+      </c>
+      <c r="G944" s="8" t="s">
+        <v>5027</v>
+      </c>
+      <c r="H944" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="I944" s="8" t="s">
+        <v>5028</v>
+      </c>
+    </row>
+    <row r="945" spans="1:9" ht="69" x14ac:dyDescent="0.3">
+      <c r="A945" s="5" t="s">
+        <v>5424</v>
+      </c>
+      <c r="B945" s="8" t="s">
+        <v>4403</v>
+      </c>
+      <c r="C945" s="8" t="s">
+        <v>5029</v>
+      </c>
+      <c r="D945" s="8" t="s">
+        <v>5030</v>
+      </c>
+      <c r="E945" s="8" t="s">
+        <v>5031</v>
+      </c>
+      <c r="F945" s="8" t="s">
+        <v>5032</v>
+      </c>
+      <c r="G945" s="8" t="s">
+        <v>5033</v>
+      </c>
+      <c r="H945" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="I945" s="8" t="s">
+        <v>5034</v>
+      </c>
+    </row>
+    <row r="946" spans="1:9" ht="69" x14ac:dyDescent="0.3">
+      <c r="A946" s="5" t="s">
+        <v>5424</v>
+      </c>
+      <c r="B946" s="8" t="s">
+        <v>4403</v>
+      </c>
+      <c r="C946" s="8" t="s">
+        <v>5035</v>
+      </c>
+      <c r="D946" s="8" t="s">
+        <v>5036</v>
+      </c>
+      <c r="E946" s="8" t="s">
+        <v>5037</v>
+      </c>
+      <c r="F946" s="8" t="s">
+        <v>5038</v>
+      </c>
+      <c r="G946" s="8" t="s">
+        <v>5039</v>
+      </c>
+      <c r="H946" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I946" s="8" t="s">
+        <v>5040</v>
+      </c>
+    </row>
+    <row r="947" spans="1:9" ht="55.2" x14ac:dyDescent="0.3">
+      <c r="A947" s="5" t="s">
+        <v>5424</v>
+      </c>
+      <c r="B947" s="8" t="s">
+        <v>4403</v>
+      </c>
+      <c r="C947" s="8" t="s">
+        <v>5041</v>
+      </c>
+      <c r="D947" s="8" t="s">
+        <v>5042</v>
+      </c>
+      <c r="E947" s="8" t="s">
+        <v>5043</v>
+      </c>
+      <c r="F947" s="8" t="s">
+        <v>5044</v>
+      </c>
+      <c r="G947" s="8" t="s">
+        <v>5045</v>
+      </c>
+      <c r="H947" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="I947" s="8" t="s">
+        <v>5046</v>
+      </c>
+    </row>
+    <row r="948" spans="1:9" ht="55.2" x14ac:dyDescent="0.3">
+      <c r="A948" s="5" t="s">
+        <v>5424</v>
+      </c>
+      <c r="B948" s="8" t="s">
+        <v>4403</v>
+      </c>
+      <c r="C948" s="8" t="s">
+        <v>5047</v>
+      </c>
+      <c r="D948" s="8" t="s">
+        <v>5048</v>
+      </c>
+      <c r="E948" s="8" t="s">
+        <v>5049</v>
+      </c>
+      <c r="F948" s="8" t="s">
+        <v>5050</v>
+      </c>
+      <c r="G948" s="8" t="s">
+        <v>5051</v>
+      </c>
+      <c r="H948" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I948" s="8" t="s">
+        <v>5052</v>
+      </c>
+    </row>
+    <row r="949" spans="1:9" ht="69" x14ac:dyDescent="0.3">
+      <c r="A949" s="5" t="s">
+        <v>5424</v>
+      </c>
+      <c r="B949" s="8" t="s">
+        <v>4403</v>
+      </c>
+      <c r="C949" s="8" t="s">
+        <v>5053</v>
+      </c>
+      <c r="D949" s="8" t="s">
+        <v>5054</v>
+      </c>
+      <c r="E949" s="8" t="s">
+        <v>5055</v>
+      </c>
+      <c r="F949" s="8" t="s">
+        <v>5056</v>
+      </c>
+      <c r="G949" s="8" t="s">
+        <v>5057</v>
+      </c>
+      <c r="H949" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="I949" s="8" t="s">
+        <v>5058</v>
+      </c>
+    </row>
+    <row r="950" spans="1:9" ht="41.4" x14ac:dyDescent="0.3">
+      <c r="A950" s="5" t="s">
+        <v>5424</v>
+      </c>
+      <c r="B950" s="8" t="s">
+        <v>4403</v>
+      </c>
+      <c r="C950" s="8" t="s">
+        <v>5059</v>
+      </c>
+      <c r="D950" s="8" t="s">
+        <v>5060</v>
+      </c>
+      <c r="E950" s="8" t="s">
+        <v>5061</v>
+      </c>
+      <c r="F950" s="8" t="s">
+        <v>5062</v>
+      </c>
+      <c r="G950" s="8" t="s">
+        <v>5063</v>
+      </c>
+      <c r="H950" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I950" s="8" t="s">
+        <v>5064</v>
+      </c>
+    </row>
+    <row r="951" spans="1:9" ht="69" x14ac:dyDescent="0.3">
+      <c r="A951" s="5" t="s">
+        <v>5424</v>
+      </c>
+      <c r="B951" s="8" t="s">
+        <v>4439</v>
+      </c>
+      <c r="C951" s="8" t="s">
+        <v>5065</v>
+      </c>
+      <c r="D951" s="8" t="s">
+        <v>5066</v>
+      </c>
+      <c r="E951" s="8" t="s">
+        <v>5067</v>
+      </c>
+      <c r="F951" s="8" t="s">
+        <v>5068</v>
+      </c>
+      <c r="G951" s="8" t="s">
+        <v>5069</v>
+      </c>
+      <c r="H951" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="I951" s="8" t="s">
+        <v>5070</v>
+      </c>
+    </row>
+    <row r="952" spans="1:9" ht="69" x14ac:dyDescent="0.3">
+      <c r="A952" s="5" t="s">
+        <v>5424</v>
+      </c>
+      <c r="B952" s="8" t="s">
+        <v>4439</v>
+      </c>
+      <c r="C952" s="8" t="s">
+        <v>5071</v>
+      </c>
+      <c r="D952" s="8" t="s">
+        <v>5072</v>
+      </c>
+      <c r="E952" s="8" t="s">
+        <v>5073</v>
+      </c>
+      <c r="F952" s="8" t="s">
+        <v>5074</v>
+      </c>
+      <c r="G952" s="8" t="s">
+        <v>5075</v>
+      </c>
+      <c r="H952" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="I952" s="8" t="s">
+        <v>5076</v>
+      </c>
+    </row>
+    <row r="953" spans="1:9" ht="41.4" x14ac:dyDescent="0.3">
+      <c r="A953" s="5" t="s">
+        <v>5424</v>
+      </c>
+      <c r="B953" s="8" t="s">
+        <v>4439</v>
+      </c>
+      <c r="C953" s="8" t="s">
+        <v>5077</v>
+      </c>
+      <c r="D953" s="8" t="s">
+        <v>5078</v>
+      </c>
+      <c r="E953" s="8" t="s">
+        <v>5079</v>
+      </c>
+      <c r="F953" s="8" t="s">
+        <v>5080</v>
+      </c>
+      <c r="G953" s="8" t="s">
+        <v>5081</v>
+      </c>
+      <c r="H953" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="I953" s="8" t="s">
+        <v>5082</v>
+      </c>
+    </row>
+    <row r="954" spans="1:9" ht="69" x14ac:dyDescent="0.3">
+      <c r="A954" s="5" t="s">
+        <v>5424</v>
+      </c>
+      <c r="B954" s="8" t="s">
+        <v>4439</v>
+      </c>
+      <c r="C954" s="8" t="s">
+        <v>5083</v>
+      </c>
+      <c r="D954" s="8" t="s">
+        <v>5084</v>
+      </c>
+      <c r="E954" s="8" t="s">
+        <v>5085</v>
+      </c>
+      <c r="F954" s="8" t="s">
+        <v>5086</v>
+      </c>
+      <c r="G954" s="8" t="s">
+        <v>5087</v>
+      </c>
+      <c r="H954" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I954" s="8" t="s">
+        <v>5088</v>
+      </c>
+    </row>
+    <row r="955" spans="1:9" ht="55.2" x14ac:dyDescent="0.3">
+      <c r="A955" s="5" t="s">
+        <v>5424</v>
+      </c>
+      <c r="B955" s="8" t="s">
+        <v>4439</v>
+      </c>
+      <c r="C955" s="8" t="s">
+        <v>5089</v>
+      </c>
+      <c r="D955" s="8" t="s">
+        <v>3677</v>
+      </c>
+      <c r="E955" s="8" t="s">
+        <v>5090</v>
+      </c>
+      <c r="F955" s="8" t="s">
+        <v>5091</v>
+      </c>
+      <c r="G955" s="8" t="s">
+        <v>5092</v>
+      </c>
+      <c r="H955" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="I955" s="8" t="s">
+        <v>5093</v>
+      </c>
+    </row>
+    <row r="956" spans="1:9" ht="69" x14ac:dyDescent="0.3">
+      <c r="A956" s="5" t="s">
+        <v>5424</v>
+      </c>
+      <c r="B956" s="8" t="s">
+        <v>4468</v>
+      </c>
+      <c r="C956" s="8" t="s">
+        <v>5094</v>
+      </c>
+      <c r="D956" s="8" t="s">
+        <v>5095</v>
+      </c>
+      <c r="E956" s="8" t="s">
+        <v>5096</v>
+      </c>
+      <c r="F956" s="8" t="s">
+        <v>5097</v>
+      </c>
+      <c r="G956" s="8" t="s">
+        <v>5098</v>
+      </c>
+      <c r="H956" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="I956" s="8" t="s">
+        <v>5099</v>
+      </c>
+    </row>
+    <row r="957" spans="1:9" ht="41.4" x14ac:dyDescent="0.3">
+      <c r="A957" s="5" t="s">
+        <v>5424</v>
+      </c>
+      <c r="B957" s="8" t="s">
+        <v>4468</v>
+      </c>
+      <c r="C957" s="8" t="s">
+        <v>5100</v>
+      </c>
+      <c r="D957" s="8" t="s">
+        <v>5101</v>
+      </c>
+      <c r="E957" s="8" t="s">
+        <v>4950</v>
+      </c>
+      <c r="F957" s="8" t="s">
+        <v>4214</v>
+      </c>
+      <c r="G957" s="8" t="s">
+        <v>4216</v>
+      </c>
+      <c r="H957" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="I957" s="8" t="s">
+        <v>5102</v>
+      </c>
+    </row>
+    <row r="958" spans="1:9" ht="69" x14ac:dyDescent="0.3">
+      <c r="A958" s="5" t="s">
+        <v>5424</v>
+      </c>
+      <c r="B958" s="8" t="s">
+        <v>4468</v>
+      </c>
+      <c r="C958" s="8" t="s">
+        <v>5103</v>
+      </c>
+      <c r="D958" s="8" t="s">
+        <v>5104</v>
+      </c>
+      <c r="E958" s="8" t="s">
+        <v>5105</v>
+      </c>
+      <c r="F958" s="8" t="s">
+        <v>5106</v>
+      </c>
+      <c r="G958" s="8" t="s">
+        <v>5107</v>
+      </c>
+      <c r="H958" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I958" s="8" t="s">
+        <v>5108</v>
+      </c>
+    </row>
+    <row r="959" spans="1:9" ht="41.4" x14ac:dyDescent="0.3">
+      <c r="A959" s="5" t="s">
+        <v>5424</v>
+      </c>
+      <c r="B959" s="8" t="s">
+        <v>4486</v>
+      </c>
+      <c r="C959" s="8" t="s">
+        <v>5109</v>
+      </c>
+      <c r="D959" s="8" t="s">
+        <v>5110</v>
+      </c>
+      <c r="E959" s="8" t="s">
+        <v>5111</v>
+      </c>
+      <c r="F959" s="8" t="s">
+        <v>5112</v>
+      </c>
+      <c r="G959" s="8" t="s">
+        <v>5113</v>
+      </c>
+      <c r="H959" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="I959" s="8" t="s">
+        <v>5114</v>
+      </c>
+    </row>
+    <row r="960" spans="1:9" ht="69" x14ac:dyDescent="0.3">
+      <c r="A960" s="5" t="s">
+        <v>5424</v>
+      </c>
+      <c r="B960" s="8" t="s">
+        <v>4486</v>
+      </c>
+      <c r="C960" s="8" t="s">
+        <v>5115</v>
+      </c>
+      <c r="D960" s="8" t="s">
+        <v>5116</v>
+      </c>
+      <c r="E960" s="8" t="s">
+        <v>5117</v>
+      </c>
+      <c r="F960" s="8" t="s">
+        <v>5118</v>
+      </c>
+      <c r="G960" s="8" t="s">
+        <v>5119</v>
+      </c>
+      <c r="H960" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="I960" s="8" t="s">
+        <v>5120</v>
+      </c>
+    </row>
+    <row r="961" spans="1:9" ht="69" x14ac:dyDescent="0.3">
+      <c r="A961" s="5" t="s">
+        <v>5424</v>
+      </c>
+      <c r="B961" s="8" t="s">
+        <v>4486</v>
+      </c>
+      <c r="C961" s="8" t="s">
+        <v>5121</v>
+      </c>
+      <c r="D961" s="8" t="s">
+        <v>5122</v>
+      </c>
+      <c r="E961" s="8" t="s">
+        <v>5123</v>
+      </c>
+      <c r="F961" s="8" t="s">
+        <v>5124</v>
+      </c>
+      <c r="G961" s="8" t="s">
+        <v>5125</v>
+      </c>
+      <c r="H961" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="I961" s="8" t="s">
+        <v>5126</v>
+      </c>
+    </row>
+    <row r="962" spans="1:9" ht="55.2" x14ac:dyDescent="0.3">
+      <c r="A962" s="5" t="s">
+        <v>5425</v>
+      </c>
+      <c r="B962" s="8" t="s">
+        <v>4504</v>
+      </c>
+      <c r="C962" s="8" t="s">
+        <v>5127</v>
+      </c>
+      <c r="D962" s="8" t="s">
+        <v>5128</v>
+      </c>
+      <c r="E962" s="8" t="s">
+        <v>5129</v>
+      </c>
+      <c r="F962" s="8" t="s">
+        <v>5130</v>
+      </c>
+      <c r="G962" s="8" t="s">
+        <v>5131</v>
+      </c>
+      <c r="H962" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="I962" s="8" t="s">
+        <v>5132</v>
+      </c>
+    </row>
+    <row r="963" spans="1:9" ht="82.8" x14ac:dyDescent="0.3">
+      <c r="A963" s="5" t="s">
+        <v>5425</v>
+      </c>
+      <c r="B963" s="8" t="s">
+        <v>4504</v>
+      </c>
+      <c r="C963" s="8" t="s">
+        <v>5133</v>
+      </c>
+      <c r="D963" s="8" t="s">
+        <v>5134</v>
+      </c>
+      <c r="E963" s="8" t="s">
+        <v>5135</v>
+      </c>
+      <c r="F963" s="8" t="s">
+        <v>5136</v>
+      </c>
+      <c r="G963" s="8" t="s">
+        <v>5137</v>
+      </c>
+      <c r="H963" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="I963" s="8" t="s">
+        <v>5138</v>
+      </c>
+    </row>
+    <row r="964" spans="1:9" ht="82.8" x14ac:dyDescent="0.3">
+      <c r="A964" s="5" t="s">
+        <v>5425</v>
+      </c>
+      <c r="B964" s="8" t="s">
+        <v>4517</v>
+      </c>
+      <c r="C964" s="8" t="s">
+        <v>5139</v>
+      </c>
+      <c r="D964" s="8" t="s">
+        <v>5140</v>
+      </c>
+      <c r="E964" s="8" t="s">
+        <v>5141</v>
+      </c>
+      <c r="F964" s="8" t="s">
+        <v>5142</v>
+      </c>
+      <c r="G964" s="8" t="s">
+        <v>5143</v>
+      </c>
+      <c r="H964" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I964" s="8" t="s">
+        <v>5144</v>
+      </c>
+    </row>
+    <row r="965" spans="1:9" ht="69" x14ac:dyDescent="0.3">
+      <c r="A965" s="5" t="s">
+        <v>5425</v>
+      </c>
+      <c r="B965" s="8" t="s">
+        <v>4517</v>
+      </c>
+      <c r="C965" s="8" t="s">
+        <v>5145</v>
+      </c>
+      <c r="D965" s="8" t="s">
+        <v>5146</v>
+      </c>
+      <c r="E965" s="8" t="s">
+        <v>5147</v>
+      </c>
+      <c r="F965" s="8" t="s">
+        <v>5148</v>
+      </c>
+      <c r="G965" s="8" t="s">
+        <v>5149</v>
+      </c>
+      <c r="H965" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="I965" s="8" t="s">
+        <v>5150</v>
+      </c>
+    </row>
+    <row r="966" spans="1:9" ht="69" x14ac:dyDescent="0.3">
+      <c r="A966" s="5" t="s">
+        <v>5425</v>
+      </c>
+      <c r="B966" s="8" t="s">
+        <v>4530</v>
+      </c>
+      <c r="C966" s="8" t="s">
+        <v>5151</v>
+      </c>
+      <c r="D966" s="8" t="s">
+        <v>5152</v>
+      </c>
+      <c r="E966" s="8" t="s">
+        <v>5153</v>
+      </c>
+      <c r="F966" s="8" t="s">
+        <v>5154</v>
+      </c>
+      <c r="G966" s="8" t="s">
+        <v>5155</v>
+      </c>
+      <c r="H966" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="I966" s="8" t="s">
+        <v>5156</v>
+      </c>
+    </row>
+    <row r="967" spans="1:9" ht="55.2" x14ac:dyDescent="0.3">
+      <c r="A967" s="5" t="s">
+        <v>5425</v>
+      </c>
+      <c r="B967" s="8" t="s">
+        <v>4537</v>
+      </c>
+      <c r="C967" s="8" t="s">
+        <v>5157</v>
+      </c>
+      <c r="D967" s="8" t="s">
+        <v>5158</v>
+      </c>
+      <c r="E967" s="8" t="s">
+        <v>5159</v>
+      </c>
+      <c r="F967" s="8" t="s">
+        <v>5160</v>
+      </c>
+      <c r="G967" s="8" t="s">
+        <v>5161</v>
+      </c>
+      <c r="H967" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="I967" s="8" t="s">
+        <v>5162</v>
+      </c>
+    </row>
+    <row r="968" spans="1:9" ht="82.8" x14ac:dyDescent="0.3">
+      <c r="A968" s="5" t="s">
+        <v>5425</v>
+      </c>
+      <c r="B968" s="8" t="s">
+        <v>4544</v>
+      </c>
+      <c r="C968" s="8" t="s">
+        <v>5163</v>
+      </c>
+      <c r="D968" s="8" t="s">
+        <v>5164</v>
+      </c>
+      <c r="E968" s="8" t="s">
+        <v>5165</v>
+      </c>
+      <c r="F968" s="8" t="s">
+        <v>5166</v>
+      </c>
+      <c r="G968" s="8" t="s">
+        <v>5167</v>
+      </c>
+      <c r="H968" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="I968" s="8" t="s">
+        <v>5168</v>
+      </c>
+    </row>
+    <row r="969" spans="1:9" ht="55.2" x14ac:dyDescent="0.3">
+      <c r="A969" s="5" t="s">
+        <v>5425</v>
+      </c>
+      <c r="B969" s="8" t="s">
+        <v>4551</v>
+      </c>
+      <c r="C969" s="8" t="s">
+        <v>5169</v>
+      </c>
+      <c r="D969" s="8" t="s">
+        <v>5170</v>
+      </c>
+      <c r="E969" s="8" t="s">
+        <v>5171</v>
+      </c>
+      <c r="F969" s="8" t="s">
+        <v>5172</v>
+      </c>
+      <c r="G969" s="8" t="s">
+        <v>5173</v>
+      </c>
+      <c r="H969" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="I969" s="8" t="s">
+        <v>5174</v>
+      </c>
+    </row>
+    <row r="970" spans="1:9" ht="55.2" x14ac:dyDescent="0.3">
+      <c r="A970" s="5" t="s">
+        <v>5425</v>
+      </c>
+      <c r="B970" s="8" t="s">
+        <v>4558</v>
+      </c>
+      <c r="C970" s="8" t="s">
+        <v>5175</v>
+      </c>
+      <c r="D970" s="8" t="s">
+        <v>5176</v>
+      </c>
+      <c r="E970" s="8" t="s">
+        <v>5177</v>
+      </c>
+      <c r="F970" s="8" t="s">
+        <v>5178</v>
+      </c>
+      <c r="G970" s="8" t="s">
+        <v>5179</v>
+      </c>
+      <c r="H970" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I970" s="8" t="s">
+        <v>5180</v>
+      </c>
+    </row>
+    <row r="971" spans="1:9" ht="69" x14ac:dyDescent="0.3">
+      <c r="A971" s="5" t="s">
+        <v>5425</v>
+      </c>
+      <c r="B971" s="8" t="s">
+        <v>4565</v>
+      </c>
+      <c r="C971" s="8" t="s">
+        <v>5181</v>
+      </c>
+      <c r="D971" s="8" t="s">
+        <v>5182</v>
+      </c>
+      <c r="E971" s="8" t="s">
+        <v>5183</v>
+      </c>
+      <c r="F971" s="8" t="s">
+        <v>5184</v>
+      </c>
+      <c r="G971" s="8" t="s">
+        <v>5185</v>
+      </c>
+      <c r="H971" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="I971" s="8" t="s">
+        <v>5186</v>
+      </c>
+    </row>
+    <row r="972" spans="1:9" ht="55.2" x14ac:dyDescent="0.3">
+      <c r="A972" s="5" t="s">
+        <v>5425</v>
+      </c>
+      <c r="B972" s="8" t="s">
+        <v>4565</v>
+      </c>
+      <c r="C972" s="8" t="s">
+        <v>5187</v>
+      </c>
+      <c r="D972" s="8" t="s">
+        <v>5188</v>
+      </c>
+      <c r="E972" s="8" t="s">
+        <v>5189</v>
+      </c>
+      <c r="F972" s="8" t="s">
+        <v>5190</v>
+      </c>
+      <c r="G972" s="8" t="s">
+        <v>5191</v>
+      </c>
+      <c r="H972" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="I972" s="8" t="s">
+        <v>5192</v>
+      </c>
+    </row>
+    <row r="973" spans="1:9" ht="69" x14ac:dyDescent="0.3">
+      <c r="A973" s="5" t="s">
+        <v>5425</v>
+      </c>
+      <c r="B973" s="8" t="s">
+        <v>4578</v>
+      </c>
+      <c r="C973" s="8" t="s">
+        <v>5193</v>
+      </c>
+      <c r="D973" s="8" t="s">
+        <v>5194</v>
+      </c>
+      <c r="E973" s="8" t="s">
+        <v>5195</v>
+      </c>
+      <c r="F973" s="8" t="s">
+        <v>5196</v>
+      </c>
+      <c r="G973" s="8" t="s">
+        <v>5197</v>
+      </c>
+      <c r="H973" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="I973" s="8" t="s">
+        <v>5198</v>
+      </c>
+    </row>
+    <row r="974" spans="1:9" ht="69" x14ac:dyDescent="0.3">
+      <c r="A974" s="5" t="s">
+        <v>5426</v>
+      </c>
+      <c r="B974" s="8" t="s">
+        <v>4585</v>
+      </c>
+      <c r="C974" s="8" t="s">
+        <v>5199</v>
+      </c>
+      <c r="D974" s="8" t="s">
+        <v>5200</v>
+      </c>
+      <c r="E974" s="8" t="s">
+        <v>5201</v>
+      </c>
+      <c r="F974" s="8" t="s">
+        <v>5202</v>
+      </c>
+      <c r="G974" s="8" t="s">
+        <v>5203</v>
+      </c>
+      <c r="H974" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="I974" s="8" t="s">
+        <v>5204</v>
+      </c>
+    </row>
+    <row r="975" spans="1:9" ht="69" x14ac:dyDescent="0.3">
+      <c r="A975" s="5" t="s">
+        <v>5426</v>
+      </c>
+      <c r="B975" s="8" t="s">
+        <v>4592</v>
+      </c>
+      <c r="C975" s="8" t="s">
+        <v>5205</v>
+      </c>
+      <c r="D975" s="8" t="s">
+        <v>5206</v>
+      </c>
+      <c r="E975" s="8" t="s">
+        <v>5207</v>
+      </c>
+      <c r="F975" s="8" t="s">
+        <v>5208</v>
+      </c>
+      <c r="G975" s="8" t="s">
+        <v>5209</v>
+      </c>
+      <c r="H975" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I975" s="8" t="s">
+        <v>5210</v>
+      </c>
+    </row>
+    <row r="976" spans="1:9" ht="55.2" x14ac:dyDescent="0.3">
+      <c r="A976" s="5" t="s">
+        <v>5426</v>
+      </c>
+      <c r="B976" s="8" t="s">
+        <v>4592</v>
+      </c>
+      <c r="C976" s="8" t="s">
+        <v>5211</v>
+      </c>
+      <c r="D976" s="8" t="s">
+        <v>5212</v>
+      </c>
+      <c r="E976" s="8" t="s">
+        <v>5213</v>
+      </c>
+      <c r="F976" s="8" t="s">
+        <v>5214</v>
+      </c>
+      <c r="G976" s="8" t="s">
+        <v>5215</v>
+      </c>
+      <c r="H976" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="I976" s="8" t="s">
+        <v>5216</v>
+      </c>
+    </row>
+    <row r="977" spans="1:9" ht="82.8" x14ac:dyDescent="0.3">
+      <c r="A977" s="5" t="s">
+        <v>5426</v>
+      </c>
+      <c r="B977" s="8" t="s">
+        <v>4592</v>
+      </c>
+      <c r="C977" s="8" t="s">
+        <v>5217</v>
+      </c>
+      <c r="D977" s="8" t="s">
+        <v>5218</v>
+      </c>
+      <c r="E977" s="8" t="s">
+        <v>5219</v>
+      </c>
+      <c r="F977" s="8" t="s">
+        <v>5220</v>
+      </c>
+      <c r="G977" s="8" t="s">
+        <v>5221</v>
+      </c>
+      <c r="H977" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="I977" s="8" t="s">
+        <v>5222</v>
+      </c>
+    </row>
+    <row r="978" spans="1:9" ht="55.2" x14ac:dyDescent="0.3">
+      <c r="A978" s="5" t="s">
+        <v>5426</v>
+      </c>
+      <c r="B978" s="8" t="s">
+        <v>4611</v>
+      </c>
+      <c r="C978" s="8" t="s">
+        <v>5223</v>
+      </c>
+      <c r="D978" s="8" t="s">
+        <v>5224</v>
+      </c>
+      <c r="E978" s="8" t="s">
+        <v>5225</v>
+      </c>
+      <c r="F978" s="8" t="s">
+        <v>5226</v>
+      </c>
+      <c r="G978" s="8" t="s">
+        <v>5227</v>
+      </c>
+      <c r="H978" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I978" s="8" t="s">
+        <v>5228</v>
+      </c>
+    </row>
+    <row r="979" spans="1:9" ht="69" x14ac:dyDescent="0.3">
+      <c r="A979" s="5" t="s">
+        <v>5426</v>
+      </c>
+      <c r="B979" s="8" t="s">
+        <v>4618</v>
+      </c>
+      <c r="C979" s="8" t="s">
+        <v>5229</v>
+      </c>
+      <c r="D979" s="8" t="s">
+        <v>5230</v>
+      </c>
+      <c r="E979" s="8" t="s">
+        <v>5231</v>
+      </c>
+      <c r="F979" s="8" t="s">
+        <v>5232</v>
+      </c>
+      <c r="G979" s="8" t="s">
+        <v>5233</v>
+      </c>
+      <c r="H979" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="I979" s="8" t="s">
+        <v>5234</v>
+      </c>
+    </row>
+    <row r="980" spans="1:9" ht="55.2" x14ac:dyDescent="0.3">
+      <c r="A980" s="5" t="s">
+        <v>5426</v>
+      </c>
+      <c r="B980" s="8" t="s">
+        <v>4618</v>
+      </c>
+      <c r="C980" s="8" t="s">
+        <v>5235</v>
+      </c>
+      <c r="D980" s="8" t="s">
+        <v>5236</v>
+      </c>
+      <c r="E980" s="8" t="s">
+        <v>5237</v>
+      </c>
+      <c r="F980" s="8" t="s">
+        <v>5238</v>
+      </c>
+      <c r="G980" s="8" t="s">
+        <v>5239</v>
+      </c>
+      <c r="H980" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="I980" s="8" t="s">
+        <v>5240</v>
+      </c>
+    </row>
+    <row r="981" spans="1:9" ht="69" x14ac:dyDescent="0.3">
+      <c r="A981" s="5" t="s">
+        <v>5426</v>
+      </c>
+      <c r="B981" s="8" t="s">
+        <v>4618</v>
+      </c>
+      <c r="C981" s="8" t="s">
+        <v>5241</v>
+      </c>
+      <c r="D981" s="8" t="s">
+        <v>5242</v>
+      </c>
+      <c r="E981" s="8" t="s">
+        <v>5243</v>
+      </c>
+      <c r="F981" s="8" t="s">
+        <v>5244</v>
+      </c>
+      <c r="G981" s="8" t="s">
+        <v>5245</v>
+      </c>
+      <c r="H981" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="I981" s="8" t="s">
+        <v>5246</v>
+      </c>
+    </row>
+    <row r="982" spans="1:9" ht="55.2" x14ac:dyDescent="0.3">
+      <c r="A982" s="5" t="s">
+        <v>5426</v>
+      </c>
+      <c r="B982" s="8" t="s">
+        <v>4618</v>
+      </c>
+      <c r="C982" s="8" t="s">
+        <v>5247</v>
+      </c>
+      <c r="D982" s="8" t="s">
+        <v>4626</v>
+      </c>
+      <c r="E982" s="8" t="s">
+        <v>4629</v>
+      </c>
+      <c r="F982" s="8" t="s">
+        <v>4627</v>
+      </c>
+      <c r="G982" s="8" t="s">
+        <v>4628</v>
+      </c>
+      <c r="H982" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="I982" s="8" t="s">
+        <v>5248</v>
+      </c>
+    </row>
+    <row r="983" spans="1:9" ht="55.2" x14ac:dyDescent="0.3">
+      <c r="A983" s="5" t="s">
+        <v>5426</v>
+      </c>
+      <c r="B983" s="8" t="s">
+        <v>4643</v>
+      </c>
+      <c r="C983" s="8" t="s">
+        <v>5249</v>
+      </c>
+      <c r="D983" s="8" t="s">
+        <v>5250</v>
+      </c>
+      <c r="E983" s="8" t="s">
+        <v>5251</v>
+      </c>
+      <c r="F983" s="8" t="s">
+        <v>5252</v>
+      </c>
+      <c r="G983" s="8" t="s">
+        <v>5253</v>
+      </c>
+      <c r="H983" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="I983" s="8" t="s">
+        <v>5254</v>
+      </c>
+    </row>
+    <row r="984" spans="1:9" ht="69" x14ac:dyDescent="0.3">
+      <c r="A984" s="5" t="s">
+        <v>5426</v>
+      </c>
+      <c r="B984" s="8" t="s">
+        <v>4643</v>
+      </c>
+      <c r="C984" s="8" t="s">
+        <v>5255</v>
+      </c>
+      <c r="D984" s="8" t="s">
+        <v>5256</v>
+      </c>
+      <c r="E984" s="8" t="s">
+        <v>5257</v>
+      </c>
+      <c r="F984" s="8" t="s">
+        <v>5258</v>
+      </c>
+      <c r="G984" s="8" t="s">
+        <v>5259</v>
+      </c>
+      <c r="H984" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="I984" s="8" t="s">
+        <v>5260</v>
+      </c>
+    </row>
+    <row r="985" spans="1:9" ht="55.2" x14ac:dyDescent="0.3">
+      <c r="A985" s="5" t="s">
+        <v>5426</v>
+      </c>
+      <c r="B985" s="8" t="s">
+        <v>4643</v>
+      </c>
+      <c r="C985" s="8" t="s">
+        <v>5261</v>
+      </c>
+      <c r="D985" s="8" t="s">
+        <v>5262</v>
+      </c>
+      <c r="E985" s="8" t="s">
+        <v>5263</v>
+      </c>
+      <c r="F985" s="8" t="s">
+        <v>5264</v>
+      </c>
+      <c r="G985" s="8" t="s">
+        <v>5265</v>
+      </c>
+      <c r="H985" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I985" s="8" t="s">
+        <v>5266</v>
+      </c>
+    </row>
+    <row r="986" spans="1:9" ht="55.2" x14ac:dyDescent="0.3">
+      <c r="A986" s="5" t="s">
+        <v>5426</v>
+      </c>
+      <c r="B986" s="8" t="s">
+        <v>4662</v>
+      </c>
+      <c r="C986" s="8" t="s">
+        <v>5267</v>
+      </c>
+      <c r="D986" s="8" t="s">
+        <v>5268</v>
+      </c>
+      <c r="E986" s="8" t="s">
+        <v>5269</v>
+      </c>
+      <c r="F986" s="8" t="s">
+        <v>5270</v>
+      </c>
+      <c r="G986" s="8" t="s">
+        <v>5271</v>
+      </c>
+      <c r="H986" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="I986" s="8" t="s">
+        <v>5272</v>
+      </c>
+    </row>
+    <row r="987" spans="1:9" ht="69" x14ac:dyDescent="0.3">
+      <c r="A987" s="5" t="s">
+        <v>5426</v>
+      </c>
+      <c r="B987" s="8" t="s">
+        <v>4662</v>
+      </c>
+      <c r="C987" s="8" t="s">
+        <v>5273</v>
+      </c>
+      <c r="D987" s="8" t="s">
+        <v>5274</v>
+      </c>
+      <c r="E987" s="8" t="s">
+        <v>5275</v>
+      </c>
+      <c r="F987" s="8" t="s">
+        <v>5276</v>
+      </c>
+      <c r="G987" s="8" t="s">
+        <v>5277</v>
+      </c>
+      <c r="H987" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="I987" s="8" t="s">
+        <v>5278</v>
+      </c>
+    </row>
+    <row r="988" spans="1:9" ht="55.2" x14ac:dyDescent="0.3">
+      <c r="A988" s="5" t="s">
+        <v>5426</v>
+      </c>
+      <c r="B988" s="8" t="s">
+        <v>4675</v>
+      </c>
+      <c r="C988" s="8" t="s">
+        <v>5279</v>
+      </c>
+      <c r="D988" s="8" t="s">
+        <v>5280</v>
+      </c>
+      <c r="E988" s="8" t="s">
+        <v>5281</v>
+      </c>
+      <c r="F988" s="8" t="s">
+        <v>5282</v>
+      </c>
+      <c r="G988" s="8" t="s">
+        <v>5283</v>
+      </c>
+      <c r="H988" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I988" s="8" t="s">
+        <v>5284</v>
+      </c>
+    </row>
+    <row r="989" spans="1:9" ht="82.8" x14ac:dyDescent="0.3">
+      <c r="A989" s="5" t="s">
+        <v>5426</v>
+      </c>
+      <c r="B989" s="8" t="s">
+        <v>4675</v>
+      </c>
+      <c r="C989" s="8" t="s">
+        <v>5285</v>
+      </c>
+      <c r="D989" s="8" t="s">
+        <v>5286</v>
+      </c>
+      <c r="E989" s="8" t="s">
+        <v>5287</v>
+      </c>
+      <c r="F989" s="8" t="s">
+        <v>5288</v>
+      </c>
+      <c r="G989" s="8" t="s">
+        <v>5289</v>
+      </c>
+      <c r="H989" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="I989" s="8" t="s">
+        <v>5290</v>
+      </c>
+    </row>
+    <row r="990" spans="1:9" ht="82.8" x14ac:dyDescent="0.3">
+      <c r="A990" s="5" t="s">
+        <v>5426</v>
+      </c>
+      <c r="B990" s="8" t="s">
+        <v>4688</v>
+      </c>
+      <c r="C990" s="8" t="s">
+        <v>5291</v>
+      </c>
+      <c r="D990" s="8" t="s">
+        <v>5292</v>
+      </c>
+      <c r="E990" s="8" t="s">
+        <v>5293</v>
+      </c>
+      <c r="F990" s="8" t="s">
+        <v>5294</v>
+      </c>
+      <c r="G990" s="8" t="s">
+        <v>5295</v>
+      </c>
+      <c r="H990" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I990" s="8" t="s">
+        <v>5296</v>
+      </c>
+    </row>
+    <row r="991" spans="1:9" ht="82.8" x14ac:dyDescent="0.3">
+      <c r="A991" s="5" t="s">
+        <v>5426</v>
+      </c>
+      <c r="B991" s="8" t="s">
+        <v>4688</v>
+      </c>
+      <c r="C991" s="8" t="s">
+        <v>5297</v>
+      </c>
+      <c r="D991" s="8" t="s">
+        <v>5298</v>
+      </c>
+      <c r="E991" s="8" t="s">
+        <v>5299</v>
+      </c>
+      <c r="F991" s="8" t="s">
+        <v>5300</v>
+      </c>
+      <c r="G991" s="8" t="s">
+        <v>5301</v>
+      </c>
+      <c r="H991" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="I991" s="8" t="s">
+        <v>5302</v>
+      </c>
+    </row>
+    <row r="992" spans="1:9" ht="55.2" x14ac:dyDescent="0.3">
+      <c r="A992" s="5" t="s">
+        <v>5427</v>
+      </c>
+      <c r="B992" s="8" t="s">
+        <v>4701</v>
+      </c>
+      <c r="C992" s="8" t="s">
+        <v>5303</v>
+      </c>
+      <c r="D992" s="8" t="s">
+        <v>5304</v>
+      </c>
+      <c r="E992" s="8" t="s">
+        <v>5305</v>
+      </c>
+      <c r="F992" s="8" t="s">
+        <v>5306</v>
+      </c>
+      <c r="G992" s="8" t="s">
+        <v>5307</v>
+      </c>
+      <c r="H992" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="I992" s="8" t="s">
+        <v>5308</v>
+      </c>
+    </row>
+    <row r="993" spans="1:9" ht="55.2" x14ac:dyDescent="0.3">
+      <c r="A993" s="5" t="s">
+        <v>5427</v>
+      </c>
+      <c r="B993" s="8" t="s">
+        <v>4701</v>
+      </c>
+      <c r="C993" s="8" t="s">
+        <v>5309</v>
+      </c>
+      <c r="D993" s="8" t="s">
+        <v>5310</v>
+      </c>
+      <c r="E993" s="8" t="s">
+        <v>5311</v>
+      </c>
+      <c r="F993" s="8" t="s">
+        <v>5312</v>
+      </c>
+      <c r="G993" s="8" t="s">
+        <v>5313</v>
+      </c>
+      <c r="H993" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I993" s="8" t="s">
+        <v>5314</v>
+      </c>
+    </row>
+    <row r="994" spans="1:9" ht="55.2" x14ac:dyDescent="0.3">
+      <c r="A994" s="5" t="s">
+        <v>5427</v>
+      </c>
+      <c r="B994" s="8" t="s">
+        <v>4701</v>
+      </c>
+      <c r="C994" s="8" t="s">
+        <v>5315</v>
+      </c>
+      <c r="D994" s="8" t="s">
+        <v>5316</v>
+      </c>
+      <c r="E994" s="8" t="s">
+        <v>5317</v>
+      </c>
+      <c r="F994" s="8" t="s">
+        <v>5318</v>
+      </c>
+      <c r="G994" s="8" t="s">
+        <v>5319</v>
+      </c>
+      <c r="H994" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="I994" s="8" t="s">
+        <v>5320</v>
+      </c>
+    </row>
+    <row r="995" spans="1:9" ht="69" x14ac:dyDescent="0.3">
+      <c r="A995" s="5" t="s">
+        <v>5427</v>
+      </c>
+      <c r="B995" s="8" t="s">
+        <v>4720</v>
+      </c>
+      <c r="C995" s="8" t="s">
+        <v>5321</v>
+      </c>
+      <c r="D995" s="8" t="s">
+        <v>5322</v>
+      </c>
+      <c r="E995" s="8" t="s">
+        <v>5323</v>
+      </c>
+      <c r="F995" s="8" t="s">
+        <v>5324</v>
+      </c>
+      <c r="G995" s="8" t="s">
+        <v>5325</v>
+      </c>
+      <c r="H995" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="I995" s="8" t="s">
+        <v>5326</v>
+      </c>
+    </row>
+    <row r="996" spans="1:9" ht="55.2" x14ac:dyDescent="0.3">
+      <c r="A996" s="5" t="s">
+        <v>5427</v>
+      </c>
+      <c r="B996" s="8" t="s">
+        <v>4720</v>
+      </c>
+      <c r="C996" s="8" t="s">
+        <v>5327</v>
+      </c>
+      <c r="D996" s="8" t="s">
+        <v>5328</v>
+      </c>
+      <c r="E996" s="8" t="s">
+        <v>5329</v>
+      </c>
+      <c r="F996" s="8" t="s">
+        <v>5330</v>
+      </c>
+      <c r="G996" s="8" t="s">
+        <v>5331</v>
+      </c>
+      <c r="H996" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="I996" s="8" t="s">
+        <v>5332</v>
+      </c>
+    </row>
+    <row r="997" spans="1:9" ht="69" x14ac:dyDescent="0.3">
+      <c r="A997" s="5" t="s">
+        <v>5427</v>
+      </c>
+      <c r="B997" s="8" t="s">
+        <v>4720</v>
+      </c>
+      <c r="C997" s="8" t="s">
+        <v>5333</v>
+      </c>
+      <c r="D997" s="8" t="s">
+        <v>5334</v>
+      </c>
+      <c r="E997" s="8" t="s">
+        <v>5335</v>
+      </c>
+      <c r="F997" s="8" t="s">
+        <v>5336</v>
+      </c>
+      <c r="G997" s="8" t="s">
+        <v>5337</v>
+      </c>
+      <c r="H997" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="I997" s="8" t="s">
+        <v>5338</v>
+      </c>
+    </row>
+    <row r="998" spans="1:9" ht="55.2" x14ac:dyDescent="0.3">
+      <c r="A998" s="5" t="s">
+        <v>5427</v>
+      </c>
+      <c r="B998" s="8" t="s">
+        <v>4720</v>
+      </c>
+      <c r="C998" s="8" t="s">
+        <v>5339</v>
+      </c>
+      <c r="D998" s="8" t="s">
+        <v>5340</v>
+      </c>
+      <c r="E998" s="8" t="s">
+        <v>5341</v>
+      </c>
+      <c r="F998" s="8" t="s">
+        <v>5342</v>
+      </c>
+      <c r="G998" s="8" t="s">
+        <v>5343</v>
+      </c>
+      <c r="H998" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="I998" s="8" t="s">
+        <v>5344</v>
+      </c>
+    </row>
+    <row r="999" spans="1:9" ht="69" x14ac:dyDescent="0.3">
+      <c r="A999" s="5" t="s">
+        <v>5427</v>
+      </c>
+      <c r="B999" s="8" t="s">
+        <v>4745</v>
+      </c>
+      <c r="C999" s="8" t="s">
+        <v>5345</v>
+      </c>
+      <c r="D999" s="8" t="s">
+        <v>5346</v>
+      </c>
+      <c r="E999" s="8" t="s">
+        <v>5347</v>
+      </c>
+      <c r="F999" s="8" t="s">
+        <v>5348</v>
+      </c>
+      <c r="G999" s="8" t="s">
+        <v>5349</v>
+      </c>
+      <c r="H999" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="I999" s="8" t="s">
+        <v>5350</v>
+      </c>
+    </row>
+    <row r="1000" spans="1:9" ht="82.8" x14ac:dyDescent="0.3">
+      <c r="A1000" s="5" t="s">
+        <v>5427</v>
+      </c>
+      <c r="B1000" s="8" t="s">
+        <v>4745</v>
+      </c>
+      <c r="C1000" s="8" t="s">
+        <v>5351</v>
+      </c>
+      <c r="D1000" s="8" t="s">
+        <v>5352</v>
+      </c>
+      <c r="E1000" s="8" t="s">
+        <v>5353</v>
+      </c>
+      <c r="F1000" s="8" t="s">
+        <v>5354</v>
+      </c>
+      <c r="G1000" s="8" t="s">
+        <v>5355</v>
+      </c>
+      <c r="H1000" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="I1000" s="8" t="s">
+        <v>5356</v>
+      </c>
+    </row>
+    <row r="1001" spans="1:9" ht="55.2" x14ac:dyDescent="0.3">
+      <c r="A1001" s="5" t="s">
+        <v>5427</v>
+      </c>
+      <c r="B1001" s="8" t="s">
+        <v>4745</v>
+      </c>
+      <c r="C1001" s="8" t="s">
+        <v>5357</v>
+      </c>
+      <c r="D1001" s="8" t="s">
+        <v>5358</v>
+      </c>
+      <c r="E1001" s="8" t="s">
+        <v>5359</v>
+      </c>
+      <c r="F1001" s="8" t="s">
+        <v>5360</v>
+      </c>
+      <c r="G1001" s="8" t="s">
+        <v>5361</v>
+      </c>
+      <c r="H1001" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="I1001" s="8" t="s">
+        <v>5362</v>
+      </c>
+    </row>
+    <row r="1002" spans="1:9" ht="55.2" x14ac:dyDescent="0.3">
+      <c r="A1002" s="5" t="s">
+        <v>5427</v>
+      </c>
+      <c r="B1002" s="8" t="s">
+        <v>4764</v>
+      </c>
+      <c r="C1002" s="8" t="s">
+        <v>5363</v>
+      </c>
+      <c r="D1002" s="8" t="s">
+        <v>5364</v>
+      </c>
+      <c r="E1002" s="8" t="s">
+        <v>5365</v>
+      </c>
+      <c r="F1002" s="8" t="s">
+        <v>5366</v>
+      </c>
+      <c r="G1002" s="8" t="s">
+        <v>5367</v>
+      </c>
+      <c r="H1002" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="I1002" s="8" t="s">
+        <v>5368</v>
+      </c>
+    </row>
+    <row r="1003" spans="1:9" ht="69" x14ac:dyDescent="0.3">
+      <c r="A1003" s="5" t="s">
+        <v>5427</v>
+      </c>
+      <c r="B1003" s="8" t="s">
+        <v>4764</v>
+      </c>
+      <c r="C1003" s="8" t="s">
+        <v>5369</v>
+      </c>
+      <c r="D1003" s="8" t="s">
+        <v>5370</v>
+      </c>
+      <c r="E1003" s="8" t="s">
+        <v>5371</v>
+      </c>
+      <c r="F1003" s="8" t="s">
+        <v>5372</v>
+      </c>
+      <c r="G1003" s="8" t="s">
+        <v>5373</v>
+      </c>
+      <c r="H1003" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="I1003" s="8" t="s">
+        <v>5374</v>
+      </c>
+    </row>
+    <row r="1004" spans="1:9" ht="69" x14ac:dyDescent="0.3">
+      <c r="A1004" s="5" t="s">
+        <v>5427</v>
+      </c>
+      <c r="B1004" s="8" t="s">
+        <v>4777</v>
+      </c>
+      <c r="C1004" s="8" t="s">
+        <v>5375</v>
+      </c>
+      <c r="D1004" s="8" t="s">
+        <v>5376</v>
+      </c>
+      <c r="E1004" s="8" t="s">
+        <v>5377</v>
+      </c>
+      <c r="F1004" s="8" t="s">
+        <v>5378</v>
+      </c>
+      <c r="G1004" s="8" t="s">
+        <v>5379</v>
+      </c>
+      <c r="H1004" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="I1004" s="8" t="s">
+        <v>5380</v>
+      </c>
+    </row>
+    <row r="1005" spans="1:9" ht="55.2" x14ac:dyDescent="0.3">
+      <c r="A1005" s="5" t="s">
+        <v>5427</v>
+      </c>
+      <c r="B1005" s="8" t="s">
+        <v>4777</v>
+      </c>
+      <c r="C1005" s="8" t="s">
+        <v>5381</v>
+      </c>
+      <c r="D1005" s="8" t="s">
+        <v>5382</v>
+      </c>
+      <c r="E1005" s="8" t="s">
+        <v>5383</v>
+      </c>
+      <c r="F1005" s="8" t="s">
+        <v>5384</v>
+      </c>
+      <c r="G1005" s="8" t="s">
+        <v>5385</v>
+      </c>
+      <c r="H1005" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="I1005" s="8" t="s">
+        <v>5386</v>
+      </c>
+    </row>
+    <row r="1006" spans="1:9" ht="55.2" x14ac:dyDescent="0.3">
+      <c r="A1006" s="5" t="s">
+        <v>5427</v>
+      </c>
+      <c r="B1006" s="8" t="s">
+        <v>4777</v>
+      </c>
+      <c r="C1006" s="8" t="s">
+        <v>5387</v>
+      </c>
+      <c r="D1006" s="8" t="s">
+        <v>5388</v>
+      </c>
+      <c r="E1006" s="8" t="s">
+        <v>5389</v>
+      </c>
+      <c r="F1006" s="8" t="s">
+        <v>5390</v>
+      </c>
+      <c r="G1006" s="8" t="s">
+        <v>5391</v>
+      </c>
+      <c r="H1006" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="I1006" s="8" t="s">
+        <v>5392</v>
+      </c>
+    </row>
+    <row r="1007" spans="1:9" ht="69" x14ac:dyDescent="0.3">
+      <c r="A1007" s="5" t="s">
+        <v>5427</v>
+      </c>
+      <c r="B1007" s="8" t="s">
+        <v>4796</v>
+      </c>
+      <c r="C1007" s="8" t="s">
+        <v>5393</v>
+      </c>
+      <c r="D1007" s="8" t="s">
+        <v>5394</v>
+      </c>
+      <c r="E1007" s="8" t="s">
+        <v>5395</v>
+      </c>
+      <c r="F1007" s="8" t="s">
+        <v>5396</v>
+      </c>
+      <c r="G1007" s="8" t="s">
+        <v>5397</v>
+      </c>
+      <c r="H1007" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1007" s="8" t="s">
+        <v>5398</v>
+      </c>
+    </row>
+    <row r="1008" spans="1:9" ht="55.2" x14ac:dyDescent="0.3">
+      <c r="A1008" s="5" t="s">
+        <v>5427</v>
+      </c>
+      <c r="B1008" s="8" t="s">
+        <v>4796</v>
+      </c>
+      <c r="C1008" s="8" t="s">
+        <v>5399</v>
+      </c>
+      <c r="D1008" s="8" t="s">
+        <v>5400</v>
+      </c>
+      <c r="E1008" s="8" t="s">
+        <v>5401</v>
+      </c>
+      <c r="F1008" s="8" t="s">
+        <v>5402</v>
+      </c>
+      <c r="G1008" s="8" t="s">
+        <v>5403</v>
+      </c>
+      <c r="H1008" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="I1008" s="8" t="s">
+        <v>5404</v>
+      </c>
+    </row>
+    <row r="1009" spans="1:9" ht="55.2" x14ac:dyDescent="0.3">
+      <c r="A1009" s="5" t="s">
+        <v>5427</v>
+      </c>
+      <c r="B1009" s="8" t="s">
+        <v>4809</v>
+      </c>
+      <c r="C1009" s="8" t="s">
+        <v>5405</v>
+      </c>
+      <c r="D1009" s="8" t="s">
+        <v>5406</v>
+      </c>
+      <c r="E1009" s="8" t="s">
+        <v>5407</v>
+      </c>
+      <c r="F1009" s="8" t="s">
+        <v>5408</v>
+      </c>
+      <c r="G1009" s="8" t="s">
+        <v>5409</v>
+      </c>
+      <c r="H1009" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="I1009" s="8" t="s">
+        <v>5410</v>
+      </c>
+    </row>
+    <row r="1010" spans="1:9" ht="69" x14ac:dyDescent="0.3">
+      <c r="A1010" s="5" t="s">
+        <v>5427</v>
+      </c>
+      <c r="B1010" s="8" t="s">
+        <v>4816</v>
+      </c>
+      <c r="C1010" s="8" t="s">
+        <v>5411</v>
+      </c>
+      <c r="D1010" s="8" t="s">
+        <v>5412</v>
+      </c>
+      <c r="E1010" s="8" t="s">
+        <v>5413</v>
+      </c>
+      <c r="F1010" s="8" t="s">
+        <v>5414</v>
+      </c>
+      <c r="G1010" s="8" t="s">
+        <v>5415</v>
+      </c>
+      <c r="H1010" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I1010" s="8" t="s">
+        <v>5416</v>
+      </c>
+    </row>
+    <row r="1011" spans="1:9" ht="69" x14ac:dyDescent="0.3">
+      <c r="A1011" s="5" t="s">
+        <v>5427</v>
+      </c>
+      <c r="B1011" s="8" t="s">
+        <v>4823</v>
+      </c>
+      <c r="C1011" s="8" t="s">
+        <v>5417</v>
+      </c>
+      <c r="D1011" s="8" t="s">
+        <v>5418</v>
+      </c>
+      <c r="E1011" s="8" t="s">
+        <v>5419</v>
+      </c>
+      <c r="F1011" s="8" t="s">
+        <v>5420</v>
+      </c>
+      <c r="G1011" s="8" t="s">
+        <v>5421</v>
+      </c>
+      <c r="H1011" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="I1011" s="8" t="s">
+        <v>5422</v>
+      </c>
+    </row>
+    <row r="1012" spans="1:9" ht="69" x14ac:dyDescent="0.3">
+      <c r="A1012" s="5" t="s">
+        <v>5428</v>
+      </c>
+      <c r="B1012" s="9" t="s">
+        <v>4199</v>
+      </c>
+      <c r="C1012" s="9" t="s">
+        <v>5433</v>
+      </c>
+      <c r="D1012" s="9" t="s">
+        <v>5434</v>
+      </c>
+      <c r="E1012" s="9" t="s">
+        <v>5435</v>
+      </c>
+      <c r="F1012" s="9" t="s">
+        <v>5436</v>
+      </c>
+      <c r="G1012" s="9" t="s">
+        <v>5437</v>
+      </c>
+      <c r="H1012" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="I1012" s="9" t="s">
+        <v>5438</v>
+      </c>
+    </row>
+    <row r="1013" spans="1:9" ht="69" x14ac:dyDescent="0.3">
+      <c r="A1013" s="5" t="s">
+        <v>5428</v>
+      </c>
+      <c r="B1013" s="9" t="s">
+        <v>4199</v>
+      </c>
+      <c r="C1013" s="9" t="s">
+        <v>5439</v>
+      </c>
+      <c r="D1013" s="9" t="s">
+        <v>5440</v>
+      </c>
+      <c r="E1013" s="9" t="s">
+        <v>5441</v>
+      </c>
+      <c r="F1013" s="9" t="s">
+        <v>5442</v>
+      </c>
+      <c r="G1013" s="9" t="s">
+        <v>5443</v>
+      </c>
+      <c r="H1013" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="I1013" s="9" t="s">
+        <v>5444</v>
+      </c>
+    </row>
+    <row r="1014" spans="1:9" ht="55.2" x14ac:dyDescent="0.3">
+      <c r="A1014" s="5" t="s">
+        <v>5428</v>
+      </c>
+      <c r="B1014" s="9" t="s">
+        <v>4212</v>
+      </c>
+      <c r="C1014" s="9" t="s">
+        <v>5445</v>
+      </c>
+      <c r="D1014" s="9" t="s">
+        <v>5446</v>
+      </c>
+      <c r="E1014" s="9" t="s">
+        <v>5447</v>
+      </c>
+      <c r="F1014" s="9" t="s">
+        <v>5448</v>
+      </c>
+      <c r="G1014" s="9" t="s">
+        <v>5449</v>
+      </c>
+      <c r="H1014" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I1014" s="9" t="s">
+        <v>5450</v>
+      </c>
+    </row>
+    <row r="1015" spans="1:9" ht="55.2" x14ac:dyDescent="0.3">
+      <c r="A1015" s="5" t="s">
+        <v>5428</v>
+      </c>
+      <c r="B1015" s="9" t="s">
+        <v>4212</v>
+      </c>
+      <c r="C1015" s="9" t="s">
+        <v>5451</v>
+      </c>
+      <c r="D1015" s="9" t="s">
+        <v>5452</v>
+      </c>
+      <c r="E1015" s="9" t="s">
+        <v>5453</v>
+      </c>
+      <c r="F1015" s="9" t="s">
+        <v>5454</v>
+      </c>
+      <c r="G1015" s="9" t="s">
+        <v>5455</v>
+      </c>
+      <c r="H1015" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="I1015" s="9" t="s">
+        <v>5456</v>
+      </c>
+    </row>
+    <row r="1016" spans="1:9" ht="69" x14ac:dyDescent="0.3">
+      <c r="A1016" s="5" t="s">
+        <v>5428</v>
+      </c>
+      <c r="B1016" s="9" t="s">
+        <v>4225</v>
+      </c>
+      <c r="C1016" s="9" t="s">
+        <v>5457</v>
+      </c>
+      <c r="D1016" s="9" t="s">
+        <v>5458</v>
+      </c>
+      <c r="E1016" s="9" t="s">
+        <v>5459</v>
+      </c>
+      <c r="F1016" s="9" t="s">
+        <v>5460</v>
+      </c>
+      <c r="G1016" s="9" t="s">
+        <v>5461</v>
+      </c>
+      <c r="H1016" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="I1016" s="9" t="s">
+        <v>5462</v>
+      </c>
+    </row>
+    <row r="1017" spans="1:9" ht="69" x14ac:dyDescent="0.3">
+      <c r="A1017" s="5" t="s">
+        <v>5428</v>
+      </c>
+      <c r="B1017" s="9" t="s">
+        <v>4225</v>
+      </c>
+      <c r="C1017" s="9" t="s">
+        <v>5463</v>
+      </c>
+      <c r="D1017" s="9" t="s">
+        <v>5464</v>
+      </c>
+      <c r="E1017" s="9" t="s">
+        <v>5465</v>
+      </c>
+      <c r="F1017" s="9" t="s">
+        <v>5466</v>
+      </c>
+      <c r="G1017" s="9" t="s">
+        <v>5467</v>
+      </c>
+      <c r="H1017" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1017" s="9" t="s">
+        <v>5468</v>
+      </c>
+    </row>
+    <row r="1018" spans="1:9" ht="69" x14ac:dyDescent="0.3">
+      <c r="A1018" s="5" t="s">
+        <v>5429</v>
+      </c>
+      <c r="B1018" s="9" t="s">
+        <v>4238</v>
+      </c>
+      <c r="C1018" s="9" t="s">
+        <v>5469</v>
+      </c>
+      <c r="D1018" s="9" t="s">
+        <v>5470</v>
+      </c>
+      <c r="E1018" s="9" t="s">
+        <v>5471</v>
+      </c>
+      <c r="F1018" s="9" t="s">
+        <v>5472</v>
+      </c>
+      <c r="G1018" s="9" t="s">
+        <v>5473</v>
+      </c>
+      <c r="H1018" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I1018" s="9" t="s">
+        <v>5474</v>
+      </c>
+    </row>
+    <row r="1019" spans="1:9" ht="55.2" x14ac:dyDescent="0.3">
+      <c r="A1019" s="5" t="s">
+        <v>5429</v>
+      </c>
+      <c r="B1019" s="9" t="s">
+        <v>4238</v>
+      </c>
+      <c r="C1019" s="9" t="s">
+        <v>5475</v>
+      </c>
+      <c r="D1019" s="9" t="s">
+        <v>5476</v>
+      </c>
+      <c r="E1019" s="9" t="s">
+        <v>5477</v>
+      </c>
+      <c r="F1019" s="9" t="s">
+        <v>5478</v>
+      </c>
+      <c r="G1019" s="9" t="s">
+        <v>5479</v>
+      </c>
+      <c r="H1019" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I1019" s="9" t="s">
+        <v>5480</v>
+      </c>
+    </row>
+    <row r="1020" spans="1:9" ht="69" x14ac:dyDescent="0.3">
+      <c r="A1020" s="5" t="s">
+        <v>5429</v>
+      </c>
+      <c r="B1020" s="9" t="s">
+        <v>4238</v>
+      </c>
+      <c r="C1020" s="9" t="s">
+        <v>5481</v>
+      </c>
+      <c r="D1020" s="9" t="s">
+        <v>5482</v>
+      </c>
+      <c r="E1020" s="9" t="s">
+        <v>5483</v>
+      </c>
+      <c r="F1020" s="9" t="s">
+        <v>5484</v>
+      </c>
+      <c r="G1020" s="9" t="s">
+        <v>5485</v>
+      </c>
+      <c r="H1020" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1020" s="9" t="s">
+        <v>5486</v>
+      </c>
+    </row>
+    <row r="1021" spans="1:9" ht="69" x14ac:dyDescent="0.3">
+      <c r="A1021" s="5" t="s">
+        <v>5429</v>
+      </c>
+      <c r="B1021" s="9" t="s">
+        <v>4238</v>
+      </c>
+      <c r="C1021" s="9" t="s">
+        <v>5487</v>
+      </c>
+      <c r="D1021" s="9" t="s">
+        <v>5488</v>
+      </c>
+      <c r="E1021" s="9" t="s">
+        <v>5489</v>
+      </c>
+      <c r="F1021" s="9" t="s">
+        <v>5490</v>
+      </c>
+      <c r="G1021" s="9" t="s">
+        <v>5491</v>
+      </c>
+      <c r="H1021" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1021" s="9" t="s">
+        <v>5492</v>
+      </c>
+    </row>
+    <row r="1022" spans="1:9" ht="69" x14ac:dyDescent="0.3">
+      <c r="A1022" s="5" t="s">
+        <v>5429</v>
+      </c>
+      <c r="B1022" s="9" t="s">
+        <v>4263</v>
+      </c>
+      <c r="C1022" s="9" t="s">
+        <v>5493</v>
+      </c>
+      <c r="D1022" s="9" t="s">
+        <v>5494</v>
+      </c>
+      <c r="E1022" s="9" t="s">
+        <v>5495</v>
+      </c>
+      <c r="F1022" s="9" t="s">
+        <v>5496</v>
+      </c>
+      <c r="G1022" s="9" t="s">
+        <v>5497</v>
+      </c>
+      <c r="H1022" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="I1022" s="9" t="s">
+        <v>5498</v>
+      </c>
+    </row>
+    <row r="1023" spans="1:9" ht="69" x14ac:dyDescent="0.3">
+      <c r="A1023" s="5" t="s">
+        <v>5429</v>
+      </c>
+      <c r="B1023" s="9" t="s">
+        <v>4263</v>
+      </c>
+      <c r="C1023" s="9" t="s">
+        <v>5499</v>
+      </c>
+      <c r="D1023" s="9" t="s">
+        <v>5500</v>
+      </c>
+      <c r="E1023" s="9" t="s">
+        <v>5501</v>
+      </c>
+      <c r="F1023" s="9" t="s">
+        <v>5502</v>
+      </c>
+      <c r="G1023" s="9" t="s">
+        <v>5503</v>
+      </c>
+      <c r="H1023" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="I1023" s="9" t="s">
+        <v>5504</v>
+      </c>
+    </row>
+    <row r="1024" spans="1:9" ht="69" x14ac:dyDescent="0.3">
+      <c r="A1024" s="5" t="s">
+        <v>5429</v>
+      </c>
+      <c r="B1024" s="9" t="s">
+        <v>4263</v>
+      </c>
+      <c r="C1024" s="9" t="s">
+        <v>5505</v>
+      </c>
+      <c r="D1024" s="9" t="s">
+        <v>5506</v>
+      </c>
+      <c r="E1024" s="9" t="s">
+        <v>5507</v>
+      </c>
+      <c r="F1024" s="9" t="s">
+        <v>5508</v>
+      </c>
+      <c r="G1024" s="9" t="s">
+        <v>5509</v>
+      </c>
+      <c r="H1024" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="I1024" s="9" t="s">
+        <v>5510</v>
+      </c>
+    </row>
+    <row r="1025" spans="1:9" ht="69" x14ac:dyDescent="0.3">
+      <c r="A1025" s="5" t="s">
+        <v>5429</v>
+      </c>
+      <c r="B1025" s="9" t="s">
+        <v>4263</v>
+      </c>
+      <c r="C1025" s="9" t="s">
+        <v>5511</v>
+      </c>
+      <c r="D1025" s="9" t="s">
+        <v>5512</v>
+      </c>
+      <c r="E1025" s="9" t="s">
+        <v>5513</v>
+      </c>
+      <c r="F1025" s="9" t="s">
+        <v>5514</v>
+      </c>
+      <c r="G1025" s="9" t="s">
+        <v>5515</v>
+      </c>
+      <c r="H1025" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="I1025" s="9" t="s">
+        <v>5516</v>
+      </c>
+    </row>
+    <row r="1026" spans="1:9" ht="55.2" x14ac:dyDescent="0.3">
+      <c r="A1026" s="5" t="s">
+        <v>5429</v>
+      </c>
+      <c r="B1026" s="9" t="s">
+        <v>4288</v>
+      </c>
+      <c r="C1026" s="9" t="s">
+        <v>5517</v>
+      </c>
+      <c r="D1026" s="9" t="s">
+        <v>5518</v>
+      </c>
+      <c r="E1026" s="9" t="s">
+        <v>4494</v>
+      </c>
+      <c r="F1026" s="9" t="s">
+        <v>4449</v>
+      </c>
+      <c r="G1026" s="9" t="s">
+        <v>4452</v>
+      </c>
+      <c r="H1026" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1026" s="9" t="s">
+        <v>5519</v>
+      </c>
+    </row>
+    <row r="1027" spans="1:9" ht="55.2" x14ac:dyDescent="0.3">
+      <c r="A1027" s="5" t="s">
+        <v>5429</v>
+      </c>
+      <c r="B1027" s="9" t="s">
+        <v>4288</v>
+      </c>
+      <c r="C1027" s="9" t="s">
+        <v>5520</v>
+      </c>
+      <c r="D1027" s="9" t="s">
+        <v>5521</v>
+      </c>
+      <c r="E1027" s="9" t="s">
+        <v>5522</v>
+      </c>
+      <c r="F1027" s="9" t="s">
+        <v>5523</v>
+      </c>
+      <c r="G1027" s="9" t="s">
+        <v>5524</v>
+      </c>
+      <c r="H1027" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1027" s="9" t="s">
+        <v>5525</v>
+      </c>
+    </row>
+    <row r="1028" spans="1:9" ht="55.2" x14ac:dyDescent="0.3">
+      <c r="A1028" s="5" t="s">
+        <v>5429</v>
+      </c>
+      <c r="B1028" s="9" t="s">
+        <v>4288</v>
+      </c>
+      <c r="C1028" s="9" t="s">
+        <v>5526</v>
+      </c>
+      <c r="D1028" s="9" t="s">
+        <v>5527</v>
+      </c>
+      <c r="E1028" s="9" t="s">
+        <v>5528</v>
+      </c>
+      <c r="F1028" s="9" t="s">
+        <v>5529</v>
+      </c>
+      <c r="G1028" s="9" t="s">
+        <v>5530</v>
+      </c>
+      <c r="H1028" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I1028" s="9" t="s">
+        <v>5531</v>
+      </c>
+    </row>
+    <row r="1029" spans="1:9" ht="55.2" x14ac:dyDescent="0.3">
+      <c r="A1029" s="5" t="s">
+        <v>5429</v>
+      </c>
+      <c r="B1029" s="9" t="s">
+        <v>4288</v>
+      </c>
+      <c r="C1029" s="9" t="s">
+        <v>5532</v>
+      </c>
+      <c r="D1029" s="9" t="s">
+        <v>5533</v>
+      </c>
+      <c r="E1029" s="9" t="s">
+        <v>5534</v>
+      </c>
+      <c r="F1029" s="9" t="s">
+        <v>5535</v>
+      </c>
+      <c r="G1029" s="9" t="s">
+        <v>5536</v>
+      </c>
+      <c r="H1029" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1029" s="9" t="s">
+        <v>5537</v>
+      </c>
+    </row>
+    <row r="1030" spans="1:9" ht="69" x14ac:dyDescent="0.3">
+      <c r="A1030" s="5" t="s">
+        <v>5429</v>
+      </c>
+      <c r="B1030" s="9" t="s">
+        <v>4288</v>
+      </c>
+      <c r="C1030" s="9" t="s">
+        <v>5538</v>
+      </c>
+      <c r="D1030" s="9" t="s">
+        <v>5539</v>
+      </c>
+      <c r="E1030" s="9" t="s">
+        <v>5540</v>
+      </c>
+      <c r="F1030" s="9" t="s">
+        <v>5541</v>
+      </c>
+      <c r="G1030" s="9" t="s">
+        <v>5542</v>
+      </c>
+      <c r="H1030" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1030" s="9" t="s">
+        <v>5543</v>
+      </c>
+    </row>
+    <row r="1031" spans="1:9" ht="55.2" x14ac:dyDescent="0.3">
+      <c r="A1031" s="5" t="s">
+        <v>5429</v>
+      </c>
+      <c r="B1031" s="9" t="s">
+        <v>4317</v>
+      </c>
+      <c r="C1031" s="9" t="s">
+        <v>5544</v>
+      </c>
+      <c r="D1031" s="9" t="s">
+        <v>5545</v>
+      </c>
+      <c r="E1031" s="9" t="s">
+        <v>5546</v>
+      </c>
+      <c r="F1031" s="9" t="s">
+        <v>5547</v>
+      </c>
+      <c r="G1031" s="9" t="s">
+        <v>5548</v>
+      </c>
+      <c r="H1031" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I1031" s="9" t="s">
+        <v>5549</v>
+      </c>
+    </row>
+    <row r="1032" spans="1:9" ht="55.2" x14ac:dyDescent="0.3">
+      <c r="A1032" s="5" t="s">
+        <v>5429</v>
+      </c>
+      <c r="B1032" s="9" t="s">
+        <v>4317</v>
+      </c>
+      <c r="C1032" s="9" t="s">
+        <v>5550</v>
+      </c>
+      <c r="D1032" s="9" t="s">
+        <v>5551</v>
+      </c>
+      <c r="E1032" s="9" t="s">
+        <v>5552</v>
+      </c>
+      <c r="F1032" s="9" t="s">
+        <v>5553</v>
+      </c>
+      <c r="G1032" s="9" t="s">
+        <v>5554</v>
+      </c>
+      <c r="H1032" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="I1032" s="9" t="s">
+        <v>5555</v>
+      </c>
+    </row>
+    <row r="1033" spans="1:9" ht="69" x14ac:dyDescent="0.3">
+      <c r="A1033" s="5" t="s">
+        <v>5429</v>
+      </c>
+      <c r="B1033" s="9" t="s">
+        <v>4317</v>
+      </c>
+      <c r="C1033" s="9" t="s">
+        <v>5556</v>
+      </c>
+      <c r="D1033" s="9" t="s">
+        <v>5557</v>
+      </c>
+      <c r="E1033" s="9" t="s">
+        <v>5558</v>
+      </c>
+      <c r="F1033" s="9" t="s">
+        <v>5559</v>
+      </c>
+      <c r="G1033" s="9" t="s">
+        <v>5560</v>
+      </c>
+      <c r="H1033" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I1033" s="9" t="s">
+        <v>5561</v>
+      </c>
+    </row>
+    <row r="1034" spans="1:9" ht="69" x14ac:dyDescent="0.3">
+      <c r="A1034" s="5" t="s">
+        <v>5429</v>
+      </c>
+      <c r="B1034" s="9" t="s">
+        <v>4317</v>
+      </c>
+      <c r="C1034" s="9" t="s">
+        <v>5562</v>
+      </c>
+      <c r="D1034" s="9" t="s">
+        <v>5563</v>
+      </c>
+      <c r="E1034" s="9" t="s">
+        <v>5564</v>
+      </c>
+      <c r="F1034" s="9" t="s">
+        <v>5565</v>
+      </c>
+      <c r="G1034" s="9" t="s">
+        <v>5566</v>
+      </c>
+      <c r="H1034" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="I1034" s="9" t="s">
+        <v>5567</v>
+      </c>
+    </row>
+    <row r="1035" spans="1:9" ht="55.2" x14ac:dyDescent="0.3">
+      <c r="A1035" s="5" t="s">
+        <v>5429</v>
+      </c>
+      <c r="B1035" s="9" t="s">
+        <v>4317</v>
+      </c>
+      <c r="C1035" s="9" t="s">
+        <v>5568</v>
+      </c>
+      <c r="D1035" s="9" t="s">
+        <v>5569</v>
+      </c>
+      <c r="E1035" s="9" t="s">
+        <v>5570</v>
+      </c>
+      <c r="F1035" s="9" t="s">
+        <v>5571</v>
+      </c>
+      <c r="G1035" s="9" t="s">
+        <v>5572</v>
+      </c>
+      <c r="H1035" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1035" s="9" t="s">
+        <v>5573</v>
+      </c>
+    </row>
+    <row r="1036" spans="1:9" ht="55.2" x14ac:dyDescent="0.3">
+      <c r="A1036" s="5" t="s">
+        <v>5429</v>
+      </c>
+      <c r="B1036" s="9" t="s">
+        <v>4317</v>
+      </c>
+      <c r="C1036" s="9" t="s">
+        <v>5574</v>
+      </c>
+      <c r="D1036" s="9" t="s">
+        <v>5575</v>
+      </c>
+      <c r="E1036" s="9" t="s">
+        <v>5576</v>
+      </c>
+      <c r="F1036" s="9" t="s">
+        <v>5577</v>
+      </c>
+      <c r="G1036" s="9" t="s">
+        <v>5578</v>
+      </c>
+      <c r="H1036" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="I1036" s="9" t="s">
+        <v>5579</v>
+      </c>
+    </row>
+    <row r="1037" spans="1:9" ht="41.4" x14ac:dyDescent="0.3">
+      <c r="A1037" s="5" t="s">
+        <v>5429</v>
+      </c>
+      <c r="B1037" s="9" t="s">
+        <v>4317</v>
+      </c>
+      <c r="C1037" s="9" t="s">
+        <v>5580</v>
+      </c>
+      <c r="D1037" s="9" t="s">
+        <v>5581</v>
+      </c>
+      <c r="E1037" s="9" t="s">
+        <v>5582</v>
+      </c>
+      <c r="F1037" s="9" t="s">
+        <v>5583</v>
+      </c>
+      <c r="G1037" s="9" t="s">
+        <v>5584</v>
+      </c>
+      <c r="H1037" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I1037" s="9" t="s">
+        <v>5585</v>
+      </c>
+    </row>
+    <row r="1038" spans="1:9" ht="82.8" x14ac:dyDescent="0.3">
+      <c r="A1038" s="5" t="s">
+        <v>5429</v>
+      </c>
+      <c r="B1038" s="9" t="s">
+        <v>4359</v>
+      </c>
+      <c r="C1038" s="9" t="s">
+        <v>5586</v>
+      </c>
+      <c r="D1038" s="9" t="s">
+        <v>5587</v>
+      </c>
+      <c r="E1038" s="9" t="s">
+        <v>5588</v>
+      </c>
+      <c r="F1038" s="9" t="s">
+        <v>5589</v>
+      </c>
+      <c r="G1038" s="9" t="s">
+        <v>5590</v>
+      </c>
+      <c r="H1038" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="I1038" s="9" t="s">
+        <v>5591</v>
+      </c>
+    </row>
+    <row r="1039" spans="1:9" ht="69" x14ac:dyDescent="0.3">
+      <c r="A1039" s="5" t="s">
+        <v>5429</v>
+      </c>
+      <c r="B1039" s="9" t="s">
+        <v>4359</v>
+      </c>
+      <c r="C1039" s="9" t="s">
+        <v>5592</v>
+      </c>
+      <c r="D1039" s="9" t="s">
+        <v>5593</v>
+      </c>
+      <c r="E1039" s="9" t="s">
+        <v>5594</v>
+      </c>
+      <c r="F1039" s="9" t="s">
+        <v>5595</v>
+      </c>
+      <c r="G1039" s="9" t="s">
+        <v>5596</v>
+      </c>
+      <c r="H1039" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I1039" s="9" t="s">
+        <v>5597</v>
+      </c>
+    </row>
+    <row r="1040" spans="1:9" ht="69" x14ac:dyDescent="0.3">
+      <c r="A1040" s="5" t="s">
+        <v>5429</v>
+      </c>
+      <c r="B1040" s="9" t="s">
+        <v>4359</v>
+      </c>
+      <c r="C1040" s="9" t="s">
+        <v>5598</v>
+      </c>
+      <c r="D1040" s="9" t="s">
+        <v>5599</v>
+      </c>
+      <c r="E1040" s="9" t="s">
+        <v>5600</v>
+      </c>
+      <c r="F1040" s="9" t="s">
+        <v>5601</v>
+      </c>
+      <c r="G1040" s="9" t="s">
+        <v>5602</v>
+      </c>
+      <c r="H1040" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="I1040" s="9" t="s">
+        <v>5603</v>
+      </c>
+    </row>
+    <row r="1041" spans="1:9" ht="69" x14ac:dyDescent="0.3">
+      <c r="A1041" s="5" t="s">
+        <v>5429</v>
+      </c>
+      <c r="B1041" s="9" t="s">
+        <v>4378</v>
+      </c>
+      <c r="C1041" s="9" t="s">
+        <v>5604</v>
+      </c>
+      <c r="D1041" s="9" t="s">
+        <v>5605</v>
+      </c>
+      <c r="E1041" s="9" t="s">
+        <v>5606</v>
+      </c>
+      <c r="F1041" s="9" t="s">
+        <v>5607</v>
+      </c>
+      <c r="G1041" s="9" t="s">
+        <v>5608</v>
+      </c>
+      <c r="H1041" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="I1041" s="9" t="s">
+        <v>5609</v>
+      </c>
+    </row>
+    <row r="1042" spans="1:9" ht="69" x14ac:dyDescent="0.3">
+      <c r="A1042" s="5" t="s">
+        <v>5429</v>
+      </c>
+      <c r="B1042" s="9" t="s">
+        <v>4378</v>
+      </c>
+      <c r="C1042" s="9" t="s">
+        <v>5610</v>
+      </c>
+      <c r="D1042" s="9" t="s">
+        <v>5611</v>
+      </c>
+      <c r="E1042" s="9" t="s">
+        <v>5612</v>
+      </c>
+      <c r="F1042" s="9" t="s">
+        <v>5613</v>
+      </c>
+      <c r="G1042" s="9" t="s">
+        <v>5614</v>
+      </c>
+      <c r="H1042" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1042" s="9" t="s">
+        <v>5615</v>
+      </c>
+    </row>
+    <row r="1043" spans="1:9" ht="69" x14ac:dyDescent="0.3">
+      <c r="A1043" s="5" t="s">
+        <v>5429</v>
+      </c>
+      <c r="B1043" s="9" t="s">
+        <v>4378</v>
+      </c>
+      <c r="C1043" s="9" t="s">
+        <v>5616</v>
+      </c>
+      <c r="D1043" s="9" t="s">
+        <v>5617</v>
+      </c>
+      <c r="E1043" s="9" t="s">
+        <v>5618</v>
+      </c>
+      <c r="F1043" s="9" t="s">
+        <v>5619</v>
+      </c>
+      <c r="G1043" s="9" t="s">
+        <v>5620</v>
+      </c>
+      <c r="H1043" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1043" s="9" t="s">
+        <v>5621</v>
+      </c>
+    </row>
+    <row r="1044" spans="1:9" ht="96.6" x14ac:dyDescent="0.3">
+      <c r="A1044" s="5" t="s">
+        <v>5429</v>
+      </c>
+      <c r="B1044" s="9" t="s">
+        <v>4378</v>
+      </c>
+      <c r="C1044" s="9" t="s">
+        <v>5622</v>
+      </c>
+      <c r="D1044" s="9" t="s">
+        <v>5623</v>
+      </c>
+      <c r="E1044" s="9" t="s">
+        <v>5624</v>
+      </c>
+      <c r="F1044" s="9" t="s">
+        <v>5625</v>
+      </c>
+      <c r="G1044" s="9" t="s">
+        <v>5626</v>
+      </c>
+      <c r="H1044" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="I1044" s="9" t="s">
+        <v>5627</v>
+      </c>
+    </row>
+    <row r="1045" spans="1:9" ht="55.2" x14ac:dyDescent="0.3">
+      <c r="A1045" s="5" t="s">
+        <v>5429</v>
+      </c>
+      <c r="B1045" s="9" t="s">
+        <v>4403</v>
+      </c>
+      <c r="C1045" s="9" t="s">
+        <v>5628</v>
+      </c>
+      <c r="D1045" s="9" t="s">
+        <v>5629</v>
+      </c>
+      <c r="E1045" s="9" t="s">
+        <v>5630</v>
+      </c>
+      <c r="F1045" s="9" t="s">
+        <v>5631</v>
+      </c>
+      <c r="G1045" s="9" t="s">
+        <v>5632</v>
+      </c>
+      <c r="H1045" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1045" s="9" t="s">
+        <v>5633</v>
+      </c>
+    </row>
+    <row r="1046" spans="1:9" ht="55.2" x14ac:dyDescent="0.3">
+      <c r="A1046" s="5" t="s">
+        <v>5429</v>
+      </c>
+      <c r="B1046" s="9" t="s">
+        <v>4403</v>
+      </c>
+      <c r="C1046" s="9" t="s">
+        <v>5634</v>
+      </c>
+      <c r="D1046" s="9" t="s">
+        <v>5635</v>
+      </c>
+      <c r="E1046" s="9" t="s">
+        <v>5636</v>
+      </c>
+      <c r="F1046" s="9" t="s">
+        <v>5637</v>
+      </c>
+      <c r="G1046" s="9" t="s">
+        <v>5638</v>
+      </c>
+      <c r="H1046" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I1046" s="9" t="s">
+        <v>5639</v>
+      </c>
+    </row>
+    <row r="1047" spans="1:9" ht="69" x14ac:dyDescent="0.3">
+      <c r="A1047" s="5" t="s">
+        <v>5429</v>
+      </c>
+      <c r="B1047" s="9" t="s">
+        <v>4403</v>
+      </c>
+      <c r="C1047" s="9" t="s">
+        <v>5640</v>
+      </c>
+      <c r="D1047" s="9" t="s">
+        <v>5641</v>
+      </c>
+      <c r="E1047" s="9" t="s">
+        <v>5642</v>
+      </c>
+      <c r="F1047" s="9" t="s">
+        <v>5643</v>
+      </c>
+      <c r="G1047" s="9" t="s">
+        <v>5644</v>
+      </c>
+      <c r="H1047" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1047" s="9" t="s">
+        <v>5645</v>
+      </c>
+    </row>
+    <row r="1048" spans="1:9" ht="69" x14ac:dyDescent="0.3">
+      <c r="A1048" s="5" t="s">
+        <v>5429</v>
+      </c>
+      <c r="B1048" s="9" t="s">
+        <v>4403</v>
+      </c>
+      <c r="C1048" s="9" t="s">
+        <v>5646</v>
+      </c>
+      <c r="D1048" s="9" t="s">
+        <v>5647</v>
+      </c>
+      <c r="E1048" s="9" t="s">
+        <v>5648</v>
+      </c>
+      <c r="F1048" s="9" t="s">
+        <v>5649</v>
+      </c>
+      <c r="G1048" s="9" t="s">
+        <v>5650</v>
+      </c>
+      <c r="H1048" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1048" s="9" t="s">
+        <v>5651</v>
+      </c>
+    </row>
+    <row r="1049" spans="1:9" ht="69" x14ac:dyDescent="0.3">
+      <c r="A1049" s="5" t="s">
+        <v>5429</v>
+      </c>
+      <c r="B1049" s="9" t="s">
+        <v>4403</v>
+      </c>
+      <c r="C1049" s="9" t="s">
+        <v>5652</v>
+      </c>
+      <c r="D1049" s="9" t="s">
+        <v>5653</v>
+      </c>
+      <c r="E1049" s="9" t="s">
+        <v>5654</v>
+      </c>
+      <c r="F1049" s="9" t="s">
+        <v>5655</v>
+      </c>
+      <c r="G1049" s="9" t="s">
+        <v>5656</v>
+      </c>
+      <c r="H1049" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="I1049" s="9" t="s">
+        <v>5657</v>
+      </c>
+    </row>
+    <row r="1050" spans="1:9" ht="55.2" x14ac:dyDescent="0.3">
+      <c r="A1050" s="5" t="s">
+        <v>5429</v>
+      </c>
+      <c r="B1050" s="9" t="s">
+        <v>4403</v>
+      </c>
+      <c r="C1050" s="9" t="s">
+        <v>5658</v>
+      </c>
+      <c r="D1050" s="9" t="s">
+        <v>5659</v>
+      </c>
+      <c r="E1050" s="9" t="s">
+        <v>5660</v>
+      </c>
+      <c r="F1050" s="9" t="s">
+        <v>5661</v>
+      </c>
+      <c r="G1050" s="9" t="s">
+        <v>5662</v>
+      </c>
+      <c r="H1050" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="I1050" s="9" t="s">
+        <v>5663</v>
+      </c>
+    </row>
+    <row r="1051" spans="1:9" ht="55.2" x14ac:dyDescent="0.3">
+      <c r="A1051" s="5" t="s">
+        <v>5429</v>
+      </c>
+      <c r="B1051" s="9" t="s">
+        <v>4439</v>
+      </c>
+      <c r="C1051" s="9" t="s">
+        <v>5664</v>
+      </c>
+      <c r="D1051" s="9" t="s">
+        <v>5665</v>
+      </c>
+      <c r="E1051" s="9" t="s">
+        <v>5666</v>
+      </c>
+      <c r="F1051" s="9" t="s">
+        <v>5667</v>
+      </c>
+      <c r="G1051" s="9" t="s">
+        <v>5668</v>
+      </c>
+      <c r="H1051" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1051" s="9" t="s">
+        <v>5669</v>
+      </c>
+    </row>
+    <row r="1052" spans="1:9" ht="69" x14ac:dyDescent="0.3">
+      <c r="A1052" s="5" t="s">
+        <v>5429</v>
+      </c>
+      <c r="B1052" s="9" t="s">
+        <v>4439</v>
+      </c>
+      <c r="C1052" s="9" t="s">
+        <v>5670</v>
+      </c>
+      <c r="D1052" s="9" t="s">
+        <v>5671</v>
+      </c>
+      <c r="E1052" s="9" t="s">
+        <v>5672</v>
+      </c>
+      <c r="F1052" s="9" t="s">
+        <v>5673</v>
+      </c>
+      <c r="G1052" s="9" t="s">
+        <v>5674</v>
+      </c>
+      <c r="H1052" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I1052" s="9" t="s">
+        <v>5675</v>
+      </c>
+    </row>
+    <row r="1053" spans="1:9" ht="41.4" x14ac:dyDescent="0.3">
+      <c r="A1053" s="5" t="s">
+        <v>5429</v>
+      </c>
+      <c r="B1053" s="9" t="s">
+        <v>4439</v>
+      </c>
+      <c r="C1053" s="9" t="s">
+        <v>5676</v>
+      </c>
+      <c r="D1053" s="9" t="s">
+        <v>5677</v>
+      </c>
+      <c r="E1053" s="9" t="s">
+        <v>5678</v>
+      </c>
+      <c r="F1053" s="9" t="s">
+        <v>5679</v>
+      </c>
+      <c r="G1053" s="9" t="s">
+        <v>5680</v>
+      </c>
+      <c r="H1053" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I1053" s="9" t="s">
+        <v>5681</v>
+      </c>
+    </row>
+    <row r="1054" spans="1:9" ht="55.2" x14ac:dyDescent="0.3">
+      <c r="A1054" s="5" t="s">
+        <v>5429</v>
+      </c>
+      <c r="B1054" s="9" t="s">
+        <v>4439</v>
+      </c>
+      <c r="C1054" s="9" t="s">
+        <v>5682</v>
+      </c>
+      <c r="D1054" s="9" t="s">
+        <v>5683</v>
+      </c>
+      <c r="E1054" s="9" t="s">
+        <v>5684</v>
+      </c>
+      <c r="F1054" s="9" t="s">
+        <v>5685</v>
+      </c>
+      <c r="G1054" s="9" t="s">
+        <v>5686</v>
+      </c>
+      <c r="H1054" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="I1054" s="9" t="s">
+        <v>5687</v>
+      </c>
+    </row>
+    <row r="1055" spans="1:9" ht="55.2" x14ac:dyDescent="0.3">
+      <c r="A1055" s="5" t="s">
+        <v>5429</v>
+      </c>
+      <c r="B1055" s="9" t="s">
+        <v>4439</v>
+      </c>
+      <c r="C1055" s="9" t="s">
+        <v>5688</v>
+      </c>
+      <c r="D1055" s="9" t="s">
+        <v>5689</v>
+      </c>
+      <c r="E1055" s="9" t="s">
+        <v>5690</v>
+      </c>
+      <c r="F1055" s="9" t="s">
+        <v>5691</v>
+      </c>
+      <c r="G1055" s="9" t="s">
+        <v>5692</v>
+      </c>
+      <c r="H1055" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="I1055" s="9" t="s">
+        <v>5693</v>
+      </c>
+    </row>
+    <row r="1056" spans="1:9" ht="55.2" x14ac:dyDescent="0.3">
+      <c r="A1056" s="5" t="s">
+        <v>5429</v>
+      </c>
+      <c r="B1056" s="9" t="s">
+        <v>4468</v>
+      </c>
+      <c r="C1056" s="9" t="s">
+        <v>5694</v>
+      </c>
+      <c r="D1056" s="9" t="s">
+        <v>5695</v>
+      </c>
+      <c r="E1056" s="9" t="s">
+        <v>5696</v>
+      </c>
+      <c r="F1056" s="9" t="s">
+        <v>5697</v>
+      </c>
+      <c r="G1056" s="9" t="s">
+        <v>5698</v>
+      </c>
+      <c r="H1056" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="I1056" s="9" t="s">
+        <v>5699</v>
+      </c>
+    </row>
+    <row r="1057" spans="1:9" ht="69" x14ac:dyDescent="0.3">
+      <c r="A1057" s="5" t="s">
+        <v>5429</v>
+      </c>
+      <c r="B1057" s="9" t="s">
+        <v>4468</v>
+      </c>
+      <c r="C1057" s="9" t="s">
+        <v>5700</v>
+      </c>
+      <c r="D1057" s="9" t="s">
+        <v>5701</v>
+      </c>
+      <c r="E1057" s="9" t="s">
+        <v>5702</v>
+      </c>
+      <c r="F1057" s="9" t="s">
+        <v>5703</v>
+      </c>
+      <c r="G1057" s="9" t="s">
+        <v>5704</v>
+      </c>
+      <c r="H1057" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="I1057" s="9" t="s">
+        <v>5705</v>
+      </c>
+    </row>
+    <row r="1058" spans="1:9" ht="69" x14ac:dyDescent="0.3">
+      <c r="A1058" s="5" t="s">
+        <v>5429</v>
+      </c>
+      <c r="B1058" s="9" t="s">
+        <v>4468</v>
+      </c>
+      <c r="C1058" s="9" t="s">
+        <v>5706</v>
+      </c>
+      <c r="D1058" s="9" t="s">
+        <v>5707</v>
+      </c>
+      <c r="E1058" s="9" t="s">
+        <v>5708</v>
+      </c>
+      <c r="F1058" s="9" t="s">
+        <v>5709</v>
+      </c>
+      <c r="G1058" s="9" t="s">
+        <v>5710</v>
+      </c>
+      <c r="H1058" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1058" s="9" t="s">
+        <v>5711</v>
+      </c>
+    </row>
+    <row r="1059" spans="1:9" ht="69" x14ac:dyDescent="0.3">
+      <c r="A1059" s="5" t="s">
+        <v>5429</v>
+      </c>
+      <c r="B1059" s="9" t="s">
+        <v>4486</v>
+      </c>
+      <c r="C1059" s="9" t="s">
+        <v>5712</v>
+      </c>
+      <c r="D1059" s="9" t="s">
+        <v>5713</v>
+      </c>
+      <c r="E1059" s="9" t="s">
+        <v>5714</v>
+      </c>
+      <c r="F1059" s="9" t="s">
+        <v>5715</v>
+      </c>
+      <c r="G1059" s="9" t="s">
+        <v>5716</v>
+      </c>
+      <c r="H1059" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="I1059" s="9" t="s">
+        <v>5717</v>
+      </c>
+    </row>
+    <row r="1060" spans="1:9" ht="55.2" x14ac:dyDescent="0.3">
+      <c r="A1060" s="5" t="s">
+        <v>5429</v>
+      </c>
+      <c r="B1060" s="9" t="s">
+        <v>4486</v>
+      </c>
+      <c r="C1060" s="9" t="s">
+        <v>5718</v>
+      </c>
+      <c r="D1060" s="9" t="s">
+        <v>5719</v>
+      </c>
+      <c r="E1060" s="9" t="s">
+        <v>4494</v>
+      </c>
+      <c r="F1060" s="9" t="s">
+        <v>5518</v>
+      </c>
+      <c r="G1060" s="9" t="s">
+        <v>5720</v>
+      </c>
+      <c r="H1060" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I1060" s="9" t="s">
+        <v>5721</v>
+      </c>
+    </row>
+    <row r="1061" spans="1:9" ht="69" x14ac:dyDescent="0.3">
+      <c r="A1061" s="5" t="s">
+        <v>5429</v>
+      </c>
+      <c r="B1061" s="9" t="s">
+        <v>4486</v>
+      </c>
+      <c r="C1061" s="9" t="s">
+        <v>5722</v>
+      </c>
+      <c r="D1061" s="9" t="s">
+        <v>5723</v>
+      </c>
+      <c r="E1061" s="9" t="s">
+        <v>5724</v>
+      </c>
+      <c r="F1061" s="9" t="s">
+        <v>5725</v>
+      </c>
+      <c r="G1061" s="9" t="s">
+        <v>5726</v>
+      </c>
+      <c r="H1061" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="I1061" s="9" t="s">
+        <v>5727</v>
+      </c>
+    </row>
+    <row r="1062" spans="1:9" ht="55.2" x14ac:dyDescent="0.3">
+      <c r="A1062" s="5" t="s">
+        <v>5430</v>
+      </c>
+      <c r="B1062" s="9" t="s">
+        <v>4504</v>
+      </c>
+      <c r="C1062" s="9" t="s">
+        <v>5728</v>
+      </c>
+      <c r="D1062" s="9" t="s">
+        <v>5729</v>
+      </c>
+      <c r="E1062" s="9" t="s">
+        <v>5730</v>
+      </c>
+      <c r="F1062" s="9" t="s">
+        <v>5731</v>
+      </c>
+      <c r="G1062" s="9" t="s">
+        <v>5732</v>
+      </c>
+      <c r="H1062" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="I1062" s="9" t="s">
+        <v>5733</v>
+      </c>
+    </row>
+    <row r="1063" spans="1:9" ht="55.2" x14ac:dyDescent="0.3">
+      <c r="A1063" s="5" t="s">
+        <v>5430</v>
+      </c>
+      <c r="B1063" s="9" t="s">
+        <v>4504</v>
+      </c>
+      <c r="C1063" s="9" t="s">
+        <v>5734</v>
+      </c>
+      <c r="D1063" s="9" t="s">
+        <v>5735</v>
+      </c>
+      <c r="E1063" s="9" t="s">
+        <v>5736</v>
+      </c>
+      <c r="F1063" s="9" t="s">
+        <v>5737</v>
+      </c>
+      <c r="G1063" s="9" t="s">
+        <v>5738</v>
+      </c>
+      <c r="H1063" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I1063" s="9" t="s">
+        <v>5739</v>
+      </c>
+    </row>
+    <row r="1064" spans="1:9" ht="69" x14ac:dyDescent="0.3">
+      <c r="A1064" s="5" t="s">
+        <v>5430</v>
+      </c>
+      <c r="B1064" s="9" t="s">
+        <v>4517</v>
+      </c>
+      <c r="C1064" s="9" t="s">
+        <v>5740</v>
+      </c>
+      <c r="D1064" s="9" t="s">
+        <v>5741</v>
+      </c>
+      <c r="E1064" s="9" t="s">
+        <v>5742</v>
+      </c>
+      <c r="F1064" s="9" t="s">
+        <v>5743</v>
+      </c>
+      <c r="G1064" s="9" t="s">
+        <v>5744</v>
+      </c>
+      <c r="H1064" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="I1064" s="9" t="s">
+        <v>5745</v>
+      </c>
+    </row>
+    <row r="1065" spans="1:9" ht="55.2" x14ac:dyDescent="0.3">
+      <c r="A1065" s="5" t="s">
+        <v>5430</v>
+      </c>
+      <c r="B1065" s="9" t="s">
+        <v>4517</v>
+      </c>
+      <c r="C1065" s="9" t="s">
+        <v>5746</v>
+      </c>
+      <c r="D1065" s="9" t="s">
+        <v>5747</v>
+      </c>
+      <c r="E1065" s="9" t="s">
+        <v>5748</v>
+      </c>
+      <c r="F1065" s="9" t="s">
+        <v>5749</v>
+      </c>
+      <c r="G1065" s="9" t="s">
+        <v>5750</v>
+      </c>
+      <c r="H1065" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I1065" s="9" t="s">
+        <v>5751</v>
+      </c>
+    </row>
+    <row r="1066" spans="1:9" ht="55.2" x14ac:dyDescent="0.3">
+      <c r="A1066" s="5" t="s">
+        <v>5430</v>
+      </c>
+      <c r="B1066" s="9" t="s">
+        <v>4530</v>
+      </c>
+      <c r="C1066" s="9" t="s">
+        <v>5752</v>
+      </c>
+      <c r="D1066" s="9" t="s">
+        <v>5753</v>
+      </c>
+      <c r="E1066" s="9" t="s">
+        <v>5754</v>
+      </c>
+      <c r="F1066" s="9" t="s">
+        <v>5755</v>
+      </c>
+      <c r="G1066" s="9" t="s">
+        <v>5756</v>
+      </c>
+      <c r="H1066" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I1066" s="9" t="s">
+        <v>5757</v>
+      </c>
+    </row>
+    <row r="1067" spans="1:9" ht="55.2" x14ac:dyDescent="0.3">
+      <c r="A1067" s="5" t="s">
+        <v>5430</v>
+      </c>
+      <c r="B1067" s="9" t="s">
+        <v>4537</v>
+      </c>
+      <c r="C1067" s="9" t="s">
+        <v>5758</v>
+      </c>
+      <c r="D1067" s="9" t="s">
+        <v>5759</v>
+      </c>
+      <c r="E1067" s="9" t="s">
+        <v>5760</v>
+      </c>
+      <c r="F1067" s="9" t="s">
+        <v>5761</v>
+      </c>
+      <c r="G1067" s="9" t="s">
+        <v>5762</v>
+      </c>
+      <c r="H1067" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="I1067" s="9" t="s">
+        <v>5763</v>
+      </c>
+    </row>
+    <row r="1068" spans="1:9" ht="69" x14ac:dyDescent="0.3">
+      <c r="A1068" s="5" t="s">
+        <v>5430</v>
+      </c>
+      <c r="B1068" s="9" t="s">
+        <v>4544</v>
+      </c>
+      <c r="C1068" s="9" t="s">
+        <v>5764</v>
+      </c>
+      <c r="D1068" s="9" t="s">
+        <v>5765</v>
+      </c>
+      <c r="E1068" s="9" t="s">
+        <v>5766</v>
+      </c>
+      <c r="F1068" s="9" t="s">
+        <v>5767</v>
+      </c>
+      <c r="G1068" s="9" t="s">
+        <v>5768</v>
+      </c>
+      <c r="H1068" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="I1068" s="9" t="s">
+        <v>5769</v>
+      </c>
+    </row>
+    <row r="1069" spans="1:9" ht="69" x14ac:dyDescent="0.3">
+      <c r="A1069" s="5" t="s">
+        <v>5430</v>
+      </c>
+      <c r="B1069" s="9" t="s">
+        <v>4551</v>
+      </c>
+      <c r="C1069" s="9" t="s">
+        <v>5770</v>
+      </c>
+      <c r="D1069" s="9" t="s">
+        <v>5771</v>
+      </c>
+      <c r="E1069" s="9" t="s">
+        <v>5772</v>
+      </c>
+      <c r="F1069" s="9" t="s">
+        <v>5773</v>
+      </c>
+      <c r="G1069" s="9" t="s">
+        <v>5774</v>
+      </c>
+      <c r="H1069" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I1069" s="9" t="s">
+        <v>5775</v>
+      </c>
+    </row>
+    <row r="1070" spans="1:9" ht="69" x14ac:dyDescent="0.3">
+      <c r="A1070" s="5" t="s">
+        <v>5430</v>
+      </c>
+      <c r="B1070" s="9" t="s">
+        <v>4558</v>
+      </c>
+      <c r="C1070" s="9" t="s">
+        <v>5776</v>
+      </c>
+      <c r="D1070" s="9" t="s">
+        <v>5777</v>
+      </c>
+      <c r="E1070" s="9" t="s">
+        <v>5778</v>
+      </c>
+      <c r="F1070" s="9" t="s">
+        <v>5779</v>
+      </c>
+      <c r="G1070" s="9" t="s">
+        <v>5780</v>
+      </c>
+      <c r="H1070" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="I1070" s="9" t="s">
+        <v>5781</v>
+      </c>
+    </row>
+    <row r="1071" spans="1:9" ht="69" x14ac:dyDescent="0.3">
+      <c r="A1071" s="5" t="s">
+        <v>5430</v>
+      </c>
+      <c r="B1071" s="9" t="s">
+        <v>4565</v>
+      </c>
+      <c r="C1071" s="9" t="s">
+        <v>5782</v>
+      </c>
+      <c r="D1071" s="9" t="s">
+        <v>5783</v>
+      </c>
+      <c r="E1071" s="9" t="s">
+        <v>5784</v>
+      </c>
+      <c r="F1071" s="9" t="s">
+        <v>5785</v>
+      </c>
+      <c r="G1071" s="9" t="s">
+        <v>5786</v>
+      </c>
+      <c r="H1071" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I1071" s="9" t="s">
+        <v>5787</v>
+      </c>
+    </row>
+    <row r="1072" spans="1:9" ht="69" x14ac:dyDescent="0.3">
+      <c r="A1072" s="5" t="s">
+        <v>5430</v>
+      </c>
+      <c r="B1072" s="9" t="s">
+        <v>4565</v>
+      </c>
+      <c r="C1072" s="9" t="s">
+        <v>5788</v>
+      </c>
+      <c r="D1072" s="9" t="s">
+        <v>5789</v>
+      </c>
+      <c r="E1072" s="9" t="s">
+        <v>5790</v>
+      </c>
+      <c r="F1072" s="9" t="s">
+        <v>5791</v>
+      </c>
+      <c r="G1072" s="9" t="s">
+        <v>5792</v>
+      </c>
+      <c r="H1072" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I1072" s="9" t="s">
+        <v>5793</v>
+      </c>
+    </row>
+    <row r="1073" spans="1:9" ht="69" x14ac:dyDescent="0.3">
+      <c r="A1073" s="5" t="s">
+        <v>5430</v>
+      </c>
+      <c r="B1073" s="9" t="s">
+        <v>4578</v>
+      </c>
+      <c r="C1073" s="9" t="s">
+        <v>5794</v>
+      </c>
+      <c r="D1073" s="9" t="s">
+        <v>5795</v>
+      </c>
+      <c r="E1073" s="9" t="s">
+        <v>5796</v>
+      </c>
+      <c r="F1073" s="9" t="s">
+        <v>5797</v>
+      </c>
+      <c r="G1073" s="9" t="s">
+        <v>5798</v>
+      </c>
+      <c r="H1073" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="I1073" s="9" t="s">
+        <v>5799</v>
+      </c>
+    </row>
+    <row r="1074" spans="1:9" ht="69" x14ac:dyDescent="0.3">
+      <c r="A1074" s="5" t="s">
+        <v>5431</v>
+      </c>
+      <c r="B1074" s="9" t="s">
+        <v>4585</v>
+      </c>
+      <c r="C1074" s="9" t="s">
+        <v>5800</v>
+      </c>
+      <c r="D1074" s="9" t="s">
+        <v>5801</v>
+      </c>
+      <c r="E1074" s="9" t="s">
+        <v>5802</v>
+      </c>
+      <c r="F1074" s="9" t="s">
+        <v>5803</v>
+      </c>
+      <c r="G1074" s="9" t="s">
+        <v>5804</v>
+      </c>
+      <c r="H1074" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="I1074" s="9" t="s">
+        <v>5805</v>
+      </c>
+    </row>
+    <row r="1075" spans="1:9" ht="69" x14ac:dyDescent="0.3">
+      <c r="A1075" s="5" t="s">
+        <v>5431</v>
+      </c>
+      <c r="B1075" s="9" t="s">
+        <v>4592</v>
+      </c>
+      <c r="C1075" s="9" t="s">
+        <v>5806</v>
+      </c>
+      <c r="D1075" s="9" t="s">
+        <v>5807</v>
+      </c>
+      <c r="E1075" s="9" t="s">
+        <v>5808</v>
+      </c>
+      <c r="F1075" s="9" t="s">
+        <v>5809</v>
+      </c>
+      <c r="G1075" s="9" t="s">
+        <v>5810</v>
+      </c>
+      <c r="H1075" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="I1075" s="9" t="s">
+        <v>5811</v>
+      </c>
+    </row>
+    <row r="1076" spans="1:9" ht="55.2" x14ac:dyDescent="0.3">
+      <c r="A1076" s="5" t="s">
+        <v>5431</v>
+      </c>
+      <c r="B1076" s="9" t="s">
+        <v>4592</v>
+      </c>
+      <c r="C1076" s="9" t="s">
+        <v>5812</v>
+      </c>
+      <c r="D1076" s="9" t="s">
+        <v>5813</v>
+      </c>
+      <c r="E1076" s="9" t="s">
+        <v>5814</v>
+      </c>
+      <c r="F1076" s="9" t="s">
+        <v>5815</v>
+      </c>
+      <c r="G1076" s="9" t="s">
+        <v>5816</v>
+      </c>
+      <c r="H1076" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1076" s="9" t="s">
+        <v>5817</v>
+      </c>
+    </row>
+    <row r="1077" spans="1:9" ht="69" x14ac:dyDescent="0.3">
+      <c r="A1077" s="5" t="s">
+        <v>5431</v>
+      </c>
+      <c r="B1077" s="9" t="s">
+        <v>4592</v>
+      </c>
+      <c r="C1077" s="9" t="s">
+        <v>5818</v>
+      </c>
+      <c r="D1077" s="9" t="s">
+        <v>5819</v>
+      </c>
+      <c r="E1077" s="9" t="s">
+        <v>5820</v>
+      </c>
+      <c r="F1077" s="9" t="s">
+        <v>5821</v>
+      </c>
+      <c r="G1077" s="9" t="s">
+        <v>5822</v>
+      </c>
+      <c r="H1077" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1077" s="9" t="s">
+        <v>5823</v>
+      </c>
+    </row>
+    <row r="1078" spans="1:9" ht="55.2" x14ac:dyDescent="0.3">
+      <c r="A1078" s="5" t="s">
+        <v>5431</v>
+      </c>
+      <c r="B1078" s="9" t="s">
+        <v>4611</v>
+      </c>
+      <c r="C1078" s="9" t="s">
+        <v>5824</v>
+      </c>
+      <c r="D1078" s="9" t="s">
+        <v>5825</v>
+      </c>
+      <c r="E1078" s="9" t="s">
+        <v>5826</v>
+      </c>
+      <c r="F1078" s="9" t="s">
+        <v>5827</v>
+      </c>
+      <c r="G1078" s="9" t="s">
+        <v>5828</v>
+      </c>
+      <c r="H1078" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="I1078" s="9" t="s">
+        <v>5829</v>
+      </c>
+    </row>
+    <row r="1079" spans="1:9" ht="55.2" x14ac:dyDescent="0.3">
+      <c r="A1079" s="5" t="s">
+        <v>5431</v>
+      </c>
+      <c r="B1079" s="9" t="s">
+        <v>4618</v>
+      </c>
+      <c r="C1079" s="9" t="s">
+        <v>5830</v>
+      </c>
+      <c r="D1079" s="9" t="s">
+        <v>5831</v>
+      </c>
+      <c r="E1079" s="9" t="s">
+        <v>5832</v>
+      </c>
+      <c r="F1079" s="9" t="s">
+        <v>5833</v>
+      </c>
+      <c r="G1079" s="9" t="s">
+        <v>5834</v>
+      </c>
+      <c r="H1079" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="I1079" s="9" t="s">
+        <v>5835</v>
+      </c>
+    </row>
+    <row r="1080" spans="1:9" ht="55.2" x14ac:dyDescent="0.3">
+      <c r="A1080" s="5" t="s">
+        <v>5431</v>
+      </c>
+      <c r="B1080" s="9" t="s">
+        <v>4618</v>
+      </c>
+      <c r="C1080" s="9" t="s">
+        <v>5836</v>
+      </c>
+      <c r="D1080" s="9" t="s">
+        <v>5837</v>
+      </c>
+      <c r="E1080" s="9" t="s">
+        <v>5838</v>
+      </c>
+      <c r="F1080" s="9" t="s">
+        <v>5839</v>
+      </c>
+      <c r="G1080" s="9" t="s">
+        <v>5840</v>
+      </c>
+      <c r="H1080" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="I1080" s="9" t="s">
+        <v>5841</v>
+      </c>
+    </row>
+    <row r="1081" spans="1:9" ht="55.2" x14ac:dyDescent="0.3">
+      <c r="A1081" s="5" t="s">
+        <v>5431</v>
+      </c>
+      <c r="B1081" s="9" t="s">
+        <v>4618</v>
+      </c>
+      <c r="C1081" s="9" t="s">
+        <v>5842</v>
+      </c>
+      <c r="D1081" s="9" t="s">
+        <v>5843</v>
+      </c>
+      <c r="E1081" s="9" t="s">
+        <v>5844</v>
+      </c>
+      <c r="F1081" s="9" t="s">
+        <v>5845</v>
+      </c>
+      <c r="G1081" s="9" t="s">
+        <v>5846</v>
+      </c>
+      <c r="H1081" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="I1081" s="9" t="s">
+        <v>5847</v>
+      </c>
+    </row>
+    <row r="1082" spans="1:9" ht="55.2" x14ac:dyDescent="0.3">
+      <c r="A1082" s="5" t="s">
+        <v>5431</v>
+      </c>
+      <c r="B1082" s="9" t="s">
+        <v>4618</v>
+      </c>
+      <c r="C1082" s="9" t="s">
+        <v>5848</v>
+      </c>
+      <c r="D1082" s="9" t="s">
+        <v>5849</v>
+      </c>
+      <c r="E1082" s="9" t="s">
+        <v>5850</v>
+      </c>
+      <c r="F1082" s="9" t="s">
+        <v>5851</v>
+      </c>
+      <c r="G1082" s="9" t="s">
+        <v>5852</v>
+      </c>
+      <c r="H1082" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="I1082" s="9" t="s">
+        <v>5853</v>
+      </c>
+    </row>
+    <row r="1083" spans="1:9" ht="55.2" x14ac:dyDescent="0.3">
+      <c r="A1083" s="5" t="s">
+        <v>5431</v>
+      </c>
+      <c r="B1083" s="9" t="s">
+        <v>4643</v>
+      </c>
+      <c r="C1083" s="9" t="s">
+        <v>5854</v>
+      </c>
+      <c r="D1083" s="9" t="s">
+        <v>5855</v>
+      </c>
+      <c r="E1083" s="9" t="s">
+        <v>5856</v>
+      </c>
+      <c r="F1083" s="9" t="s">
+        <v>5857</v>
+      </c>
+      <c r="G1083" s="9" t="s">
+        <v>5858</v>
+      </c>
+      <c r="H1083" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="I1083" s="9" t="s">
+        <v>5859</v>
+      </c>
+    </row>
+    <row r="1084" spans="1:9" ht="55.2" x14ac:dyDescent="0.3">
+      <c r="A1084" s="5" t="s">
+        <v>5431</v>
+      </c>
+      <c r="B1084" s="9" t="s">
+        <v>4643</v>
+      </c>
+      <c r="C1084" s="9" t="s">
+        <v>5860</v>
+      </c>
+      <c r="D1084" s="9" t="s">
+        <v>5861</v>
+      </c>
+      <c r="E1084" s="9" t="s">
+        <v>5862</v>
+      </c>
+      <c r="F1084" s="9" t="s">
+        <v>5863</v>
+      </c>
+      <c r="G1084" s="9" t="s">
+        <v>5864</v>
+      </c>
+      <c r="H1084" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I1084" s="9" t="s">
+        <v>5865</v>
+      </c>
+    </row>
+    <row r="1085" spans="1:9" ht="69" x14ac:dyDescent="0.3">
+      <c r="A1085" s="5" t="s">
+        <v>5431</v>
+      </c>
+      <c r="B1085" s="9" t="s">
+        <v>4643</v>
+      </c>
+      <c r="C1085" s="9" t="s">
+        <v>5866</v>
+      </c>
+      <c r="D1085" s="9" t="s">
+        <v>5867</v>
+      </c>
+      <c r="E1085" s="9" t="s">
+        <v>5868</v>
+      </c>
+      <c r="F1085" s="9" t="s">
+        <v>5869</v>
+      </c>
+      <c r="G1085" s="9" t="s">
+        <v>5870</v>
+      </c>
+      <c r="H1085" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1085" s="9" t="s">
+        <v>5871</v>
+      </c>
+    </row>
+    <row r="1086" spans="1:9" ht="69" x14ac:dyDescent="0.3">
+      <c r="A1086" s="5" t="s">
+        <v>5431</v>
+      </c>
+      <c r="B1086" s="9" t="s">
+        <v>4662</v>
+      </c>
+      <c r="C1086" s="9" t="s">
+        <v>5872</v>
+      </c>
+      <c r="D1086" s="9" t="s">
+        <v>5873</v>
+      </c>
+      <c r="E1086" s="9" t="s">
+        <v>5874</v>
+      </c>
+      <c r="F1086" s="9" t="s">
+        <v>5875</v>
+      </c>
+      <c r="G1086" s="9" t="s">
+        <v>5876</v>
+      </c>
+      <c r="H1086" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="I1086" s="9" t="s">
+        <v>5877</v>
+      </c>
+    </row>
+    <row r="1087" spans="1:9" ht="55.2" x14ac:dyDescent="0.3">
+      <c r="A1087" s="5" t="s">
+        <v>5431</v>
+      </c>
+      <c r="B1087" s="9" t="s">
+        <v>4662</v>
+      </c>
+      <c r="C1087" s="9" t="s">
+        <v>5878</v>
+      </c>
+      <c r="D1087" s="9" t="s">
+        <v>5879</v>
+      </c>
+      <c r="E1087" s="9" t="s">
+        <v>5880</v>
+      </c>
+      <c r="F1087" s="9" t="s">
+        <v>5881</v>
+      </c>
+      <c r="G1087" s="9" t="s">
+        <v>5882</v>
+      </c>
+      <c r="H1087" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="I1087" s="9" t="s">
+        <v>5883</v>
+      </c>
+    </row>
+    <row r="1088" spans="1:9" ht="55.2" x14ac:dyDescent="0.3">
+      <c r="A1088" s="5" t="s">
+        <v>5431</v>
+      </c>
+      <c r="B1088" s="9" t="s">
+        <v>4675</v>
+      </c>
+      <c r="C1088" s="9" t="s">
+        <v>5884</v>
+      </c>
+      <c r="D1088" s="9" t="s">
+        <v>5885</v>
+      </c>
+      <c r="E1088" s="9" t="s">
+        <v>5886</v>
+      </c>
+      <c r="F1088" s="9" t="s">
+        <v>5887</v>
+      </c>
+      <c r="G1088" s="9" t="s">
+        <v>5888</v>
+      </c>
+      <c r="H1088" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I1088" s="9" t="s">
+        <v>5889</v>
+      </c>
+    </row>
+    <row r="1089" spans="1:9" ht="55.2" x14ac:dyDescent="0.3">
+      <c r="A1089" s="5" t="s">
+        <v>5431</v>
+      </c>
+      <c r="B1089" s="9" t="s">
+        <v>4675</v>
+      </c>
+      <c r="C1089" s="9" t="s">
+        <v>5890</v>
+      </c>
+      <c r="D1089" s="9" t="s">
+        <v>5891</v>
+      </c>
+      <c r="E1089" s="9" t="s">
+        <v>5892</v>
+      </c>
+      <c r="F1089" s="9" t="s">
+        <v>5893</v>
+      </c>
+      <c r="G1089" s="9" t="s">
+        <v>5894</v>
+      </c>
+      <c r="H1089" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="I1089" s="9" t="s">
+        <v>5895</v>
+      </c>
+    </row>
+    <row r="1090" spans="1:9" ht="55.2" x14ac:dyDescent="0.3">
+      <c r="A1090" s="5" t="s">
+        <v>5431</v>
+      </c>
+      <c r="B1090" s="9" t="s">
+        <v>4688</v>
+      </c>
+      <c r="C1090" s="9" t="s">
+        <v>5896</v>
+      </c>
+      <c r="D1090" s="9" t="s">
+        <v>5897</v>
+      </c>
+      <c r="E1090" s="9" t="s">
+        <v>5898</v>
+      </c>
+      <c r="F1090" s="9" t="s">
+        <v>5899</v>
+      </c>
+      <c r="G1090" s="9" t="s">
+        <v>5900</v>
+      </c>
+      <c r="H1090" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I1090" s="9" t="s">
+        <v>5901</v>
+      </c>
+    </row>
+    <row r="1091" spans="1:9" ht="55.2" x14ac:dyDescent="0.3">
+      <c r="A1091" s="5" t="s">
+        <v>5431</v>
+      </c>
+      <c r="B1091" s="9" t="s">
+        <v>4688</v>
+      </c>
+      <c r="C1091" s="9" t="s">
+        <v>5902</v>
+      </c>
+      <c r="D1091" s="9" t="s">
+        <v>5903</v>
+      </c>
+      <c r="E1091" s="9" t="s">
+        <v>5904</v>
+      </c>
+      <c r="F1091" s="9" t="s">
+        <v>5905</v>
+      </c>
+      <c r="G1091" s="9" t="s">
+        <v>5906</v>
+      </c>
+      <c r="H1091" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="I1091" s="9" t="s">
+        <v>5907</v>
+      </c>
+    </row>
+    <row r="1092" spans="1:9" ht="55.2" x14ac:dyDescent="0.3">
+      <c r="A1092" s="5" t="s">
+        <v>5432</v>
+      </c>
+      <c r="B1092" s="9" t="s">
+        <v>4701</v>
+      </c>
+      <c r="C1092" s="9" t="s">
+        <v>5908</v>
+      </c>
+      <c r="D1092" s="9" t="s">
+        <v>5909</v>
+      </c>
+      <c r="E1092" s="9" t="s">
+        <v>5910</v>
+      </c>
+      <c r="F1092" s="9" t="s">
+        <v>5911</v>
+      </c>
+      <c r="G1092" s="9" t="s">
+        <v>5912</v>
+      </c>
+      <c r="H1092" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="I1092" s="9" t="s">
+        <v>5913</v>
+      </c>
+    </row>
+    <row r="1093" spans="1:9" ht="55.2" x14ac:dyDescent="0.3">
+      <c r="A1093" s="5" t="s">
+        <v>5432</v>
+      </c>
+      <c r="B1093" s="9" t="s">
+        <v>4701</v>
+      </c>
+      <c r="C1093" s="9" t="s">
+        <v>5914</v>
+      </c>
+      <c r="D1093" s="9" t="s">
+        <v>5915</v>
+      </c>
+      <c r="E1093" s="9" t="s">
+        <v>5916</v>
+      </c>
+      <c r="F1093" s="9" t="s">
+        <v>5917</v>
+      </c>
+      <c r="G1093" s="9" t="s">
+        <v>5918</v>
+      </c>
+      <c r="H1093" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I1093" s="9" t="s">
+        <v>5919</v>
+      </c>
+    </row>
+    <row r="1094" spans="1:9" ht="69" x14ac:dyDescent="0.3">
+      <c r="A1094" s="5" t="s">
+        <v>5432</v>
+      </c>
+      <c r="B1094" s="9" t="s">
+        <v>4701</v>
+      </c>
+      <c r="C1094" s="9" t="s">
+        <v>5920</v>
+      </c>
+      <c r="D1094" s="9" t="s">
+        <v>5921</v>
+      </c>
+      <c r="E1094" s="9" t="s">
+        <v>5922</v>
+      </c>
+      <c r="F1094" s="9" t="s">
+        <v>5923</v>
+      </c>
+      <c r="G1094" s="9" t="s">
+        <v>5924</v>
+      </c>
+      <c r="H1094" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1094" s="9" t="s">
+        <v>5925</v>
+      </c>
+    </row>
+    <row r="1095" spans="1:9" ht="55.2" x14ac:dyDescent="0.3">
+      <c r="A1095" s="5" t="s">
+        <v>5432</v>
+      </c>
+      <c r="B1095" s="9" t="s">
+        <v>4720</v>
+      </c>
+      <c r="C1095" s="9" t="s">
+        <v>5926</v>
+      </c>
+      <c r="D1095" s="9" t="s">
+        <v>5927</v>
+      </c>
+      <c r="E1095" s="9" t="s">
+        <v>5928</v>
+      </c>
+      <c r="F1095" s="9" t="s">
+        <v>5929</v>
+      </c>
+      <c r="G1095" s="9" t="s">
+        <v>5930</v>
+      </c>
+      <c r="H1095" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1095" s="9" t="s">
+        <v>5931</v>
+      </c>
+    </row>
+    <row r="1096" spans="1:9" ht="55.2" x14ac:dyDescent="0.3">
+      <c r="A1096" s="5" t="s">
+        <v>5432</v>
+      </c>
+      <c r="B1096" s="9" t="s">
+        <v>4720</v>
+      </c>
+      <c r="C1096" s="9" t="s">
+        <v>5932</v>
+      </c>
+      <c r="D1096" s="9" t="s">
+        <v>5933</v>
+      </c>
+      <c r="E1096" s="9" t="s">
+        <v>5934</v>
+      </c>
+      <c r="F1096" s="9" t="s">
+        <v>5935</v>
+      </c>
+      <c r="G1096" s="9" t="s">
+        <v>5936</v>
+      </c>
+      <c r="H1096" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1096" s="9" t="s">
+        <v>5937</v>
+      </c>
+    </row>
+    <row r="1097" spans="1:9" ht="69" x14ac:dyDescent="0.3">
+      <c r="A1097" s="5" t="s">
+        <v>5432</v>
+      </c>
+      <c r="B1097" s="9" t="s">
+        <v>4720</v>
+      </c>
+      <c r="C1097" s="9" t="s">
+        <v>5938</v>
+      </c>
+      <c r="D1097" s="9" t="s">
+        <v>5939</v>
+      </c>
+      <c r="E1097" s="9" t="s">
+        <v>5940</v>
+      </c>
+      <c r="F1097" s="9" t="s">
+        <v>5941</v>
+      </c>
+      <c r="G1097" s="9" t="s">
+        <v>5942</v>
+      </c>
+      <c r="H1097" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="I1097" s="9" t="s">
+        <v>5943</v>
+      </c>
+    </row>
+    <row r="1098" spans="1:9" ht="55.2" x14ac:dyDescent="0.3">
+      <c r="A1098" s="5" t="s">
+        <v>5432</v>
+      </c>
+      <c r="B1098" s="9" t="s">
+        <v>4720</v>
+      </c>
+      <c r="C1098" s="9" t="s">
+        <v>5944</v>
+      </c>
+      <c r="D1098" s="9" t="s">
+        <v>5945</v>
+      </c>
+      <c r="E1098" s="9" t="s">
+        <v>5946</v>
+      </c>
+      <c r="F1098" s="9" t="s">
+        <v>5947</v>
+      </c>
+      <c r="G1098" s="9" t="s">
+        <v>5948</v>
+      </c>
+      <c r="H1098" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="I1098" s="9" t="s">
+        <v>5949</v>
+      </c>
+    </row>
+    <row r="1099" spans="1:9" ht="55.2" x14ac:dyDescent="0.3">
+      <c r="A1099" s="5" t="s">
+        <v>5432</v>
+      </c>
+      <c r="B1099" s="9" t="s">
+        <v>4745</v>
+      </c>
+      <c r="C1099" s="9" t="s">
+        <v>5950</v>
+      </c>
+      <c r="D1099" s="9" t="s">
+        <v>5951</v>
+      </c>
+      <c r="E1099" s="9" t="s">
+        <v>5952</v>
+      </c>
+      <c r="F1099" s="9" t="s">
+        <v>5953</v>
+      </c>
+      <c r="G1099" s="9" t="s">
+        <v>5954</v>
+      </c>
+      <c r="H1099" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1099" s="9" t="s">
+        <v>5955</v>
+      </c>
+    </row>
+    <row r="1100" spans="1:9" ht="55.2" x14ac:dyDescent="0.3">
+      <c r="A1100" s="5" t="s">
+        <v>5432</v>
+      </c>
+      <c r="B1100" s="9" t="s">
+        <v>4745</v>
+      </c>
+      <c r="C1100" s="9" t="s">
+        <v>5956</v>
+      </c>
+      <c r="D1100" s="9" t="s">
+        <v>5957</v>
+      </c>
+      <c r="E1100" s="9" t="s">
+        <v>5958</v>
+      </c>
+      <c r="F1100" s="9" t="s">
+        <v>5959</v>
+      </c>
+      <c r="G1100" s="9" t="s">
+        <v>5960</v>
+      </c>
+      <c r="H1100" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="I1100" s="9" t="s">
+        <v>5961</v>
+      </c>
+    </row>
+    <row r="1101" spans="1:9" ht="55.2" x14ac:dyDescent="0.3">
+      <c r="A1101" s="5" t="s">
+        <v>5432</v>
+      </c>
+      <c r="B1101" s="9" t="s">
+        <v>4745</v>
+      </c>
+      <c r="C1101" s="9" t="s">
+        <v>5962</v>
+      </c>
+      <c r="D1101" s="9" t="s">
+        <v>5963</v>
+      </c>
+      <c r="E1101" s="9" t="s">
+        <v>5964</v>
+      </c>
+      <c r="F1101" s="9" t="s">
+        <v>5965</v>
+      </c>
+      <c r="G1101" s="9" t="s">
+        <v>5966</v>
+      </c>
+      <c r="H1101" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I1101" s="9" t="s">
+        <v>5967</v>
+      </c>
+    </row>
+    <row r="1102" spans="1:9" ht="55.2" x14ac:dyDescent="0.3">
+      <c r="A1102" s="5" t="s">
+        <v>5432</v>
+      </c>
+      <c r="B1102" s="9" t="s">
+        <v>4764</v>
+      </c>
+      <c r="C1102" s="9" t="s">
+        <v>5968</v>
+      </c>
+      <c r="D1102" s="9" t="s">
+        <v>5969</v>
+      </c>
+      <c r="E1102" s="9" t="s">
+        <v>5970</v>
+      </c>
+      <c r="F1102" s="9" t="s">
+        <v>5971</v>
+      </c>
+      <c r="G1102" s="9" t="s">
+        <v>5972</v>
+      </c>
+      <c r="H1102" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="I1102" s="9" t="s">
+        <v>5973</v>
+      </c>
+    </row>
+    <row r="1103" spans="1:9" ht="55.2" x14ac:dyDescent="0.3">
+      <c r="A1103" s="5" t="s">
+        <v>5432</v>
+      </c>
+      <c r="B1103" s="9" t="s">
+        <v>4764</v>
+      </c>
+      <c r="C1103" s="9" t="s">
+        <v>5974</v>
+      </c>
+      <c r="D1103" s="9" t="s">
+        <v>5975</v>
+      </c>
+      <c r="E1103" s="9" t="s">
+        <v>5976</v>
+      </c>
+      <c r="F1103" s="9" t="s">
+        <v>5977</v>
+      </c>
+      <c r="G1103" s="9" t="s">
+        <v>5978</v>
+      </c>
+      <c r="H1103" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1103" s="9" t="s">
+        <v>5979</v>
+      </c>
+    </row>
+    <row r="1104" spans="1:9" ht="55.2" x14ac:dyDescent="0.3">
+      <c r="A1104" s="5" t="s">
+        <v>5432</v>
+      </c>
+      <c r="B1104" s="9" t="s">
+        <v>4777</v>
+      </c>
+      <c r="C1104" s="9" t="s">
+        <v>5980</v>
+      </c>
+      <c r="D1104" s="9" t="s">
+        <v>5981</v>
+      </c>
+      <c r="E1104" s="9" t="s">
+        <v>5982</v>
+      </c>
+      <c r="F1104" s="9" t="s">
+        <v>5983</v>
+      </c>
+      <c r="G1104" s="9" t="s">
+        <v>5984</v>
+      </c>
+      <c r="H1104" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="I1104" s="9" t="s">
+        <v>5985</v>
+      </c>
+    </row>
+    <row r="1105" spans="1:9" ht="55.2" x14ac:dyDescent="0.3">
+      <c r="A1105" s="5" t="s">
+        <v>5432</v>
+      </c>
+      <c r="B1105" s="9" t="s">
+        <v>4777</v>
+      </c>
+      <c r="C1105" s="9" t="s">
+        <v>5986</v>
+      </c>
+      <c r="D1105" s="9" t="s">
+        <v>5987</v>
+      </c>
+      <c r="E1105" s="9" t="s">
+        <v>5988</v>
+      </c>
+      <c r="F1105" s="9" t="s">
+        <v>5989</v>
+      </c>
+      <c r="G1105" s="9" t="s">
+        <v>5990</v>
+      </c>
+      <c r="H1105" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="I1105" s="9" t="s">
+        <v>5991</v>
+      </c>
+    </row>
+    <row r="1106" spans="1:9" ht="55.2" x14ac:dyDescent="0.3">
+      <c r="A1106" s="5" t="s">
+        <v>5432</v>
+      </c>
+      <c r="B1106" s="9" t="s">
+        <v>4777</v>
+      </c>
+      <c r="C1106" s="9" t="s">
+        <v>5992</v>
+      </c>
+      <c r="D1106" s="9" t="s">
+        <v>5993</v>
+      </c>
+      <c r="E1106" s="9" t="s">
+        <v>5994</v>
+      </c>
+      <c r="F1106" s="9" t="s">
+        <v>5995</v>
+      </c>
+      <c r="G1106" s="9" t="s">
+        <v>5996</v>
+      </c>
+      <c r="H1106" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I1106" s="9" t="s">
+        <v>5997</v>
+      </c>
+    </row>
+    <row r="1107" spans="1:9" ht="55.2" x14ac:dyDescent="0.3">
+      <c r="A1107" s="5" t="s">
+        <v>5432</v>
+      </c>
+      <c r="B1107" s="9" t="s">
+        <v>4796</v>
+      </c>
+      <c r="C1107" s="9" t="s">
+        <v>5998</v>
+      </c>
+      <c r="D1107" s="9" t="s">
+        <v>5999</v>
+      </c>
+      <c r="E1107" s="9" t="s">
+        <v>6000</v>
+      </c>
+      <c r="F1107" s="9" t="s">
+        <v>6001</v>
+      </c>
+      <c r="G1107" s="9" t="s">
+        <v>6002</v>
+      </c>
+      <c r="H1107" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="I1107" s="9" t="s">
+        <v>6003</v>
+      </c>
+    </row>
+    <row r="1108" spans="1:9" ht="69" x14ac:dyDescent="0.3">
+      <c r="A1108" s="5" t="s">
+        <v>5432</v>
+      </c>
+      <c r="B1108" s="9" t="s">
+        <v>4796</v>
+      </c>
+      <c r="C1108" s="9" t="s">
+        <v>6004</v>
+      </c>
+      <c r="D1108" s="9" t="s">
+        <v>6005</v>
+      </c>
+      <c r="E1108" s="9" t="s">
+        <v>6006</v>
+      </c>
+      <c r="F1108" s="9" t="s">
+        <v>6007</v>
+      </c>
+      <c r="G1108" s="9" t="s">
+        <v>6008</v>
+      </c>
+      <c r="H1108" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1108" s="9" t="s">
+        <v>6009</v>
+      </c>
+    </row>
+    <row r="1109" spans="1:9" ht="55.2" x14ac:dyDescent="0.3">
+      <c r="A1109" s="5" t="s">
+        <v>5432</v>
+      </c>
+      <c r="B1109" s="9" t="s">
+        <v>4809</v>
+      </c>
+      <c r="C1109" s="9" t="s">
+        <v>6010</v>
+      </c>
+      <c r="D1109" s="9" t="s">
+        <v>6011</v>
+      </c>
+      <c r="E1109" s="9" t="s">
+        <v>6012</v>
+      </c>
+      <c r="F1109" s="9" t="s">
+        <v>6013</v>
+      </c>
+      <c r="G1109" s="9" t="s">
+        <v>6014</v>
+      </c>
+      <c r="H1109" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="I1109" s="9" t="s">
+        <v>6015</v>
+      </c>
+    </row>
+    <row r="1110" spans="1:9" ht="55.2" x14ac:dyDescent="0.3">
+      <c r="A1110" s="5" t="s">
+        <v>5432</v>
+      </c>
+      <c r="B1110" s="9" t="s">
+        <v>4816</v>
+      </c>
+      <c r="C1110" s="9" t="s">
+        <v>6016</v>
+      </c>
+      <c r="D1110" s="9" t="s">
+        <v>6017</v>
+      </c>
+      <c r="E1110" s="9" t="s">
+        <v>6018</v>
+      </c>
+      <c r="F1110" s="9" t="s">
+        <v>6019</v>
+      </c>
+      <c r="G1110" s="9" t="s">
+        <v>6020</v>
+      </c>
+      <c r="H1110" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1110" s="9" t="s">
+        <v>6021</v>
+      </c>
+    </row>
+    <row r="1111" spans="1:9" ht="55.2" x14ac:dyDescent="0.3">
+      <c r="A1111" s="5" t="s">
+        <v>5432</v>
+      </c>
+      <c r="B1111" s="9" t="s">
+        <v>4823</v>
+      </c>
+      <c r="C1111" s="9" t="s">
+        <v>6022</v>
+      </c>
+      <c r="D1111" s="9" t="s">
+        <v>6023</v>
+      </c>
+      <c r="E1111" s="9" t="s">
+        <v>6024</v>
+      </c>
+      <c r="F1111" s="9" t="s">
+        <v>6025</v>
+      </c>
+      <c r="G1111" s="9" t="s">
+        <v>6026</v>
+      </c>
+      <c r="H1111" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I1111" s="9" t="s">
+        <v>6027</v>
       </c>
     </row>
   </sheetData>
